--- a/dados_coletados/normal/primeiroteste_helicenormal.xlsx
+++ b/dados_coletados/normal/primeiroteste_helicenormal.xlsx
@@ -3745,961 +3745,961 @@
                   <c:v>-785</c:v>
                 </c:pt>
                 <c:pt idx="334">
-                  <c:v>-796</c:v>
+                  <c:v>-616</c:v>
                 </c:pt>
                 <c:pt idx="335">
-                  <c:v>-807</c:v>
+                  <c:v>-627</c:v>
                 </c:pt>
                 <c:pt idx="336">
-                  <c:v>-818</c:v>
+                  <c:v>-638</c:v>
                 </c:pt>
                 <c:pt idx="337">
-                  <c:v>-838</c:v>
+                  <c:v>-658</c:v>
                 </c:pt>
                 <c:pt idx="338">
-                  <c:v>-846</c:v>
+                  <c:v>-666</c:v>
                 </c:pt>
                 <c:pt idx="339">
-                  <c:v>-847</c:v>
+                  <c:v>-667</c:v>
                 </c:pt>
                 <c:pt idx="340">
-                  <c:v>-847</c:v>
+                  <c:v>-667</c:v>
                 </c:pt>
                 <c:pt idx="341">
-                  <c:v>-847</c:v>
+                  <c:v>-667</c:v>
                 </c:pt>
                 <c:pt idx="342">
-                  <c:v>-847</c:v>
+                  <c:v>-667</c:v>
                 </c:pt>
                 <c:pt idx="343">
-                  <c:v>-846</c:v>
+                  <c:v>-666</c:v>
                 </c:pt>
                 <c:pt idx="344">
-                  <c:v>-846</c:v>
+                  <c:v>-666</c:v>
                 </c:pt>
                 <c:pt idx="345">
-                  <c:v>-846</c:v>
+                  <c:v>-666</c:v>
                 </c:pt>
                 <c:pt idx="346">
-                  <c:v>-847</c:v>
+                  <c:v>-667</c:v>
                 </c:pt>
                 <c:pt idx="347">
-                  <c:v>-847</c:v>
+                  <c:v>-667</c:v>
                 </c:pt>
                 <c:pt idx="348">
-                  <c:v>-847</c:v>
+                  <c:v>-667</c:v>
                 </c:pt>
                 <c:pt idx="349">
-                  <c:v>-847</c:v>
+                  <c:v>-667</c:v>
                 </c:pt>
                 <c:pt idx="350">
-                  <c:v>-847</c:v>
+                  <c:v>-667</c:v>
                 </c:pt>
                 <c:pt idx="351">
-                  <c:v>-848</c:v>
+                  <c:v>-668</c:v>
                 </c:pt>
                 <c:pt idx="352">
-                  <c:v>-848</c:v>
+                  <c:v>-668</c:v>
                 </c:pt>
                 <c:pt idx="353">
-                  <c:v>-849</c:v>
+                  <c:v>-669</c:v>
                 </c:pt>
                 <c:pt idx="354">
-                  <c:v>-849</c:v>
+                  <c:v>-669</c:v>
                 </c:pt>
                 <c:pt idx="355">
-                  <c:v>-849</c:v>
+                  <c:v>-669</c:v>
                 </c:pt>
                 <c:pt idx="356">
-                  <c:v>-850</c:v>
+                  <c:v>-670</c:v>
                 </c:pt>
                 <c:pt idx="357">
-                  <c:v>-850</c:v>
+                  <c:v>-670</c:v>
                 </c:pt>
                 <c:pt idx="358">
-                  <c:v>-850</c:v>
+                  <c:v>-670</c:v>
                 </c:pt>
                 <c:pt idx="359">
-                  <c:v>-850</c:v>
+                  <c:v>-670</c:v>
                 </c:pt>
                 <c:pt idx="360">
-                  <c:v>-851</c:v>
+                  <c:v>-671</c:v>
                 </c:pt>
                 <c:pt idx="361">
-                  <c:v>-851</c:v>
+                  <c:v>-671</c:v>
                 </c:pt>
                 <c:pt idx="362">
-                  <c:v>-852</c:v>
+                  <c:v>-672</c:v>
                 </c:pt>
                 <c:pt idx="363">
-                  <c:v>-852</c:v>
+                  <c:v>-672</c:v>
                 </c:pt>
                 <c:pt idx="364">
-                  <c:v>-853</c:v>
+                  <c:v>-673</c:v>
                 </c:pt>
                 <c:pt idx="365">
-                  <c:v>-853</c:v>
+                  <c:v>-673</c:v>
                 </c:pt>
                 <c:pt idx="366">
-                  <c:v>-853</c:v>
+                  <c:v>-673</c:v>
                 </c:pt>
                 <c:pt idx="367">
-                  <c:v>-853</c:v>
+                  <c:v>-673</c:v>
                 </c:pt>
                 <c:pt idx="368">
-                  <c:v>-853</c:v>
+                  <c:v>-673</c:v>
                 </c:pt>
                 <c:pt idx="369">
-                  <c:v>-854</c:v>
+                  <c:v>-674</c:v>
                 </c:pt>
                 <c:pt idx="370">
-                  <c:v>-854</c:v>
+                  <c:v>-674</c:v>
                 </c:pt>
                 <c:pt idx="371">
-                  <c:v>-855</c:v>
+                  <c:v>-675</c:v>
                 </c:pt>
                 <c:pt idx="372">
-                  <c:v>-855</c:v>
+                  <c:v>-675</c:v>
                 </c:pt>
                 <c:pt idx="373">
-                  <c:v>-855</c:v>
+                  <c:v>-675</c:v>
                 </c:pt>
                 <c:pt idx="374">
-                  <c:v>-855</c:v>
+                  <c:v>-675</c:v>
                 </c:pt>
                 <c:pt idx="375">
-                  <c:v>-855</c:v>
+                  <c:v>-675</c:v>
                 </c:pt>
                 <c:pt idx="376">
-                  <c:v>-855</c:v>
+                  <c:v>-675</c:v>
                 </c:pt>
                 <c:pt idx="377">
-                  <c:v>-855</c:v>
+                  <c:v>-675</c:v>
                 </c:pt>
                 <c:pt idx="378">
-                  <c:v>-856</c:v>
+                  <c:v>-676</c:v>
                 </c:pt>
                 <c:pt idx="379">
-                  <c:v>-856</c:v>
+                  <c:v>-676</c:v>
                 </c:pt>
                 <c:pt idx="380">
-                  <c:v>-856</c:v>
+                  <c:v>-676</c:v>
                 </c:pt>
                 <c:pt idx="381">
-                  <c:v>-857</c:v>
+                  <c:v>-677</c:v>
                 </c:pt>
                 <c:pt idx="382">
-                  <c:v>-857</c:v>
+                  <c:v>-677</c:v>
                 </c:pt>
                 <c:pt idx="383">
-                  <c:v>-858</c:v>
+                  <c:v>-678</c:v>
                 </c:pt>
                 <c:pt idx="384">
-                  <c:v>-858</c:v>
+                  <c:v>-678</c:v>
                 </c:pt>
                 <c:pt idx="385">
-                  <c:v>-858</c:v>
+                  <c:v>-678</c:v>
                 </c:pt>
                 <c:pt idx="386">
-                  <c:v>-858</c:v>
+                  <c:v>-678</c:v>
                 </c:pt>
                 <c:pt idx="387">
-                  <c:v>-858</c:v>
+                  <c:v>-678</c:v>
                 </c:pt>
                 <c:pt idx="388">
-                  <c:v>-858</c:v>
+                  <c:v>-678</c:v>
                 </c:pt>
                 <c:pt idx="389">
-                  <c:v>-858</c:v>
+                  <c:v>-678</c:v>
                 </c:pt>
                 <c:pt idx="390">
-                  <c:v>-858</c:v>
+                  <c:v>-678</c:v>
                 </c:pt>
                 <c:pt idx="391">
-                  <c:v>-858</c:v>
+                  <c:v>-678</c:v>
                 </c:pt>
                 <c:pt idx="392">
-                  <c:v>-858</c:v>
+                  <c:v>-678</c:v>
                 </c:pt>
                 <c:pt idx="393">
-                  <c:v>-858</c:v>
+                  <c:v>-678</c:v>
                 </c:pt>
                 <c:pt idx="394">
-                  <c:v>-858</c:v>
+                  <c:v>-678</c:v>
                 </c:pt>
                 <c:pt idx="395">
-                  <c:v>-857</c:v>
+                  <c:v>-677</c:v>
                 </c:pt>
                 <c:pt idx="396">
-                  <c:v>-856</c:v>
+                  <c:v>-676</c:v>
                 </c:pt>
                 <c:pt idx="397">
-                  <c:v>-856</c:v>
+                  <c:v>-676</c:v>
                 </c:pt>
                 <c:pt idx="398">
-                  <c:v>-855</c:v>
+                  <c:v>-675</c:v>
                 </c:pt>
                 <c:pt idx="399">
-                  <c:v>-855</c:v>
+                  <c:v>-675</c:v>
                 </c:pt>
                 <c:pt idx="400">
-                  <c:v>-854</c:v>
+                  <c:v>-674</c:v>
                 </c:pt>
                 <c:pt idx="401">
-                  <c:v>-854</c:v>
+                  <c:v>-674</c:v>
                 </c:pt>
                 <c:pt idx="402">
-                  <c:v>-854</c:v>
+                  <c:v>-674</c:v>
                 </c:pt>
                 <c:pt idx="403">
-                  <c:v>-854</c:v>
+                  <c:v>-674</c:v>
                 </c:pt>
                 <c:pt idx="404">
-                  <c:v>-853</c:v>
+                  <c:v>-673</c:v>
                 </c:pt>
                 <c:pt idx="405">
-                  <c:v>-853</c:v>
+                  <c:v>-673</c:v>
                 </c:pt>
                 <c:pt idx="406">
-                  <c:v>-853</c:v>
+                  <c:v>-673</c:v>
                 </c:pt>
                 <c:pt idx="407">
-                  <c:v>-853</c:v>
+                  <c:v>-673</c:v>
                 </c:pt>
                 <c:pt idx="408">
-                  <c:v>-853</c:v>
+                  <c:v>-673</c:v>
                 </c:pt>
                 <c:pt idx="409">
-                  <c:v>-853</c:v>
+                  <c:v>-673</c:v>
                 </c:pt>
                 <c:pt idx="410">
-                  <c:v>-853</c:v>
+                  <c:v>-673</c:v>
                 </c:pt>
                 <c:pt idx="411">
-                  <c:v>-853</c:v>
+                  <c:v>-673</c:v>
                 </c:pt>
                 <c:pt idx="412">
-                  <c:v>-854</c:v>
+                  <c:v>-674</c:v>
                 </c:pt>
                 <c:pt idx="413">
-                  <c:v>-854</c:v>
+                  <c:v>-674</c:v>
                 </c:pt>
                 <c:pt idx="414">
-                  <c:v>-854</c:v>
+                  <c:v>-674</c:v>
                 </c:pt>
                 <c:pt idx="415">
-                  <c:v>-854</c:v>
+                  <c:v>-674</c:v>
                 </c:pt>
                 <c:pt idx="416">
-                  <c:v>-855</c:v>
+                  <c:v>-675</c:v>
                 </c:pt>
                 <c:pt idx="417">
-                  <c:v>-855</c:v>
+                  <c:v>-675</c:v>
                 </c:pt>
                 <c:pt idx="418">
-                  <c:v>-855</c:v>
+                  <c:v>-675</c:v>
                 </c:pt>
                 <c:pt idx="419">
-                  <c:v>-855</c:v>
+                  <c:v>-675</c:v>
                 </c:pt>
                 <c:pt idx="420">
-                  <c:v>-855</c:v>
+                  <c:v>-675</c:v>
                 </c:pt>
                 <c:pt idx="421">
-                  <c:v>-855</c:v>
+                  <c:v>-675</c:v>
                 </c:pt>
                 <c:pt idx="422">
-                  <c:v>-855</c:v>
+                  <c:v>-675</c:v>
                 </c:pt>
                 <c:pt idx="423">
-                  <c:v>-855</c:v>
+                  <c:v>-675</c:v>
                 </c:pt>
                 <c:pt idx="424">
-                  <c:v>-855</c:v>
+                  <c:v>-675</c:v>
                 </c:pt>
                 <c:pt idx="425">
-                  <c:v>-855</c:v>
+                  <c:v>-675</c:v>
                 </c:pt>
                 <c:pt idx="426">
-                  <c:v>-855</c:v>
+                  <c:v>-675</c:v>
                 </c:pt>
                 <c:pt idx="427">
-                  <c:v>-855</c:v>
+                  <c:v>-675</c:v>
                 </c:pt>
                 <c:pt idx="428">
-                  <c:v>-855</c:v>
+                  <c:v>-675</c:v>
                 </c:pt>
                 <c:pt idx="429">
-                  <c:v>-855</c:v>
+                  <c:v>-675</c:v>
                 </c:pt>
                 <c:pt idx="430">
-                  <c:v>-855</c:v>
+                  <c:v>-675</c:v>
                 </c:pt>
                 <c:pt idx="431">
-                  <c:v>-854</c:v>
+                  <c:v>-674</c:v>
                 </c:pt>
                 <c:pt idx="432">
-                  <c:v>-854</c:v>
+                  <c:v>-674</c:v>
                 </c:pt>
                 <c:pt idx="433">
-                  <c:v>-854</c:v>
+                  <c:v>-674</c:v>
                 </c:pt>
                 <c:pt idx="434">
-                  <c:v>-854</c:v>
+                  <c:v>-674</c:v>
                 </c:pt>
                 <c:pt idx="435">
-                  <c:v>-854</c:v>
+                  <c:v>-674</c:v>
                 </c:pt>
                 <c:pt idx="436">
-                  <c:v>-854</c:v>
+                  <c:v>-674</c:v>
                 </c:pt>
                 <c:pt idx="437">
-                  <c:v>-853</c:v>
+                  <c:v>-673</c:v>
                 </c:pt>
                 <c:pt idx="438">
-                  <c:v>-853</c:v>
+                  <c:v>-673</c:v>
                 </c:pt>
                 <c:pt idx="439">
-                  <c:v>-853</c:v>
+                  <c:v>-673</c:v>
                 </c:pt>
                 <c:pt idx="440">
-                  <c:v>-853</c:v>
+                  <c:v>-673</c:v>
                 </c:pt>
                 <c:pt idx="441">
-                  <c:v>-853</c:v>
+                  <c:v>-673</c:v>
                 </c:pt>
                 <c:pt idx="442">
-                  <c:v>-853</c:v>
+                  <c:v>-673</c:v>
                 </c:pt>
                 <c:pt idx="443">
-                  <c:v>-853</c:v>
+                  <c:v>-673</c:v>
                 </c:pt>
                 <c:pt idx="444">
-                  <c:v>-852</c:v>
+                  <c:v>-672</c:v>
                 </c:pt>
                 <c:pt idx="445">
-                  <c:v>-852</c:v>
+                  <c:v>-672</c:v>
                 </c:pt>
                 <c:pt idx="446">
-                  <c:v>-852</c:v>
+                  <c:v>-672</c:v>
                 </c:pt>
                 <c:pt idx="447">
-                  <c:v>-852</c:v>
+                  <c:v>-672</c:v>
                 </c:pt>
                 <c:pt idx="448">
-                  <c:v>-852</c:v>
+                  <c:v>-672</c:v>
                 </c:pt>
                 <c:pt idx="449">
-                  <c:v>-852</c:v>
+                  <c:v>-672</c:v>
                 </c:pt>
                 <c:pt idx="450">
-                  <c:v>-852</c:v>
+                  <c:v>-672</c:v>
                 </c:pt>
                 <c:pt idx="451">
-                  <c:v>-852</c:v>
+                  <c:v>-672</c:v>
                 </c:pt>
                 <c:pt idx="452">
-                  <c:v>-851</c:v>
+                  <c:v>-671</c:v>
                 </c:pt>
                 <c:pt idx="453">
-                  <c:v>-851</c:v>
+                  <c:v>-671</c:v>
                 </c:pt>
                 <c:pt idx="454">
-                  <c:v>-851</c:v>
+                  <c:v>-671</c:v>
                 </c:pt>
                 <c:pt idx="455">
-                  <c:v>-851</c:v>
+                  <c:v>-671</c:v>
                 </c:pt>
                 <c:pt idx="456">
-                  <c:v>-850</c:v>
+                  <c:v>-670</c:v>
                 </c:pt>
                 <c:pt idx="457">
-                  <c:v>-850</c:v>
+                  <c:v>-670</c:v>
                 </c:pt>
                 <c:pt idx="458">
-                  <c:v>-850</c:v>
+                  <c:v>-670</c:v>
                 </c:pt>
                 <c:pt idx="459">
-                  <c:v>-849</c:v>
+                  <c:v>-669</c:v>
                 </c:pt>
                 <c:pt idx="460">
-                  <c:v>-849</c:v>
+                  <c:v>-669</c:v>
                 </c:pt>
                 <c:pt idx="461">
-                  <c:v>-849</c:v>
+                  <c:v>-669</c:v>
                 </c:pt>
                 <c:pt idx="462">
-                  <c:v>-849</c:v>
+                  <c:v>-669</c:v>
                 </c:pt>
                 <c:pt idx="463">
-                  <c:v>-848</c:v>
+                  <c:v>-668</c:v>
                 </c:pt>
                 <c:pt idx="464">
-                  <c:v>-848</c:v>
+                  <c:v>-668</c:v>
                 </c:pt>
                 <c:pt idx="465">
-                  <c:v>-848</c:v>
+                  <c:v>-668</c:v>
                 </c:pt>
                 <c:pt idx="466">
-                  <c:v>-848</c:v>
+                  <c:v>-668</c:v>
                 </c:pt>
                 <c:pt idx="467">
-                  <c:v>-848</c:v>
+                  <c:v>-668</c:v>
                 </c:pt>
                 <c:pt idx="468">
-                  <c:v>-848</c:v>
+                  <c:v>-668</c:v>
                 </c:pt>
                 <c:pt idx="469">
-                  <c:v>-848</c:v>
+                  <c:v>-668</c:v>
                 </c:pt>
                 <c:pt idx="470">
-                  <c:v>-848</c:v>
+                  <c:v>-668</c:v>
                 </c:pt>
                 <c:pt idx="471">
-                  <c:v>-848</c:v>
+                  <c:v>-668</c:v>
                 </c:pt>
                 <c:pt idx="472">
-                  <c:v>-848</c:v>
+                  <c:v>-668</c:v>
                 </c:pt>
                 <c:pt idx="473">
-                  <c:v>-848</c:v>
+                  <c:v>-668</c:v>
                 </c:pt>
                 <c:pt idx="474">
-                  <c:v>-848</c:v>
+                  <c:v>-668</c:v>
                 </c:pt>
                 <c:pt idx="475">
-                  <c:v>-848</c:v>
+                  <c:v>-668</c:v>
                 </c:pt>
                 <c:pt idx="476">
-                  <c:v>-848</c:v>
+                  <c:v>-668</c:v>
                 </c:pt>
                 <c:pt idx="477">
-                  <c:v>-847</c:v>
+                  <c:v>-667</c:v>
                 </c:pt>
                 <c:pt idx="478">
-                  <c:v>-847</c:v>
+                  <c:v>-667</c:v>
                 </c:pt>
                 <c:pt idx="479">
-                  <c:v>-846</c:v>
+                  <c:v>-666</c:v>
                 </c:pt>
                 <c:pt idx="480">
-                  <c:v>-846</c:v>
+                  <c:v>-666</c:v>
                 </c:pt>
                 <c:pt idx="481">
-                  <c:v>-846</c:v>
+                  <c:v>-666</c:v>
                 </c:pt>
                 <c:pt idx="482">
-                  <c:v>-846</c:v>
+                  <c:v>-666</c:v>
                 </c:pt>
                 <c:pt idx="483">
-                  <c:v>-845</c:v>
+                  <c:v>-665</c:v>
                 </c:pt>
                 <c:pt idx="484">
-                  <c:v>-845</c:v>
+                  <c:v>-665</c:v>
                 </c:pt>
                 <c:pt idx="485">
-                  <c:v>-844</c:v>
+                  <c:v>-664</c:v>
                 </c:pt>
                 <c:pt idx="486">
-                  <c:v>-844</c:v>
+                  <c:v>-664</c:v>
                 </c:pt>
                 <c:pt idx="487">
-                  <c:v>-843</c:v>
+                  <c:v>-663</c:v>
                 </c:pt>
                 <c:pt idx="488">
-                  <c:v>-843</c:v>
+                  <c:v>-663</c:v>
                 </c:pt>
                 <c:pt idx="489">
-                  <c:v>-842</c:v>
+                  <c:v>-662</c:v>
                 </c:pt>
                 <c:pt idx="490">
-                  <c:v>-842</c:v>
+                  <c:v>-662</c:v>
                 </c:pt>
                 <c:pt idx="491">
-                  <c:v>-841</c:v>
+                  <c:v>-661</c:v>
                 </c:pt>
                 <c:pt idx="492">
-                  <c:v>-841</c:v>
+                  <c:v>-661</c:v>
                 </c:pt>
                 <c:pt idx="493">
-                  <c:v>-841</c:v>
+                  <c:v>-661</c:v>
                 </c:pt>
                 <c:pt idx="494">
-                  <c:v>-840</c:v>
+                  <c:v>-660</c:v>
                 </c:pt>
                 <c:pt idx="495">
-                  <c:v>-840</c:v>
+                  <c:v>-660</c:v>
                 </c:pt>
                 <c:pt idx="496">
-                  <c:v>-839</c:v>
+                  <c:v>-659</c:v>
                 </c:pt>
                 <c:pt idx="497">
-                  <c:v>-839</c:v>
+                  <c:v>-659</c:v>
                 </c:pt>
                 <c:pt idx="498">
-                  <c:v>-838</c:v>
+                  <c:v>-658</c:v>
                 </c:pt>
                 <c:pt idx="499">
-                  <c:v>-838</c:v>
+                  <c:v>-658</c:v>
                 </c:pt>
                 <c:pt idx="500">
-                  <c:v>-838</c:v>
+                  <c:v>-658</c:v>
                 </c:pt>
                 <c:pt idx="501">
-                  <c:v>-838</c:v>
+                  <c:v>-658</c:v>
                 </c:pt>
                 <c:pt idx="502">
-                  <c:v>-839</c:v>
+                  <c:v>-659</c:v>
                 </c:pt>
                 <c:pt idx="503">
-                  <c:v>-839</c:v>
+                  <c:v>-659</c:v>
                 </c:pt>
                 <c:pt idx="504">
-                  <c:v>-839</c:v>
+                  <c:v>-659</c:v>
                 </c:pt>
                 <c:pt idx="505">
-                  <c:v>-840</c:v>
+                  <c:v>-660</c:v>
                 </c:pt>
                 <c:pt idx="506">
-                  <c:v>-841</c:v>
+                  <c:v>-661</c:v>
                 </c:pt>
                 <c:pt idx="507">
-                  <c:v>-841</c:v>
+                  <c:v>-661</c:v>
                 </c:pt>
                 <c:pt idx="508">
-                  <c:v>-842</c:v>
+                  <c:v>-662</c:v>
                 </c:pt>
                 <c:pt idx="509">
-                  <c:v>-842</c:v>
+                  <c:v>-662</c:v>
                 </c:pt>
                 <c:pt idx="510">
-                  <c:v>-843</c:v>
+                  <c:v>-663</c:v>
                 </c:pt>
                 <c:pt idx="511">
-                  <c:v>-844</c:v>
+                  <c:v>-664</c:v>
                 </c:pt>
                 <c:pt idx="512">
-                  <c:v>-844</c:v>
+                  <c:v>-664</c:v>
                 </c:pt>
                 <c:pt idx="513">
-                  <c:v>-845</c:v>
+                  <c:v>-665</c:v>
                 </c:pt>
                 <c:pt idx="514">
-                  <c:v>-845</c:v>
+                  <c:v>-665</c:v>
                 </c:pt>
                 <c:pt idx="515">
-                  <c:v>-845</c:v>
+                  <c:v>-665</c:v>
                 </c:pt>
                 <c:pt idx="516">
-                  <c:v>-845</c:v>
+                  <c:v>-665</c:v>
                 </c:pt>
                 <c:pt idx="517">
-                  <c:v>-845</c:v>
+                  <c:v>-665</c:v>
                 </c:pt>
                 <c:pt idx="518">
-                  <c:v>-845</c:v>
+                  <c:v>-665</c:v>
                 </c:pt>
                 <c:pt idx="519">
-                  <c:v>-845</c:v>
+                  <c:v>-665</c:v>
                 </c:pt>
                 <c:pt idx="520">
-                  <c:v>-846</c:v>
+                  <c:v>-666</c:v>
                 </c:pt>
                 <c:pt idx="521">
-                  <c:v>-846</c:v>
+                  <c:v>-666</c:v>
                 </c:pt>
                 <c:pt idx="522">
-                  <c:v>-846</c:v>
+                  <c:v>-666</c:v>
                 </c:pt>
                 <c:pt idx="523">
-                  <c:v>-846</c:v>
+                  <c:v>-666</c:v>
                 </c:pt>
                 <c:pt idx="524">
-                  <c:v>-846</c:v>
+                  <c:v>-666</c:v>
                 </c:pt>
                 <c:pt idx="525">
-                  <c:v>-846</c:v>
+                  <c:v>-666</c:v>
                 </c:pt>
                 <c:pt idx="526">
-                  <c:v>-846</c:v>
+                  <c:v>-666</c:v>
                 </c:pt>
                 <c:pt idx="527">
-                  <c:v>-847</c:v>
+                  <c:v>-667</c:v>
                 </c:pt>
                 <c:pt idx="528">
-                  <c:v>-847</c:v>
+                  <c:v>-667</c:v>
                 </c:pt>
                 <c:pt idx="529">
-                  <c:v>-847</c:v>
+                  <c:v>-667</c:v>
                 </c:pt>
                 <c:pt idx="530">
-                  <c:v>-847</c:v>
+                  <c:v>-667</c:v>
                 </c:pt>
                 <c:pt idx="531">
-                  <c:v>-847</c:v>
+                  <c:v>-667</c:v>
                 </c:pt>
                 <c:pt idx="532">
-                  <c:v>-847</c:v>
+                  <c:v>-667</c:v>
                 </c:pt>
                 <c:pt idx="533">
-                  <c:v>-848</c:v>
+                  <c:v>-668</c:v>
                 </c:pt>
                 <c:pt idx="534">
-                  <c:v>-847</c:v>
+                  <c:v>-667</c:v>
                 </c:pt>
                 <c:pt idx="535">
-                  <c:v>-847</c:v>
+                  <c:v>-667</c:v>
                 </c:pt>
                 <c:pt idx="536">
-                  <c:v>-847</c:v>
+                  <c:v>-667</c:v>
                 </c:pt>
                 <c:pt idx="537">
-                  <c:v>-847</c:v>
+                  <c:v>-667</c:v>
                 </c:pt>
                 <c:pt idx="538">
-                  <c:v>-847</c:v>
+                  <c:v>-667</c:v>
                 </c:pt>
                 <c:pt idx="539">
-                  <c:v>-846</c:v>
+                  <c:v>-666</c:v>
                 </c:pt>
                 <c:pt idx="540">
-                  <c:v>-846</c:v>
+                  <c:v>-666</c:v>
                 </c:pt>
                 <c:pt idx="541">
-                  <c:v>-846</c:v>
+                  <c:v>-666</c:v>
                 </c:pt>
                 <c:pt idx="542">
-                  <c:v>-846</c:v>
+                  <c:v>-666</c:v>
                 </c:pt>
                 <c:pt idx="543">
-                  <c:v>-845</c:v>
+                  <c:v>-665</c:v>
                 </c:pt>
                 <c:pt idx="544">
-                  <c:v>-845</c:v>
+                  <c:v>-665</c:v>
                 </c:pt>
                 <c:pt idx="545">
-                  <c:v>-845</c:v>
+                  <c:v>-665</c:v>
                 </c:pt>
                 <c:pt idx="546">
-                  <c:v>-845</c:v>
+                  <c:v>-665</c:v>
                 </c:pt>
                 <c:pt idx="547">
-                  <c:v>-845</c:v>
+                  <c:v>-665</c:v>
                 </c:pt>
                 <c:pt idx="548">
-                  <c:v>-844</c:v>
+                  <c:v>-664</c:v>
                 </c:pt>
                 <c:pt idx="549">
-                  <c:v>-842</c:v>
+                  <c:v>-662</c:v>
                 </c:pt>
                 <c:pt idx="550">
-                  <c:v>-839</c:v>
+                  <c:v>-659</c:v>
                 </c:pt>
                 <c:pt idx="551">
-                  <c:v>-832</c:v>
+                  <c:v>-652</c:v>
                 </c:pt>
                 <c:pt idx="552">
-                  <c:v>-828</c:v>
+                  <c:v>-648</c:v>
                 </c:pt>
                 <c:pt idx="553">
-                  <c:v>-824</c:v>
+                  <c:v>-644</c:v>
                 </c:pt>
                 <c:pt idx="554">
-                  <c:v>-821</c:v>
+                  <c:v>-641</c:v>
                 </c:pt>
                 <c:pt idx="555">
-                  <c:v>-817</c:v>
+                  <c:v>-637</c:v>
                 </c:pt>
                 <c:pt idx="556">
-                  <c:v>-813</c:v>
+                  <c:v>-633</c:v>
                 </c:pt>
                 <c:pt idx="557">
-                  <c:v>-808</c:v>
+                  <c:v>-628</c:v>
                 </c:pt>
                 <c:pt idx="558">
-                  <c:v>-803</c:v>
+                  <c:v>-623</c:v>
                 </c:pt>
                 <c:pt idx="559">
-                  <c:v>-791</c:v>
+                  <c:v>-611</c:v>
                 </c:pt>
                 <c:pt idx="560">
-                  <c:v>-783</c:v>
+                  <c:v>-603</c:v>
                 </c:pt>
                 <c:pt idx="561">
-                  <c:v>-773</c:v>
+                  <c:v>-593</c:v>
                 </c:pt>
                 <c:pt idx="562">
-                  <c:v>-764</c:v>
+                  <c:v>-584</c:v>
                 </c:pt>
                 <c:pt idx="563">
-                  <c:v>-757</c:v>
+                  <c:v>-577</c:v>
                 </c:pt>
                 <c:pt idx="564">
-                  <c:v>-749</c:v>
+                  <c:v>-569</c:v>
                 </c:pt>
                 <c:pt idx="565">
-                  <c:v>-742</c:v>
+                  <c:v>-562</c:v>
                 </c:pt>
                 <c:pt idx="566">
-                  <c:v>-736</c:v>
+                  <c:v>-556</c:v>
                 </c:pt>
                 <c:pt idx="567">
-                  <c:v>-724</c:v>
+                  <c:v>-544</c:v>
                 </c:pt>
                 <c:pt idx="568">
-                  <c:v>-718</c:v>
+                  <c:v>-538</c:v>
                 </c:pt>
                 <c:pt idx="569">
-                  <c:v>-711</c:v>
+                  <c:v>-531</c:v>
                 </c:pt>
                 <c:pt idx="570">
-                  <c:v>-704</c:v>
+                  <c:v>-524</c:v>
                 </c:pt>
                 <c:pt idx="571">
-                  <c:v>-696</c:v>
+                  <c:v>-516</c:v>
                 </c:pt>
                 <c:pt idx="572">
-                  <c:v>-689</c:v>
+                  <c:v>-509</c:v>
                 </c:pt>
                 <c:pt idx="573">
-                  <c:v>-682</c:v>
+                  <c:v>-502</c:v>
                 </c:pt>
                 <c:pt idx="574">
-                  <c:v>-674</c:v>
+                  <c:v>-494</c:v>
                 </c:pt>
                 <c:pt idx="575">
-                  <c:v>-669</c:v>
+                  <c:v>-489</c:v>
                 </c:pt>
                 <c:pt idx="576">
-                  <c:v>-658</c:v>
+                  <c:v>-478</c:v>
                 </c:pt>
                 <c:pt idx="577">
-                  <c:v>-652</c:v>
+                  <c:v>-472</c:v>
                 </c:pt>
                 <c:pt idx="578">
-                  <c:v>-644</c:v>
+                  <c:v>-464</c:v>
                 </c:pt>
                 <c:pt idx="579">
-                  <c:v>-635</c:v>
+                  <c:v>-455</c:v>
                 </c:pt>
                 <c:pt idx="580">
-                  <c:v>-622</c:v>
+                  <c:v>-442</c:v>
                 </c:pt>
                 <c:pt idx="581">
-                  <c:v>-611</c:v>
+                  <c:v>-431</c:v>
                 </c:pt>
                 <c:pt idx="582">
-                  <c:v>-601</c:v>
+                  <c:v>-421</c:v>
                 </c:pt>
                 <c:pt idx="583">
-                  <c:v>-592</c:v>
+                  <c:v>-412</c:v>
                 </c:pt>
                 <c:pt idx="584">
-                  <c:v>-575</c:v>
+                  <c:v>-395</c:v>
                 </c:pt>
                 <c:pt idx="585">
-                  <c:v>-566</c:v>
+                  <c:v>-386</c:v>
                 </c:pt>
                 <c:pt idx="586">
-                  <c:v>-557</c:v>
+                  <c:v>-377</c:v>
                 </c:pt>
                 <c:pt idx="587">
-                  <c:v>-549</c:v>
+                  <c:v>-369</c:v>
                 </c:pt>
                 <c:pt idx="588">
-                  <c:v>-539</c:v>
+                  <c:v>-359</c:v>
                 </c:pt>
                 <c:pt idx="589">
-                  <c:v>-530</c:v>
+                  <c:v>-350</c:v>
                 </c:pt>
                 <c:pt idx="590">
-                  <c:v>-518</c:v>
+                  <c:v>-338</c:v>
                 </c:pt>
                 <c:pt idx="591">
-                  <c:v>-507</c:v>
+                  <c:v>-327</c:v>
                 </c:pt>
                 <c:pt idx="592">
-                  <c:v>-486</c:v>
+                  <c:v>-306</c:v>
                 </c:pt>
                 <c:pt idx="593">
-                  <c:v>-475</c:v>
+                  <c:v>-295</c:v>
                 </c:pt>
                 <c:pt idx="594">
-                  <c:v>-463</c:v>
+                  <c:v>-283</c:v>
                 </c:pt>
                 <c:pt idx="595">
-                  <c:v>-455</c:v>
+                  <c:v>-275</c:v>
                 </c:pt>
                 <c:pt idx="596">
-                  <c:v>-447</c:v>
+                  <c:v>-267</c:v>
                 </c:pt>
                 <c:pt idx="597">
-                  <c:v>-436</c:v>
+                  <c:v>-256</c:v>
                 </c:pt>
                 <c:pt idx="598">
-                  <c:v>-422</c:v>
+                  <c:v>-242</c:v>
                 </c:pt>
                 <c:pt idx="599">
-                  <c:v>-406</c:v>
+                  <c:v>-226</c:v>
                 </c:pt>
                 <c:pt idx="600">
-                  <c:v>-372</c:v>
+                  <c:v>-192</c:v>
                 </c:pt>
                 <c:pt idx="601">
-                  <c:v>-355</c:v>
+                  <c:v>-175</c:v>
                 </c:pt>
                 <c:pt idx="602">
-                  <c:v>-337</c:v>
+                  <c:v>-157</c:v>
                 </c:pt>
                 <c:pt idx="603">
-                  <c:v>-317</c:v>
+                  <c:v>-137</c:v>
                 </c:pt>
                 <c:pt idx="604">
-                  <c:v>-301</c:v>
+                  <c:v>-121</c:v>
                 </c:pt>
                 <c:pt idx="605">
-                  <c:v>-287</c:v>
+                  <c:v>-107</c:v>
                 </c:pt>
                 <c:pt idx="606">
-                  <c:v>-271</c:v>
+                  <c:v>-91</c:v>
                 </c:pt>
                 <c:pt idx="607">
-                  <c:v>-254</c:v>
+                  <c:v>-74</c:v>
                 </c:pt>
                 <c:pt idx="608">
-                  <c:v>-236</c:v>
+                  <c:v>-56</c:v>
                 </c:pt>
                 <c:pt idx="609">
-                  <c:v>-209</c:v>
+                  <c:v>-29</c:v>
                 </c:pt>
                 <c:pt idx="610">
-                  <c:v>-199</c:v>
+                  <c:v>-19</c:v>
                 </c:pt>
                 <c:pt idx="611">
-                  <c:v>-190</c:v>
+                  <c:v>-10</c:v>
                 </c:pt>
                 <c:pt idx="612">
-                  <c:v>-181</c:v>
+                  <c:v>-1</c:v>
                 </c:pt>
                 <c:pt idx="613">
-                  <c:v>-177</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="614">
-                  <c:v>-173</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="615">
-                  <c:v>-171</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="616">
-                  <c:v>-168</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="617">
-                  <c:v>-167</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="618">
-                  <c:v>-171</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="619">
-                  <c:v>-175</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="620">
-                  <c:v>-177</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="621">
-                  <c:v>-179</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="622">
-                  <c:v>-182</c:v>
+                  <c:v>-2</c:v>
                 </c:pt>
                 <c:pt idx="623">
-                  <c:v>-191</c:v>
+                  <c:v>-11</c:v>
                 </c:pt>
                 <c:pt idx="624">
-                  <c:v>-198</c:v>
+                  <c:v>-18</c:v>
                 </c:pt>
                 <c:pt idx="625">
-                  <c:v>-203</c:v>
+                  <c:v>-23</c:v>
                 </c:pt>
                 <c:pt idx="626">
-                  <c:v>-204</c:v>
+                  <c:v>-24</c:v>
                 </c:pt>
                 <c:pt idx="627">
-                  <c:v>-205</c:v>
+                  <c:v>-25</c:v>
                 </c:pt>
                 <c:pt idx="628">
-                  <c:v>-206</c:v>
+                  <c:v>-26</c:v>
                 </c:pt>
                 <c:pt idx="629">
-                  <c:v>-207</c:v>
+                  <c:v>-27</c:v>
                 </c:pt>
                 <c:pt idx="630">
-                  <c:v>-208</c:v>
+                  <c:v>-28</c:v>
                 </c:pt>
                 <c:pt idx="631">
-                  <c:v>-208</c:v>
+                  <c:v>-28</c:v>
                 </c:pt>
                 <c:pt idx="632">
-                  <c:v>-209</c:v>
+                  <c:v>-29</c:v>
                 </c:pt>
                 <c:pt idx="633">
-                  <c:v>-210</c:v>
+                  <c:v>-30</c:v>
                 </c:pt>
                 <c:pt idx="634">
-                  <c:v>-211</c:v>
+                  <c:v>-31</c:v>
                 </c:pt>
                 <c:pt idx="635">
-                  <c:v>-211</c:v>
+                  <c:v>-31</c:v>
                 </c:pt>
                 <c:pt idx="636">
-                  <c:v>-212</c:v>
+                  <c:v>-32</c:v>
                 </c:pt>
                 <c:pt idx="637">
-                  <c:v>-212</c:v>
+                  <c:v>-32</c:v>
                 </c:pt>
                 <c:pt idx="638">
-                  <c:v>-213</c:v>
+                  <c:v>-33</c:v>
                 </c:pt>
                 <c:pt idx="639">
-                  <c:v>-214</c:v>
+                  <c:v>-34</c:v>
                 </c:pt>
                 <c:pt idx="640">
-                  <c:v>-214</c:v>
+                  <c:v>-34</c:v>
                 </c:pt>
                 <c:pt idx="641">
-                  <c:v>-215</c:v>
+                  <c:v>-35</c:v>
                 </c:pt>
                 <c:pt idx="642">
-                  <c:v>-216</c:v>
+                  <c:v>-36</c:v>
                 </c:pt>
                 <c:pt idx="643">
-                  <c:v>-217</c:v>
+                  <c:v>-37</c:v>
                 </c:pt>
                 <c:pt idx="644">
-                  <c:v>-217</c:v>
+                  <c:v>-37</c:v>
                 </c:pt>
                 <c:pt idx="645">
-                  <c:v>-218</c:v>
+                  <c:v>-38</c:v>
                 </c:pt>
                 <c:pt idx="646">
-                  <c:v>-219</c:v>
+                  <c:v>-39</c:v>
                 </c:pt>
                 <c:pt idx="647">
-                  <c:v>-219</c:v>
+                  <c:v>-39</c:v>
                 </c:pt>
                 <c:pt idx="648">
-                  <c:v>-220</c:v>
+                  <c:v>-40</c:v>
                 </c:pt>
                 <c:pt idx="649">
-                  <c:v>-220</c:v>
+                  <c:v>-40</c:v>
                 </c:pt>
                 <c:pt idx="650">
-                  <c:v>-221</c:v>
+                  <c:v>-41</c:v>
                 </c:pt>
                 <c:pt idx="651">
-                  <c:v>-222</c:v>
+                  <c:v>-42</c:v>
                 </c:pt>
                 <c:pt idx="652">
-                  <c:v>-222</c:v>
+                  <c:v>-42</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4714,11 +4714,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="91886960"/>
-        <c:axId val="70343826"/>
+        <c:axId val="88463767"/>
+        <c:axId val="43202790"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="91886960"/>
+        <c:axId val="88463767"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4784,7 +4784,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70343826"/>
+        <c:crossAx val="43202790"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4792,7 +4792,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="70343826"/>
+        <c:axId val="43202790"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4868,7 +4868,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="91886960"/>
+        <c:crossAx val="88463767"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9398,11 +9398,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="52609460"/>
-        <c:axId val="67230674"/>
+        <c:axId val="99363500"/>
+        <c:axId val="24053402"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="52609460"/>
+        <c:axId val="99363500"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9468,7 +9468,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67230674"/>
+        <c:crossAx val="24053402"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -9476,7 +9476,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="67230674"/>
+        <c:axId val="24053402"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9552,7 +9552,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="52609460"/>
+        <c:crossAx val="99363500"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14082,11 +14082,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="37471180"/>
-        <c:axId val="23199298"/>
+        <c:axId val="5673720"/>
+        <c:axId val="38453701"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="37471180"/>
+        <c:axId val="5673720"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14152,7 +14152,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="23199298"/>
+        <c:crossAx val="38453701"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -14160,7 +14160,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="23199298"/>
+        <c:axId val="38453701"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14236,7 +14236,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37471180"/>
+        <c:crossAx val="5673720"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14302,9 +14302,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>304200</xdr:colOff>
+      <xdr:colOff>303480</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>75600</xdr:rowOff>
+      <xdr:rowOff>74880</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -14313,7 +14313,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="6745680" y="190440"/>
-        <a:ext cx="4518000" cy="2742840"/>
+        <a:ext cx="4517280" cy="2742120"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -14332,9 +14332,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>304200</xdr:colOff>
+      <xdr:colOff>303480</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>75600</xdr:rowOff>
+      <xdr:rowOff>74880</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -14343,7 +14343,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="6745680" y="3238560"/>
-        <a:ext cx="4518000" cy="2742480"/>
+        <a:ext cx="4517280" cy="2741760"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -14362,9 +14362,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>304200</xdr:colOff>
+      <xdr:colOff>303480</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>75600</xdr:rowOff>
+      <xdr:rowOff>74880</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -14373,7 +14373,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="6745680" y="6286680"/>
-        <a:ext cx="4518000" cy="2742480"/>
+        <a:ext cx="4517280" cy="2741760"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -14566,7 +14566,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H794"/>
+  <dimension ref="A1:J654"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.52"/>
@@ -23292,7 +23292,7 @@
         <v>1775776880.39676</v>
       </c>
       <c r="B336" s="1" t="n">
-        <v>-796</v>
+        <v>-616</v>
       </c>
       <c r="C336" s="1" t="n">
         <v>2795</v>
@@ -23312,13 +23312,14 @@
       <c r="H336" s="1" t="n">
         <v>510.5108</v>
       </c>
+      <c r="J336" s="1"/>
     </row>
     <row r="337" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="1" t="n">
         <v>1775776880.39922</v>
       </c>
       <c r="B337" s="1" t="n">
-        <v>-807</v>
+        <v>-627</v>
       </c>
       <c r="C337" s="1" t="n">
         <v>2787</v>
@@ -23338,13 +23339,14 @@
       <c r="H337" s="1" t="n">
         <v>506.7794</v>
       </c>
+      <c r="J337" s="1"/>
     </row>
     <row r="338" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A338" s="1" t="n">
         <v>1775776880.47643</v>
       </c>
       <c r="B338" s="1" t="n">
-        <v>-818</v>
+        <v>-638</v>
       </c>
       <c r="C338" s="1" t="n">
         <v>2779</v>
@@ -23364,13 +23366,14 @@
       <c r="H338" s="1" t="n">
         <v>503.8772</v>
       </c>
+      <c r="J338" s="1"/>
     </row>
     <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A339" s="1" t="n">
         <v>1775776880.6538</v>
       </c>
       <c r="B339" s="1" t="n">
-        <v>-838</v>
+        <v>-658</v>
       </c>
       <c r="C339" s="1" t="n">
         <v>2761</v>
@@ -23390,13 +23393,14 @@
       <c r="H339" s="1" t="n">
         <v>507.8816</v>
       </c>
+      <c r="J339" s="1"/>
     </row>
     <row r="340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A340" s="1" t="n">
         <v>1775776880.694</v>
       </c>
       <c r="B340" s="1" t="n">
-        <v>-846</v>
+        <v>-666</v>
       </c>
       <c r="C340" s="1" t="n">
         <v>2752</v>
@@ -23416,13 +23420,14 @@
       <c r="H340" s="1" t="n">
         <v>511.3216</v>
       </c>
+      <c r="J340" s="1"/>
     </row>
     <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A341" s="1" t="n">
         <v>1775776880.90724</v>
       </c>
       <c r="B341" s="1" t="n">
-        <v>-847</v>
+        <v>-667</v>
       </c>
       <c r="C341" s="1" t="n">
         <v>2743</v>
@@ -23442,13 +23447,14 @@
       <c r="H341" s="1" t="n">
         <v>517.9736</v>
       </c>
+      <c r="J341" s="1"/>
     </row>
     <row r="342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A342" s="1" t="n">
         <v>1775776880.91057</v>
       </c>
       <c r="B342" s="1" t="n">
-        <v>-847</v>
+        <v>-667</v>
       </c>
       <c r="C342" s="1" t="n">
         <v>2734</v>
@@ -23468,13 +23474,14 @@
       <c r="H342" s="1" t="n">
         <v>517.5136</v>
       </c>
+      <c r="J342" s="1"/>
     </row>
     <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="1" t="n">
         <v>1775776881.16361</v>
       </c>
       <c r="B343" s="1" t="n">
-        <v>-847</v>
+        <v>-667</v>
       </c>
       <c r="C343" s="1" t="n">
         <v>2728</v>
@@ -23494,13 +23501,14 @@
       <c r="H343" s="1" t="n">
         <v>512.6976</v>
       </c>
+      <c r="J343" s="1"/>
     </row>
     <row r="344" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="1" t="n">
         <v>1775776881.16584</v>
       </c>
       <c r="B344" s="1" t="n">
-        <v>-847</v>
+        <v>-667</v>
       </c>
       <c r="C344" s="1" t="n">
         <v>2727</v>
@@ -23520,13 +23528,14 @@
       <c r="H344" s="1" t="n">
         <v>507.7468</v>
       </c>
+      <c r="J344" s="1"/>
     </row>
     <row r="345" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="1" t="n">
         <v>1775776881.23435</v>
       </c>
       <c r="B345" s="1" t="n">
-        <v>-846</v>
+        <v>-666</v>
       </c>
       <c r="C345" s="1" t="n">
         <v>2726</v>
@@ -23546,13 +23555,14 @@
       <c r="H345" s="1" t="n">
         <v>500.415</v>
       </c>
+      <c r="J345" s="1"/>
     </row>
     <row r="346" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A346" s="1" t="n">
         <v>1775776881.41899</v>
       </c>
       <c r="B346" s="1" t="n">
-        <v>-846</v>
+        <v>-666</v>
       </c>
       <c r="C346" s="1" t="n">
         <v>2725</v>
@@ -23572,13 +23582,14 @@
       <c r="H346" s="1" t="n">
         <v>503.2032</v>
       </c>
+      <c r="J346" s="1"/>
     </row>
     <row r="347" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="1" t="n">
         <v>1775776881.45064</v>
       </c>
       <c r="B347" s="1" t="n">
-        <v>-846</v>
+        <v>-666</v>
       </c>
       <c r="C347" s="1" t="n">
         <v>2724</v>
@@ -23598,13 +23609,14 @@
       <c r="H347" s="1" t="n">
         <v>499.9008</v>
       </c>
+      <c r="J347" s="1"/>
     </row>
     <row r="348" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="1" t="n">
         <v>1775776881.67763</v>
       </c>
       <c r="B348" s="1" t="n">
-        <v>-847</v>
+        <v>-667</v>
       </c>
       <c r="C348" s="1" t="n">
         <v>2722</v>
@@ -23624,13 +23636,14 @@
       <c r="H348" s="1" t="n">
         <v>505.6738</v>
       </c>
+      <c r="J348" s="1"/>
     </row>
     <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A349" s="1" t="n">
         <v>1775776881.68043</v>
       </c>
       <c r="B349" s="1" t="n">
-        <v>-847</v>
+        <v>-667</v>
       </c>
       <c r="C349" s="1" t="n">
         <v>2720</v>
@@ -23650,13 +23663,14 @@
       <c r="H349" s="1" t="n">
         <v>481.8752</v>
       </c>
+      <c r="J349" s="1"/>
     </row>
     <row r="350" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="1" t="n">
         <v>1775776881.92449</v>
       </c>
       <c r="B350" s="1" t="n">
-        <v>-847</v>
+        <v>-667</v>
       </c>
       <c r="C350" s="1" t="n">
         <v>2720</v>
@@ -23676,13 +23690,14 @@
       <c r="H350" s="1" t="n">
         <v>507.056</v>
       </c>
+      <c r="J350" s="1"/>
     </row>
     <row r="351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="1" t="n">
         <v>1775776881.93175</v>
       </c>
       <c r="B351" s="1" t="n">
-        <v>-847</v>
+        <v>-667</v>
       </c>
       <c r="C351" s="1" t="n">
         <v>2719</v>
@@ -23702,13 +23717,14 @@
       <c r="H351" s="1" t="n">
         <v>513.5232</v>
       </c>
+      <c r="J351" s="1"/>
     </row>
     <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="1" t="n">
         <v>1775776881.99078</v>
       </c>
       <c r="B352" s="1" t="n">
-        <v>-847</v>
+        <v>-667</v>
       </c>
       <c r="C352" s="1" t="n">
         <v>2718</v>
@@ -23728,13 +23744,14 @@
       <c r="H352" s="1" t="n">
         <v>520.4612</v>
       </c>
+      <c r="J352" s="1"/>
     </row>
     <row r="353" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="1" t="n">
         <v>1775776882.18493</v>
       </c>
       <c r="B353" s="1" t="n">
-        <v>-848</v>
+        <v>-668</v>
       </c>
       <c r="C353" s="1" t="n">
         <v>2719</v>
@@ -23754,13 +23771,14 @@
       <c r="H353" s="1" t="n">
         <v>513.5512</v>
       </c>
+      <c r="J353" s="1"/>
     </row>
     <row r="354" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="1" t="n">
         <v>1775776882.20709</v>
       </c>
       <c r="B354" s="1" t="n">
-        <v>-848</v>
+        <v>-668</v>
       </c>
       <c r="C354" s="1" t="n">
         <v>2720</v>
@@ -23780,13 +23798,14 @@
       <c r="H354" s="1" t="n">
         <v>515.7248</v>
       </c>
+      <c r="J354" s="1"/>
     </row>
     <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="1" t="n">
         <v>1775776882.44012</v>
       </c>
       <c r="B355" s="1" t="n">
-        <v>-849</v>
+        <v>-669</v>
       </c>
       <c r="C355" s="1" t="n">
         <v>2720</v>
@@ -23806,13 +23825,14 @@
       <c r="H355" s="1" t="n">
         <v>510.3584</v>
       </c>
+      <c r="J355" s="1"/>
     </row>
     <row r="356" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="1" t="n">
         <v>1775776882.4426</v>
       </c>
       <c r="B356" s="1" t="n">
-        <v>-849</v>
+        <v>-669</v>
       </c>
       <c r="C356" s="1" t="n">
         <v>2722</v>
@@ -23832,13 +23852,14 @@
       <c r="H356" s="1" t="n">
         <v>507.7468</v>
       </c>
+      <c r="J356" s="1"/>
     </row>
     <row r="357" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="1" t="n">
         <v>1775776882.53249</v>
       </c>
       <c r="B357" s="1" t="n">
-        <v>-849</v>
+        <v>-669</v>
       </c>
       <c r="C357" s="1" t="n">
         <v>2724</v>
@@ -23858,13 +23879,14 @@
       <c r="H357" s="1" t="n">
         <v>510.496</v>
       </c>
+      <c r="J357" s="1"/>
     </row>
     <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="1" t="n">
         <v>1775776882.69649</v>
       </c>
       <c r="B358" s="1" t="n">
-        <v>-850</v>
+        <v>-670</v>
       </c>
       <c r="C358" s="1" t="n">
         <v>2728</v>
@@ -23884,13 +23906,14 @@
       <c r="H358" s="1" t="n">
         <v>507.3312</v>
       </c>
+      <c r="J358" s="1"/>
     </row>
     <row r="359" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="1" t="n">
         <v>1775776882.74923</v>
       </c>
       <c r="B359" s="1" t="n">
-        <v>-850</v>
+        <v>-670</v>
       </c>
       <c r="C359" s="1" t="n">
         <v>2730</v>
@@ -23910,13 +23933,14 @@
       <c r="H359" s="1" t="n">
         <v>511.0464</v>
       </c>
+      <c r="J359" s="1"/>
     </row>
     <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A360" s="1" t="n">
         <v>1775776882.94597</v>
       </c>
       <c r="B360" s="1" t="n">
-        <v>-850</v>
+        <v>-670</v>
       </c>
       <c r="C360" s="1" t="n">
         <v>2731</v>
@@ -23936,13 +23960,14 @@
       <c r="H360" s="1" t="n">
         <v>518.8896</v>
       </c>
+      <c r="J360" s="1"/>
     </row>
     <row r="361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A361" s="1" t="n">
         <v>1775776882.96473</v>
       </c>
       <c r="B361" s="1" t="n">
-        <v>-850</v>
+        <v>-670</v>
       </c>
       <c r="C361" s="1" t="n">
         <v>2732</v>
@@ -23962,13 +23987,14 @@
       <c r="H361" s="1" t="n">
         <v>513.6608</v>
       </c>
+      <c r="J361" s="1"/>
     </row>
     <row r="362" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="1" t="n">
         <v>1775776883.20334</v>
       </c>
       <c r="B362" s="1" t="n">
-        <v>-851</v>
+        <v>-671</v>
       </c>
       <c r="C362" s="1" t="n">
         <v>2733</v>
@@ -23988,13 +24014,14 @@
       <c r="H362" s="1" t="n">
         <v>513.248</v>
       </c>
+      <c r="J362" s="1"/>
     </row>
     <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="1" t="n">
         <v>1775776883.20566</v>
       </c>
       <c r="B363" s="1" t="n">
-        <v>-851</v>
+        <v>-671</v>
       </c>
       <c r="C363" s="1" t="n">
         <v>2735</v>
@@ -24014,13 +24041,14 @@
       <c r="H363" s="1" t="n">
         <v>511.4592</v>
       </c>
+      <c r="J363" s="1"/>
     </row>
     <row r="364" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A364" s="1" t="n">
         <v>1775776883.2883</v>
       </c>
       <c r="B364" s="1" t="n">
-        <v>-852</v>
+        <v>-672</v>
       </c>
       <c r="C364" s="1" t="n">
         <v>2736</v>
@@ -24040,13 +24068,14 @@
       <c r="H364" s="1" t="n">
         <v>511.4592</v>
       </c>
+      <c r="J364" s="1"/>
     </row>
     <row r="365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A365" s="1" t="n">
         <v>1775776883.45682</v>
       </c>
       <c r="B365" s="1" t="n">
-        <v>-852</v>
+        <v>-672</v>
       </c>
       <c r="C365" s="1" t="n">
         <v>2739</v>
@@ -24066,13 +24095,14 @@
       <c r="H365" s="1" t="n">
         <v>506.6432</v>
       </c>
+      <c r="J365" s="1"/>
     </row>
     <row r="366" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="1" t="n">
         <v>1775776883.50425</v>
       </c>
       <c r="B366" s="1" t="n">
-        <v>-853</v>
+        <v>-673</v>
       </c>
       <c r="C366" s="1" t="n">
         <v>2740</v>
@@ -24092,13 +24122,14 @@
       <c r="H366" s="1" t="n">
         <v>509.029</v>
       </c>
+      <c r="J366" s="1"/>
     </row>
     <row r="367" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="1" t="n">
         <v>1775776883.70492</v>
       </c>
       <c r="B367" s="1" t="n">
-        <v>-853</v>
+        <v>-673</v>
       </c>
       <c r="C367" s="1" t="n">
         <v>2741</v>
@@ -24118,13 +24149,14 @@
       <c r="H367" s="1" t="n">
         <v>505.5424</v>
       </c>
+      <c r="J367" s="1"/>
     </row>
     <row r="368" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A368" s="1" t="n">
         <v>1775776883.72152</v>
       </c>
       <c r="B368" s="1" t="n">
-        <v>-853</v>
+        <v>-673</v>
       </c>
       <c r="C368" s="1" t="n">
         <v>2745</v>
@@ -24144,13 +24176,14 @@
       <c r="H368" s="1" t="n">
         <v>510.3584</v>
       </c>
+      <c r="J368" s="1"/>
     </row>
     <row r="369" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A369" s="1" t="n">
         <v>1775776883.96615</v>
       </c>
       <c r="B369" s="1" t="n">
-        <v>-853</v>
+        <v>-673</v>
       </c>
       <c r="C369" s="1" t="n">
         <v>2747</v>
@@ -24170,13 +24203,14 @@
       <c r="H369" s="1" t="n">
         <v>516.868</v>
       </c>
+      <c r="J369" s="1"/>
     </row>
     <row r="370" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A370" s="1" t="n">
         <v>1775776883.9687</v>
       </c>
       <c r="B370" s="1" t="n">
-        <v>-853</v>
+        <v>-673</v>
       </c>
       <c r="C370" s="1" t="n">
         <v>2748</v>
@@ -24196,13 +24230,14 @@
       <c r="H370" s="1" t="n">
         <v>513.248</v>
       </c>
+      <c r="J370" s="1"/>
     </row>
     <row r="371" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A371" s="1" t="n">
         <v>1775776884.04693</v>
       </c>
       <c r="B371" s="1" t="n">
-        <v>-854</v>
+        <v>-674</v>
       </c>
       <c r="C371" s="1" t="n">
         <v>2749</v>
@@ -24222,13 +24257,14 @@
       <c r="H371" s="1" t="n">
         <v>509.1894</v>
       </c>
+      <c r="J371" s="1"/>
     </row>
     <row r="372" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="1" t="n">
         <v>1775776884.22656</v>
       </c>
       <c r="B372" s="1" t="n">
-        <v>-854</v>
+        <v>-674</v>
       </c>
       <c r="C372" s="1" t="n">
         <v>2750</v>
@@ -24248,13 +24284,14 @@
       <c r="H372" s="1" t="n">
         <v>508.5039</v>
       </c>
+      <c r="J372" s="1"/>
     </row>
     <row r="373" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="1" t="n">
         <v>1775776884.26321</v>
       </c>
       <c r="B373" s="1" t="n">
-        <v>-855</v>
+        <v>-675</v>
       </c>
       <c r="C373" s="1" t="n">
         <v>2752</v>
@@ -24274,13 +24311,14 @@
       <c r="H373" s="1" t="n">
         <v>507.6064</v>
       </c>
+      <c r="J373" s="1"/>
     </row>
     <row r="374" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A374" s="1" t="n">
         <v>1775776884.49068</v>
       </c>
       <c r="B374" s="1" t="n">
-        <v>-855</v>
+        <v>-675</v>
       </c>
       <c r="C374" s="1" t="n">
         <v>2753</v>
@@ -24300,13 +24338,14 @@
       <c r="H374" s="1" t="n">
         <v>508.0192</v>
       </c>
+      <c r="J374" s="1"/>
     </row>
     <row r="375" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A375" s="1" t="n">
         <v>1775776884.49372</v>
       </c>
       <c r="B375" s="1" t="n">
-        <v>-855</v>
+        <v>-675</v>
       </c>
       <c r="C375" s="1" t="n">
         <v>2755</v>
@@ -24326,13 +24365,14 @@
       <c r="H375" s="1" t="n">
         <v>507.3312</v>
       </c>
+      <c r="J375" s="1"/>
     </row>
     <row r="376" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="1" t="n">
         <v>1775776884.58771</v>
       </c>
       <c r="B376" s="1" t="n">
-        <v>-855</v>
+        <v>-675</v>
       </c>
       <c r="C376" s="1" t="n">
         <v>2756</v>
@@ -24352,13 +24392,14 @@
       <c r="H376" s="1" t="n">
         <v>514.3804</v>
       </c>
+      <c r="J376" s="1"/>
     </row>
     <row r="377" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A377" s="1" t="n">
         <v>1775776884.74621</v>
       </c>
       <c r="B377" s="1" t="n">
-        <v>-855</v>
+        <v>-675</v>
       </c>
       <c r="C377" s="1" t="n">
         <v>2757</v>
@@ -24378,13 +24419,14 @@
       <c r="H377" s="1" t="n">
         <v>509.12</v>
       </c>
+      <c r="J377" s="1"/>
     </row>
     <row r="378" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="1" t="n">
         <v>1775776884.80407</v>
       </c>
       <c r="B378" s="1" t="n">
-        <v>-855</v>
+        <v>-675</v>
       </c>
       <c r="C378" s="1" t="n">
         <v>2758</v>
@@ -24404,13 +24446,14 @@
       <c r="H378" s="1" t="n">
         <v>516.4128</v>
       </c>
+      <c r="J378" s="1"/>
     </row>
     <row r="379" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="1" t="n">
         <v>1775776885.01134</v>
       </c>
       <c r="B379" s="1" t="n">
-        <v>-855</v>
+        <v>-675</v>
       </c>
       <c r="C379" s="1" t="n">
         <v>2757</v>
@@ -24430,13 +24473,14 @@
       <c r="H379" s="1" t="n">
         <v>517.1008</v>
       </c>
+      <c r="J379" s="1"/>
     </row>
     <row r="380" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="1" t="n">
         <v>1775776885.0198</v>
       </c>
       <c r="B380" s="1" t="n">
-        <v>-856</v>
+        <v>-676</v>
       </c>
       <c r="C380" s="1" t="n">
         <v>2756</v>
@@ -24456,13 +24500,14 @@
       <c r="H380" s="1" t="n">
         <v>511.2018</v>
       </c>
+      <c r="J380" s="1"/>
     </row>
     <row r="381" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A381" s="1" t="n">
         <v>1775776885.26236</v>
       </c>
       <c r="B381" s="1" t="n">
-        <v>-856</v>
+        <v>-676</v>
       </c>
       <c r="C381" s="1" t="n">
         <v>2754</v>
@@ -24482,13 +24527,14 @@
       <c r="H381" s="1" t="n">
         <v>510.3584</v>
       </c>
+      <c r="J381" s="1"/>
     </row>
     <row r="382" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A382" s="1" t="n">
         <v>1775776885.26482</v>
       </c>
       <c r="B382" s="1" t="n">
-        <v>-856</v>
+        <v>-676</v>
       </c>
       <c r="C382" s="1" t="n">
         <v>2753</v>
@@ -24508,13 +24554,14 @@
       <c r="H382" s="1" t="n">
         <v>504.0288</v>
       </c>
+      <c r="J382" s="1"/>
     </row>
     <row r="383" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A383" s="1" t="n">
         <v>1775776885.34477</v>
       </c>
       <c r="B383" s="1" t="n">
-        <v>-857</v>
+        <v>-677</v>
       </c>
       <c r="C383" s="1" t="n">
         <v>2753</v>
@@ -24534,13 +24581,14 @@
       <c r="H383" s="1" t="n">
         <v>508.2297</v>
       </c>
+      <c r="J383" s="1"/>
     </row>
     <row r="384" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A384" s="1" t="n">
         <v>1775776885.51417</v>
       </c>
       <c r="B384" s="1" t="n">
-        <v>-857</v>
+        <v>-677</v>
       </c>
       <c r="C384" s="1" t="n">
         <v>2754</v>
@@ -24560,13 +24608,14 @@
       <c r="H384" s="1" t="n">
         <v>508.2944</v>
       </c>
+      <c r="J384" s="1"/>
     </row>
     <row r="385" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A385" s="1" t="n">
         <v>1775776885.5621</v>
       </c>
       <c r="B385" s="1" t="n">
-        <v>-858</v>
+        <v>-678</v>
       </c>
       <c r="C385" s="1" t="n">
         <v>2753</v>
@@ -24586,13 +24635,14 @@
       <c r="H385" s="1" t="n">
         <v>514.0736</v>
       </c>
+      <c r="J385" s="1"/>
     </row>
     <row r="386" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A386" s="1" t="n">
         <v>1775776885.77088</v>
       </c>
       <c r="B386" s="1" t="n">
-        <v>-858</v>
+        <v>-678</v>
       </c>
       <c r="C386" s="1" t="n">
         <v>2750</v>
@@ -24612,13 +24662,14 @@
       <c r="H386" s="1" t="n">
         <v>514.7616</v>
       </c>
+      <c r="J386" s="1"/>
     </row>
     <row r="387" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A387" s="1" t="n">
         <v>1775776885.77787</v>
       </c>
       <c r="B387" s="1" t="n">
-        <v>-858</v>
+        <v>-678</v>
       </c>
       <c r="C387" s="1" t="n">
         <v>2748</v>
@@ -24638,13 +24689,14 @@
       <c r="H387" s="1" t="n">
         <v>514.7616</v>
       </c>
+      <c r="J387" s="1"/>
     </row>
     <row r="388" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A388" s="1" t="n">
         <v>1775776886.02244</v>
       </c>
       <c r="B388" s="1" t="n">
-        <v>-858</v>
+        <v>-678</v>
       </c>
       <c r="C388" s="1" t="n">
         <v>2744</v>
@@ -24664,13 +24716,14 @@
       <c r="H388" s="1" t="n">
         <v>511.872</v>
       </c>
+      <c r="J388" s="1"/>
     </row>
     <row r="389" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A389" s="1" t="n">
         <v>1775776886.02503</v>
       </c>
       <c r="B389" s="1" t="n">
-        <v>-858</v>
+        <v>-678</v>
       </c>
       <c r="C389" s="1" t="n">
         <v>2742</v>
@@ -24690,13 +24743,14 @@
       <c r="H389" s="1" t="n">
         <v>507.4688</v>
       </c>
+      <c r="J389" s="1"/>
     </row>
     <row r="390" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A390" s="1" t="n">
         <v>1775776886.10169</v>
       </c>
       <c r="B390" s="1" t="n">
-        <v>-858</v>
+        <v>-678</v>
       </c>
       <c r="C390" s="1" t="n">
         <v>2740</v>
@@ -24716,13 +24770,14 @@
       <c r="H390" s="1" t="n">
         <v>504.5682</v>
       </c>
+      <c r="J390" s="1"/>
     </row>
     <row r="391" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A391" s="1" t="n">
         <v>1775776886.2784</v>
       </c>
       <c r="B391" s="1" t="n">
-        <v>-858</v>
+        <v>-678</v>
       </c>
       <c r="C391" s="1" t="n">
         <v>2739</v>
@@ -24742,13 +24797,14 @@
       <c r="H391" s="1" t="n">
         <v>501.1392</v>
       </c>
+      <c r="J391" s="1"/>
     </row>
     <row r="392" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A392" s="1" t="n">
         <v>1775776886.31743</v>
       </c>
       <c r="B392" s="1" t="n">
-        <v>-858</v>
+        <v>-678</v>
       </c>
       <c r="C392" s="1" t="n">
         <v>2737</v>
@@ -24768,13 +24824,14 @@
       <c r="H392" s="1" t="n">
         <v>502.3776</v>
       </c>
+      <c r="J392" s="1"/>
     </row>
     <row r="393" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A393" s="1" t="n">
         <v>1775776886.52654</v>
       </c>
       <c r="B393" s="1" t="n">
-        <v>-858</v>
+        <v>-678</v>
       </c>
       <c r="C393" s="1" t="n">
         <v>2734</v>
@@ -24794,13 +24851,14 @@
       <c r="H393" s="1" t="n">
         <v>508.0192</v>
       </c>
+      <c r="J393" s="1"/>
     </row>
     <row r="394" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A394" s="1" t="n">
         <v>1775776886.53352</v>
       </c>
       <c r="B394" s="1" t="n">
-        <v>-858</v>
+        <v>-678</v>
       </c>
       <c r="C394" s="1" t="n">
         <v>2733</v>
@@ -24820,13 +24878,14 @@
       <c r="H394" s="1" t="n">
         <v>503.2941</v>
       </c>
+      <c r="J394" s="1"/>
     </row>
     <row r="395" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A395" s="1" t="n">
         <v>1775776886.78199</v>
       </c>
       <c r="B395" s="1" t="n">
-        <v>-858</v>
+        <v>-678</v>
       </c>
       <c r="C395" s="1" t="n">
         <v>2734</v>
@@ -24846,13 +24905,14 @@
       <c r="H395" s="1" t="n">
         <v>509.808</v>
       </c>
+      <c r="J395" s="1"/>
     </row>
     <row r="396" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A396" s="1" t="n">
         <v>1775776886.78475</v>
       </c>
       <c r="B396" s="1" t="n">
-        <v>-858</v>
+        <v>-678</v>
       </c>
       <c r="C396" s="1" t="n">
         <v>2734</v>
@@ -24872,13 +24932,14 @@
       <c r="H396" s="1" t="n">
         <v>513.248</v>
       </c>
+      <c r="J396" s="1"/>
     </row>
     <row r="397" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A397" s="1" t="n">
         <v>1775776886.85953</v>
       </c>
       <c r="B397" s="1" t="n">
-        <v>-857</v>
+        <v>-677</v>
       </c>
       <c r="C397" s="1" t="n">
         <v>2733</v>
@@ -24898,13 +24959,14 @@
       <c r="H397" s="1" t="n">
         <v>517.5136</v>
       </c>
+      <c r="J397" s="1"/>
     </row>
     <row r="398" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A398" s="1" t="n">
         <v>1775776887.04091</v>
       </c>
       <c r="B398" s="1" t="n">
-        <v>-856</v>
+        <v>-676</v>
       </c>
       <c r="C398" s="1" t="n">
         <v>2732</v>
@@ -24924,13 +24986,14 @@
       <c r="H398" s="1" t="n">
         <v>512.8352</v>
       </c>
+      <c r="J398" s="1"/>
     </row>
     <row r="399" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A399" s="1" t="n">
         <v>1775776887.07605</v>
       </c>
       <c r="B399" s="1" t="n">
-        <v>-856</v>
+        <v>-676</v>
       </c>
       <c r="C399" s="1" t="n">
         <v>2731</v>
@@ -24950,13 +25013,14 @@
       <c r="H399" s="1" t="n">
         <v>510.2208</v>
       </c>
+      <c r="J399" s="1"/>
     </row>
     <row r="400" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="1" t="n">
         <v>1775776887.29046</v>
       </c>
       <c r="B400" s="1" t="n">
-        <v>-855</v>
+        <v>-675</v>
       </c>
       <c r="C400" s="1" t="n">
         <v>2730</v>
@@ -24976,13 +25040,14 @@
       <c r="H400" s="1" t="n">
         <v>510.0832</v>
       </c>
+      <c r="J400" s="1"/>
     </row>
     <row r="401" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="1" t="n">
         <v>1775776887.29238</v>
       </c>
       <c r="B401" s="1" t="n">
-        <v>-855</v>
+        <v>-675</v>
       </c>
       <c r="C401" s="1" t="n">
         <v>2730</v>
@@ -25002,13 +25067,14 @@
       <c r="H401" s="1" t="n">
         <v>511.7344</v>
       </c>
+      <c r="J401" s="1"/>
     </row>
     <row r="402" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="1" t="n">
         <v>1775776887.54423</v>
       </c>
       <c r="B402" s="1" t="n">
-        <v>-854</v>
+        <v>-674</v>
       </c>
       <c r="C402" s="1" t="n">
         <v>2730</v>
@@ -25028,13 +25094,14 @@
       <c r="H402" s="1" t="n">
         <v>498.9376</v>
       </c>
+      <c r="J402" s="1"/>
     </row>
     <row r="403" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A403" s="1" t="n">
         <v>1775776887.54724</v>
       </c>
       <c r="B403" s="1" t="n">
-        <v>-854</v>
+        <v>-674</v>
       </c>
       <c r="C403" s="1" t="n">
         <v>2730</v>
@@ -25054,13 +25121,14 @@
       <c r="H403" s="1" t="n">
         <v>513.248</v>
       </c>
+      <c r="J403" s="1"/>
     </row>
     <row r="404" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A404" s="1" t="n">
         <v>1775776887.61738</v>
       </c>
       <c r="B404" s="1" t="n">
-        <v>-854</v>
+        <v>-674</v>
       </c>
       <c r="C404" s="1" t="n">
         <v>2731</v>
@@ -25080,13 +25148,14 @@
       <c r="H404" s="1" t="n">
         <v>517.5136</v>
       </c>
+      <c r="J404" s="1"/>
     </row>
     <row r="405" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A405" s="1" t="n">
         <v>1775776887.80256</v>
       </c>
       <c r="B405" s="1" t="n">
-        <v>-854</v>
+        <v>-674</v>
       </c>
       <c r="C405" s="1" t="n">
         <v>2732</v>
@@ -25106,13 +25175,14 @@
       <c r="H405" s="1" t="n">
         <v>520.9536</v>
       </c>
+      <c r="J405" s="1"/>
     </row>
     <row r="406" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A406" s="1" t="n">
         <v>1775776887.83284</v>
       </c>
       <c r="B406" s="1" t="n">
-        <v>-853</v>
+        <v>-673</v>
       </c>
       <c r="C406" s="1" t="n">
         <v>2733</v>
@@ -25132,13 +25202,14 @@
       <c r="H406" s="1" t="n">
         <v>513.1104</v>
       </c>
+      <c r="J406" s="1"/>
     </row>
     <row r="407" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A407" s="1" t="n">
         <v>1775776888.0514</v>
       </c>
       <c r="B407" s="1" t="n">
-        <v>-853</v>
+        <v>-673</v>
       </c>
       <c r="C407" s="1" t="n">
         <v>2732</v>
@@ -25158,13 +25229,14 @@
       <c r="H407" s="1" t="n">
         <v>516.4128</v>
       </c>
+      <c r="J407" s="1"/>
     </row>
     <row r="408" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A408" s="1" t="n">
         <v>1775776888.05445</v>
       </c>
       <c r="B408" s="1" t="n">
-        <v>-853</v>
+        <v>-673</v>
       </c>
       <c r="C408" s="1" t="n">
         <v>2731</v>
@@ -25184,13 +25256,14 @@
       <c r="H408" s="1" t="n">
         <v>512.4798</v>
       </c>
+      <c r="J408" s="1"/>
     </row>
     <row r="409" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A409" s="1" t="n">
         <v>1775776888.30445</v>
       </c>
       <c r="B409" s="1" t="n">
-        <v>-853</v>
+        <v>-673</v>
       </c>
       <c r="C409" s="1" t="n">
         <v>2729</v>
@@ -25210,13 +25283,14 @@
       <c r="H409" s="1" t="n">
         <v>510.1491</v>
       </c>
+      <c r="J409" s="1"/>
     </row>
     <row r="410" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A410" s="1" t="n">
         <v>1775776888.30711</v>
       </c>
       <c r="B410" s="1" t="n">
-        <v>-853</v>
+        <v>-673</v>
       </c>
       <c r="C410" s="1" t="n">
         <v>2728</v>
@@ -25236,13 +25310,14 @@
       <c r="H410" s="1" t="n">
         <v>508.3668</v>
       </c>
+      <c r="J410" s="1"/>
     </row>
     <row r="411" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="1" t="n">
         <v>1775776888.37374</v>
       </c>
       <c r="B411" s="1" t="n">
-        <v>-853</v>
+        <v>-673</v>
       </c>
       <c r="C411" s="1" t="n">
         <v>2729</v>
@@ -25262,13 +25337,14 @@
       <c r="H411" s="1" t="n">
         <v>516.5916</v>
       </c>
+      <c r="J411" s="1"/>
     </row>
     <row r="412" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A412" s="1" t="n">
         <v>1775776888.55544</v>
       </c>
       <c r="B412" s="1" t="n">
-        <v>-853</v>
+        <v>-673</v>
       </c>
       <c r="C412" s="1" t="n">
         <v>2731</v>
@@ -25288,13 +25364,14 @@
       <c r="H412" s="1" t="n">
         <v>505.4048</v>
       </c>
+      <c r="J412" s="1"/>
     </row>
     <row r="413" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A413" s="1" t="n">
         <v>1775776888.59064</v>
       </c>
       <c r="B413" s="1" t="n">
-        <v>-853</v>
+        <v>-673</v>
       </c>
       <c r="C413" s="1" t="n">
         <v>2733</v>
@@ -25314,13 +25391,14 @@
       <c r="H413" s="1" t="n">
         <v>502.928</v>
       </c>
+      <c r="J413" s="1"/>
     </row>
     <row r="414" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A414" s="1" t="n">
         <v>1775776888.80665</v>
       </c>
       <c r="B414" s="1" t="n">
-        <v>-854</v>
+        <v>-674</v>
       </c>
       <c r="C414" s="1" t="n">
         <v>2733</v>
@@ -25340,13 +25418,14 @@
       <c r="H414" s="1" t="n">
         <v>511.872</v>
       </c>
+      <c r="J414" s="1"/>
     </row>
     <row r="415" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A415" s="1" t="n">
         <v>1775776888.81269</v>
       </c>
       <c r="B415" s="1" t="n">
-        <v>-854</v>
+        <v>-674</v>
       </c>
       <c r="C415" s="1" t="n">
         <v>2734</v>
@@ -25366,13 +25445,14 @@
       <c r="H415" s="1" t="n">
         <v>511.6164</v>
       </c>
+      <c r="J415" s="1"/>
     </row>
     <row r="416" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A416" s="1" t="n">
         <v>1775776889.06568</v>
       </c>
       <c r="B416" s="1" t="n">
-        <v>-854</v>
+        <v>-674</v>
       </c>
       <c r="C416" s="1" t="n">
         <v>2733</v>
@@ -25392,13 +25472,14 @@
       <c r="H416" s="1" t="n">
         <v>506.2304</v>
       </c>
+      <c r="J416" s="1"/>
     </row>
     <row r="417" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A417" s="1" t="n">
         <v>1775776889.0732</v>
       </c>
       <c r="B417" s="1" t="n">
-        <v>-854</v>
+        <v>-674</v>
       </c>
       <c r="C417" s="1" t="n">
         <v>2730</v>
@@ -25418,13 +25499,14 @@
       <c r="H417" s="1" t="n">
         <v>507.4688</v>
       </c>
+      <c r="J417" s="1"/>
     </row>
     <row r="418" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A418" s="1" t="n">
         <v>1775776889.13152</v>
       </c>
       <c r="B418" s="1" t="n">
-        <v>-855</v>
+        <v>-675</v>
       </c>
       <c r="C418" s="1" t="n">
         <v>2729</v>
@@ -25444,13 +25526,14 @@
       <c r="H418" s="1" t="n">
         <v>508.2996</v>
       </c>
+      <c r="J418" s="1"/>
     </row>
     <row r="419" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A419" s="1" t="n">
         <v>1775776889.31732</v>
       </c>
       <c r="B419" s="1" t="n">
-        <v>-855</v>
+        <v>-675</v>
       </c>
       <c r="C419" s="1" t="n">
         <v>2728</v>
@@ -25470,13 +25553,14 @@
       <c r="H419" s="1" t="n">
         <v>505.2672</v>
       </c>
+      <c r="J419" s="1"/>
     </row>
     <row r="420" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A420" s="1" t="n">
         <v>1775776889.34614</v>
       </c>
       <c r="B420" s="1" t="n">
-        <v>-855</v>
+        <v>-675</v>
       </c>
       <c r="C420" s="1" t="n">
         <v>2725</v>
@@ -25496,13 +25580,14 @@
       <c r="H420" s="1" t="n">
         <v>501.552</v>
       </c>
+      <c r="J420" s="1"/>
     </row>
     <row r="421" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A421" s="1" t="n">
         <v>1775776889.57545</v>
       </c>
       <c r="B421" s="1" t="n">
-        <v>-855</v>
+        <v>-675</v>
       </c>
       <c r="C421" s="1" t="n">
         <v>2724</v>
@@ -25522,13 +25607,14 @@
       <c r="H421" s="1" t="n">
         <v>497.673</v>
       </c>
+      <c r="J421" s="1"/>
     </row>
     <row r="422" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A422" s="1" t="n">
         <v>1775776889.57776</v>
       </c>
       <c r="B422" s="1" t="n">
-        <v>-855</v>
+        <v>-675</v>
       </c>
       <c r="C422" s="1" t="n">
         <v>2723</v>
@@ -25548,13 +25634,14 @@
       <c r="H422" s="1" t="n">
         <v>500.864</v>
       </c>
+      <c r="J422" s="1"/>
     </row>
     <row r="423" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="1" t="n">
         <v>1775776889.67152</v>
       </c>
       <c r="B423" s="1" t="n">
-        <v>-855</v>
+        <v>-675</v>
       </c>
       <c r="C423" s="1" t="n">
         <v>2723</v>
@@ -25574,13 +25661,14 @@
       <c r="H423" s="1" t="n">
         <v>497.673</v>
       </c>
+      <c r="J423" s="1"/>
     </row>
     <row r="424" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A424" s="1" t="n">
         <v>1775776889.82648</v>
       </c>
       <c r="B424" s="1" t="n">
-        <v>-855</v>
+        <v>-675</v>
       </c>
       <c r="C424" s="1" t="n">
         <v>2723</v>
@@ -25600,13 +25688,14 @@
       <c r="H424" s="1" t="n">
         <v>493.4229</v>
       </c>
+      <c r="J424" s="1"/>
     </row>
     <row r="425" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A425" s="1" t="n">
         <v>1775776889.88749</v>
       </c>
       <c r="B425" s="1" t="n">
-        <v>-855</v>
+        <v>-675</v>
       </c>
       <c r="C425" s="1" t="n">
         <v>2723</v>
@@ -25626,13 +25715,14 @@
       <c r="H425" s="1" t="n">
         <v>501.2376</v>
       </c>
+      <c r="J425" s="1"/>
     </row>
     <row r="426" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A426" s="1" t="n">
         <v>1775776890.08671</v>
       </c>
       <c r="B426" s="1" t="n">
-        <v>-855</v>
+        <v>-675</v>
       </c>
       <c r="C426" s="1" t="n">
         <v>2722</v>
@@ -25652,13 +25742,14 @@
       <c r="H426" s="1" t="n">
         <v>512.2848</v>
       </c>
+      <c r="J426" s="1"/>
     </row>
     <row r="427" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A427" s="1" t="n">
         <v>1775776890.10395</v>
       </c>
       <c r="B427" s="1" t="n">
-        <v>-855</v>
+        <v>-675</v>
       </c>
       <c r="C427" s="1" t="n">
         <v>2721</v>
@@ -25678,13 +25769,14 @@
       <c r="H427" s="1" t="n">
         <v>511.7344</v>
       </c>
+      <c r="J427" s="1"/>
     </row>
     <row r="428" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A428" s="1" t="n">
         <v>1775776890.33399</v>
       </c>
       <c r="B428" s="1" t="n">
-        <v>-855</v>
+        <v>-675</v>
       </c>
       <c r="C428" s="1" t="n">
         <v>2719</v>
@@ -25704,13 +25796,14 @@
       <c r="H428" s="1" t="n">
         <v>506.4474</v>
       </c>
+      <c r="J428" s="1"/>
     </row>
     <row r="429" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="1" t="n">
         <v>1775776890.33659</v>
       </c>
       <c r="B429" s="1" t="n">
-        <v>-855</v>
+        <v>-675</v>
       </c>
       <c r="C429" s="1" t="n">
         <v>2718</v>
@@ -25730,13 +25823,14 @@
       <c r="H429" s="1" t="n">
         <v>509.8749</v>
       </c>
+      <c r="J429" s="1"/>
     </row>
     <row r="430" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="1" t="n">
         <v>1775776890.42959</v>
       </c>
       <c r="B430" s="1" t="n">
-        <v>-855</v>
+        <v>-675</v>
       </c>
       <c r="C430" s="1" t="n">
         <v>2718</v>
@@ -25756,13 +25850,14 @@
       <c r="H430" s="1" t="n">
         <v>504.1167</v>
       </c>
+      <c r="J430" s="1"/>
     </row>
     <row r="431" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A431" s="1" t="n">
         <v>1775776890.58598</v>
       </c>
       <c r="B431" s="1" t="n">
-        <v>-855</v>
+        <v>-675</v>
       </c>
       <c r="C431" s="1" t="n">
         <v>2719</v>
@@ -25782,13 +25877,14 @@
       <c r="H431" s="1" t="n">
         <v>505.7619</v>
       </c>
+      <c r="J431" s="1"/>
     </row>
     <row r="432" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A432" s="1" t="n">
         <v>1775776890.6452</v>
       </c>
       <c r="B432" s="1" t="n">
-        <v>-855</v>
+        <v>-675</v>
       </c>
       <c r="C432" s="1" t="n">
         <v>2721</v>
@@ -25808,13 +25904,14 @@
       <c r="H432" s="1" t="n">
         <v>486.5536</v>
       </c>
+      <c r="J432" s="1"/>
     </row>
     <row r="433" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A433" s="1" t="n">
         <v>1775776890.84232</v>
       </c>
       <c r="B433" s="1" t="n">
-        <v>-854</v>
+        <v>-674</v>
       </c>
       <c r="C433" s="1" t="n">
         <v>2724</v>
@@ -25834,13 +25931,14 @@
       <c r="H433" s="1" t="n">
         <v>506.6432</v>
       </c>
+      <c r="J433" s="1"/>
     </row>
     <row r="434" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A434" s="1" t="n">
         <v>1775776890.86097</v>
       </c>
       <c r="B434" s="1" t="n">
-        <v>-854</v>
+        <v>-674</v>
       </c>
       <c r="C434" s="1" t="n">
         <v>2727</v>
@@ -25860,13 +25958,14 @@
       <c r="H434" s="1" t="n">
         <v>499.8666</v>
       </c>
+      <c r="J434" s="1"/>
     </row>
     <row r="435" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A435" s="1" t="n">
         <v>1775776891.10104</v>
       </c>
       <c r="B435" s="1" t="n">
-        <v>-854</v>
+        <v>-674</v>
       </c>
       <c r="C435" s="1" t="n">
         <v>2730</v>
@@ -25886,13 +25985,14 @@
       <c r="H435" s="1" t="n">
         <v>474.9144</v>
       </c>
+      <c r="J435" s="1"/>
     </row>
     <row r="436" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A436" s="1" t="n">
         <v>1775776891.10413</v>
       </c>
       <c r="B436" s="1" t="n">
-        <v>-854</v>
+        <v>-674</v>
       </c>
       <c r="C436" s="1" t="n">
         <v>2736</v>
@@ -25912,13 +26012,14 @@
       <c r="H436" s="1" t="n">
         <v>498.0843</v>
       </c>
+      <c r="J436" s="1"/>
     </row>
     <row r="437" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A437" s="1" t="n">
         <v>1775776891.18521</v>
       </c>
       <c r="B437" s="1" t="n">
-        <v>-854</v>
+        <v>-674</v>
       </c>
       <c r="C437" s="1" t="n">
         <v>2736</v>
@@ -25938,13 +26039,14 @@
       <c r="H437" s="1" t="n">
         <v>489.0357</v>
       </c>
+      <c r="J437" s="1"/>
     </row>
     <row r="438" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A438" s="1" t="n">
         <v>1775776891.35191</v>
       </c>
       <c r="B438" s="1" t="n">
-        <v>-854</v>
+        <v>-674</v>
       </c>
       <c r="C438" s="1" t="n">
         <v>2736</v>
@@ -25964,13 +26066,14 @@
       <c r="H438" s="1" t="n">
         <v>502.1024</v>
       </c>
+      <c r="J438" s="1"/>
     </row>
     <row r="439" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A439" s="1" t="n">
         <v>1775776891.40178</v>
       </c>
       <c r="B439" s="1" t="n">
-        <v>-853</v>
+        <v>-673</v>
       </c>
       <c r="C439" s="1" t="n">
         <v>2735</v>
@@ -25990,13 +26093,14 @@
       <c r="H439" s="1" t="n">
         <v>514.8992</v>
       </c>
+      <c r="J439" s="1"/>
     </row>
     <row r="440" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A440" s="1" t="n">
         <v>1775776891.60073</v>
       </c>
       <c r="B440" s="1" t="n">
-        <v>-853</v>
+        <v>-673</v>
       </c>
       <c r="C440" s="1" t="n">
         <v>2735</v>
@@ -26016,13 +26120,14 @@
       <c r="H440" s="1" t="n">
         <v>513.1104</v>
       </c>
+      <c r="J440" s="1"/>
     </row>
     <row r="441" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A441" s="1" t="n">
         <v>1775776891.61917</v>
       </c>
       <c r="B441" s="1" t="n">
-        <v>-853</v>
+        <v>-673</v>
       </c>
       <c r="C441" s="1" t="n">
         <v>2735</v>
@@ -26042,13 +26147,14 @@
       <c r="H441" s="1" t="n">
         <v>504.3909</v>
       </c>
+      <c r="J441" s="1"/>
     </row>
     <row r="442" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A442" s="1" t="n">
         <v>1775776891.8578</v>
       </c>
       <c r="B442" s="1" t="n">
-        <v>-853</v>
+        <v>-673</v>
       </c>
       <c r="C442" s="1" t="n">
         <v>2737</v>
@@ -26068,13 +26174,14 @@
       <c r="H442" s="1" t="n">
         <v>503.616</v>
       </c>
+      <c r="J442" s="1"/>
     </row>
     <row r="443" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A443" s="1" t="n">
         <v>1775776891.86065</v>
       </c>
       <c r="B443" s="1" t="n">
-        <v>-853</v>
+        <v>-673</v>
       </c>
       <c r="C443" s="1" t="n">
         <v>2738</v>
@@ -26094,13 +26201,14 @@
       <c r="H443" s="1" t="n">
         <v>494.2455</v>
       </c>
+      <c r="J443" s="1"/>
     </row>
     <row r="444" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A444" s="1" t="n">
         <v>1775776891.94378</v>
       </c>
       <c r="B444" s="1" t="n">
-        <v>-853</v>
+        <v>-673</v>
       </c>
       <c r="C444" s="1" t="n">
         <v>2739</v>
@@ -26120,13 +26228,14 @@
       <c r="H444" s="1" t="n">
         <v>496.4391</v>
       </c>
+      <c r="J444" s="1"/>
     </row>
     <row r="445" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A445" s="1" t="n">
         <v>1775776892.11359</v>
       </c>
       <c r="B445" s="1" t="n">
-        <v>-853</v>
+        <v>-673</v>
       </c>
       <c r="C445" s="1" t="n">
         <v>2741</v>
@@ -26146,13 +26255,14 @@
       <c r="H445" s="1" t="n">
         <v>489.8583</v>
       </c>
+      <c r="J445" s="1"/>
     </row>
     <row r="446" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A446" s="1" t="n">
         <v>1775776892.15997</v>
       </c>
       <c r="B446" s="1" t="n">
-        <v>-852</v>
+        <v>-672</v>
       </c>
       <c r="C446" s="1" t="n">
         <v>2743</v>
@@ -26172,13 +26282,14 @@
       <c r="H446" s="1" t="n">
         <v>496.4391</v>
       </c>
+      <c r="J446" s="1"/>
     </row>
     <row r="447" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A447" s="1" t="n">
         <v>1775776892.36171</v>
       </c>
       <c r="B447" s="1" t="n">
-        <v>-852</v>
+        <v>-672</v>
       </c>
       <c r="C447" s="1" t="n">
         <v>2743</v>
@@ -26198,13 +26309,14 @@
       <c r="H447" s="1" t="n">
         <v>506.0928</v>
       </c>
+      <c r="J447" s="1"/>
     </row>
     <row r="448" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A448" s="1" t="n">
         <v>1775776892.37546</v>
       </c>
       <c r="B448" s="1" t="n">
-        <v>-852</v>
+        <v>-672</v>
       </c>
       <c r="C448" s="1" t="n">
         <v>2743</v>
@@ -26224,13 +26336,14 @@
       <c r="H448" s="1" t="n">
         <v>489.5841</v>
       </c>
+      <c r="J448" s="1"/>
     </row>
     <row r="449" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A449" s="1" t="n">
         <v>1775776892.61654</v>
       </c>
       <c r="B449" s="1" t="n">
-        <v>-852</v>
+        <v>-672</v>
       </c>
       <c r="C449" s="1" t="n">
         <v>2744</v>
@@ -26250,13 +26363,14 @@
       <c r="H449" s="1" t="n">
         <v>469.4304</v>
       </c>
+      <c r="J449" s="1"/>
     </row>
     <row r="450" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A450" s="1" t="n">
         <v>1775776892.61902</v>
       </c>
       <c r="B450" s="1" t="n">
-        <v>-852</v>
+        <v>-672</v>
       </c>
       <c r="C450" s="1" t="n">
         <v>2744</v>
@@ -26276,13 +26390,14 @@
       <c r="H450" s="1" t="n">
         <v>487.2534</v>
       </c>
+      <c r="J450" s="1"/>
     </row>
     <row r="451" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A451" s="1" t="n">
         <v>1775776892.70003</v>
       </c>
       <c r="B451" s="1" t="n">
-        <v>-852</v>
+        <v>-672</v>
       </c>
       <c r="C451" s="1" t="n">
         <v>2744</v>
@@ -26302,13 +26417,14 @@
       <c r="H451" s="1" t="n">
         <v>515.0847</v>
       </c>
+      <c r="J451" s="1"/>
     </row>
     <row r="452" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A452" s="1" t="n">
         <v>1775776892.86606</v>
       </c>
       <c r="B452" s="1" t="n">
-        <v>-852</v>
+        <v>-672</v>
       </c>
       <c r="C452" s="1" t="n">
         <v>2744</v>
@@ -26328,13 +26444,14 @@
       <c r="H452" s="1" t="n">
         <v>513.0282</v>
       </c>
+      <c r="J452" s="1"/>
     </row>
     <row r="453" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A453" s="1" t="n">
         <v>1775776892.91614</v>
       </c>
       <c r="B453" s="1" t="n">
-        <v>-852</v>
+        <v>-672</v>
       </c>
       <c r="C453" s="1" t="n">
         <v>2743</v>
@@ -26354,13 +26471,14 @@
       <c r="H453" s="1" t="n">
         <v>501.552</v>
       </c>
+      <c r="J453" s="1"/>
     </row>
     <row r="454" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A454" s="1" t="n">
         <v>1775776893.12346</v>
       </c>
       <c r="B454" s="1" t="n">
-        <v>-851</v>
+        <v>-671</v>
       </c>
       <c r="C454" s="1" t="n">
         <v>2743</v>
@@ -26380,13 +26498,14 @@
       <c r="H454" s="1" t="n">
         <v>496.9875</v>
       </c>
+      <c r="J454" s="1"/>
     </row>
     <row r="455" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A455" s="1" t="n">
         <v>1775776893.13351</v>
       </c>
       <c r="B455" s="1" t="n">
-        <v>-851</v>
+        <v>-671</v>
       </c>
       <c r="C455" s="1" t="n">
         <v>2742</v>
@@ -26406,13 +26525,14 @@
       <c r="H455" s="1" t="n">
         <v>489.9954</v>
       </c>
+      <c r="J455" s="1"/>
     </row>
     <row r="456" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A456" s="1" t="n">
         <v>1775776893.36021</v>
       </c>
       <c r="B456" s="1" t="n">
-        <v>-851</v>
+        <v>-671</v>
       </c>
       <c r="C456" s="1" t="n">
         <v>2742</v>
@@ -26432,13 +26552,14 @@
       <c r="H456" s="1" t="n">
         <v>500.4512</v>
       </c>
+      <c r="J456" s="1"/>
     </row>
     <row r="457" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A457" s="1" t="n">
         <v>1775776893.36275</v>
       </c>
       <c r="B457" s="1" t="n">
-        <v>-851</v>
+        <v>-671</v>
       </c>
       <c r="C457" s="1" t="n">
         <v>2741</v>
@@ -26458,13 +26579,14 @@
       <c r="H457" s="1" t="n">
         <v>505.7619</v>
       </c>
+      <c r="J457" s="1"/>
     </row>
     <row r="458" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A458" s="1" t="n">
         <v>1775776893.59495</v>
       </c>
       <c r="B458" s="1" t="n">
-        <v>-850</v>
+        <v>-670</v>
       </c>
       <c r="C458" s="1" t="n">
         <v>2740</v>
@@ -26484,13 +26606,14 @@
       <c r="H458" s="1" t="n">
         <v>512.1472</v>
       </c>
+      <c r="J458" s="1"/>
     </row>
     <row r="459" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A459" s="1" t="n">
         <v>1775776893.60061</v>
       </c>
       <c r="B459" s="1" t="n">
-        <v>-850</v>
+        <v>-670</v>
       </c>
       <c r="C459" s="1" t="n">
         <v>2737</v>
@@ -26510,13 +26633,14 @@
       <c r="H459" s="1" t="n">
         <v>506.9184</v>
       </c>
+      <c r="J459" s="1"/>
     </row>
     <row r="460" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A460" s="1" t="n">
         <v>1775776893.67533</v>
       </c>
       <c r="B460" s="1" t="n">
-        <v>-850</v>
+        <v>-670</v>
       </c>
       <c r="C460" s="1" t="n">
         <v>2733</v>
@@ -26536,13 +26660,14 @@
       <c r="H460" s="1" t="n">
         <v>511.6572</v>
       </c>
+      <c r="J460" s="1"/>
     </row>
     <row r="461" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A461" s="1" t="n">
         <v>1775776893.83801</v>
       </c>
       <c r="B461" s="1" t="n">
-        <v>-849</v>
+        <v>-669</v>
       </c>
       <c r="C461" s="1" t="n">
         <v>2729</v>
@@ -26562,13 +26687,14 @@
       <c r="H461" s="1" t="n">
         <v>514.624</v>
       </c>
+      <c r="J461" s="1"/>
     </row>
     <row r="462" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A462" s="1" t="n">
         <v>1775776893.89152</v>
       </c>
       <c r="B462" s="1" t="n">
-        <v>-849</v>
+        <v>-669</v>
       </c>
       <c r="C462" s="1" t="n">
         <v>2725</v>
@@ -26588,13 +26714,14 @@
       <c r="H462" s="1" t="n">
         <v>514.7616</v>
       </c>
+      <c r="J462" s="1"/>
     </row>
     <row r="463" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A463" s="1" t="n">
         <v>1775776894.08795</v>
       </c>
       <c r="B463" s="1" t="n">
-        <v>-849</v>
+        <v>-669</v>
       </c>
       <c r="C463" s="1" t="n">
         <v>2721</v>
@@ -26614,13 +26741,14 @@
       <c r="H463" s="1" t="n">
         <v>518.752</v>
       </c>
+      <c r="J463" s="1"/>
     </row>
     <row r="464" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A464" s="1" t="n">
         <v>1775776894.10715</v>
       </c>
       <c r="B464" s="1" t="n">
-        <v>-849</v>
+        <v>-669</v>
       </c>
       <c r="C464" s="1" t="n">
         <v>2718</v>
@@ -26640,13 +26768,14 @@
       <c r="H464" s="1" t="n">
         <v>511.9768</v>
       </c>
+      <c r="J464" s="1"/>
     </row>
     <row r="465" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A465" s="1" t="n">
         <v>1775776894.33408</v>
       </c>
       <c r="B465" s="1" t="n">
-        <v>-848</v>
+        <v>-668</v>
       </c>
       <c r="C465" s="1" t="n">
         <v>2711</v>
@@ -26666,13 +26795,14 @@
       <c r="H465" s="1" t="n">
         <v>507.6056</v>
       </c>
+      <c r="J465" s="1"/>
     </row>
     <row r="466" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A466" s="1" t="n">
         <v>1775776894.33653</v>
       </c>
       <c r="B466" s="1" t="n">
-        <v>-848</v>
+        <v>-668</v>
       </c>
       <c r="C466" s="1" t="n">
         <v>2708</v>
@@ -26692,13 +26822,14 @@
       <c r="H466" s="1" t="n">
         <v>509.3952</v>
       </c>
+      <c r="J466" s="1"/>
     </row>
     <row r="467" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A467" s="1" t="n">
         <v>1775776894.58001</v>
       </c>
       <c r="B467" s="1" t="n">
-        <v>-848</v>
+        <v>-668</v>
       </c>
       <c r="C467" s="1" t="n">
         <v>2707</v>
@@ -26718,13 +26849,14 @@
       <c r="H467" s="1" t="n">
         <v>504.9393</v>
       </c>
+      <c r="J467" s="1"/>
     </row>
     <row r="468" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A468" s="1" t="n">
         <v>1775776894.58532</v>
       </c>
       <c r="B468" s="1" t="n">
-        <v>-848</v>
+        <v>-668</v>
       </c>
       <c r="C468" s="1" t="n">
         <v>2706</v>
@@ -26744,13 +26876,14 @@
       <c r="H468" s="1" t="n">
         <v>501.3747</v>
       </c>
+      <c r="J468" s="1"/>
     </row>
     <row r="469" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A469" s="1" t="n">
         <v>1775776894.64889</v>
       </c>
       <c r="B469" s="1" t="n">
-        <v>-848</v>
+        <v>-668</v>
       </c>
       <c r="C469" s="1" t="n">
         <v>2704</v>
@@ -26770,13 +26903,14 @@
       <c r="H469" s="1" t="n">
         <v>497.9472</v>
       </c>
+      <c r="J469" s="1"/>
     </row>
     <row r="470" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A470" s="1" t="n">
         <v>1775776894.84107</v>
       </c>
       <c r="B470" s="1" t="n">
-        <v>-848</v>
+        <v>-668</v>
       </c>
       <c r="C470" s="1" t="n">
         <v>2704</v>
@@ -26796,13 +26930,14 @@
       <c r="H470" s="1" t="n">
         <v>497.5359</v>
       </c>
+      <c r="J470" s="1"/>
     </row>
     <row r="471" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A471" s="1" t="n">
         <v>1775776894.86472</v>
       </c>
       <c r="B471" s="1" t="n">
-        <v>-848</v>
+        <v>-668</v>
       </c>
       <c r="C471" s="1" t="n">
         <v>2704</v>
@@ -26822,13 +26957,14 @@
       <c r="H471" s="1" t="n">
         <v>493.9713</v>
       </c>
+      <c r="J471" s="1"/>
     </row>
     <row r="472" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A472" s="1" t="n">
         <v>1775776895.09823</v>
       </c>
       <c r="B472" s="1" t="n">
-        <v>-848</v>
+        <v>-668</v>
       </c>
       <c r="C472" s="1" t="n">
         <v>2703</v>
@@ -26848,13 +26984,14 @@
       <c r="H472" s="1" t="n">
         <v>496.4391</v>
       </c>
+      <c r="J472" s="1"/>
     </row>
     <row r="473" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A473" s="1" t="n">
         <v>1775776895.10067</v>
       </c>
       <c r="B473" s="1" t="n">
-        <v>-848</v>
+        <v>-668</v>
       </c>
       <c r="C473" s="1" t="n">
         <v>2703</v>
@@ -26874,13 +27011,14 @@
       <c r="H473" s="1" t="n">
         <v>505.2592</v>
       </c>
+      <c r="J473" s="1"/>
     </row>
     <row r="474" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A474" s="1" t="n">
         <v>1775776895.18863</v>
       </c>
       <c r="B474" s="1" t="n">
-        <v>-848</v>
+        <v>-668</v>
       </c>
       <c r="C474" s="1" t="n">
         <v>2704</v>
@@ -26900,13 +27038,14 @@
       <c r="H474" s="1" t="n">
         <v>495.4794</v>
       </c>
+      <c r="J474" s="1"/>
     </row>
     <row r="475" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A475" s="1" t="n">
         <v>1775776895.35448</v>
       </c>
       <c r="B475" s="1" t="n">
-        <v>-848</v>
+        <v>-668</v>
       </c>
       <c r="C475" s="1" t="n">
         <v>2707</v>
@@ -26926,13 +27065,14 @@
       <c r="H475" s="1" t="n">
         <v>500.2779</v>
       </c>
+      <c r="J475" s="1"/>
     </row>
     <row r="476" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A476" s="1" t="n">
         <v>1775776895.40463</v>
       </c>
       <c r="B476" s="1" t="n">
-        <v>-848</v>
+        <v>-668</v>
       </c>
       <c r="C476" s="1" t="n">
         <v>2710</v>
@@ -26952,13 +27092,14 @@
       <c r="H476" s="1" t="n">
         <v>522.0768</v>
       </c>
+      <c r="J476" s="1"/>
     </row>
     <row r="477" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A477" s="1" t="n">
         <v>1775776895.60029</v>
       </c>
       <c r="B477" s="1" t="n">
-        <v>-848</v>
+        <v>-668</v>
       </c>
       <c r="C477" s="1" t="n">
         <v>2713</v>
@@ -26978,13 +27119,14 @@
       <c r="H477" s="1" t="n">
         <v>523.1736</v>
       </c>
+      <c r="J477" s="1"/>
     </row>
     <row r="478" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A478" s="1" t="n">
         <v>1775776895.62042</v>
       </c>
       <c r="B478" s="1" t="n">
-        <v>-848</v>
+        <v>-668</v>
       </c>
       <c r="C478" s="1" t="n">
         <v>2715</v>
@@ -27004,13 +27146,14 @@
       <c r="H478" s="1" t="n">
         <v>515.3918</v>
       </c>
+      <c r="J478" s="1"/>
     </row>
     <row r="479" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A479" s="1" t="n">
         <v>1775776895.85525</v>
       </c>
       <c r="B479" s="1" t="n">
-        <v>-847</v>
+        <v>-667</v>
       </c>
       <c r="C479" s="1" t="n">
         <v>2716</v>
@@ -27030,13 +27173,14 @@
       <c r="H479" s="1" t="n">
         <v>516.0748</v>
       </c>
+      <c r="J479" s="1"/>
     </row>
     <row r="480" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A480" s="1" t="n">
         <v>1775776895.85769</v>
       </c>
       <c r="B480" s="1" t="n">
-        <v>-847</v>
+        <v>-667</v>
       </c>
       <c r="C480" s="1" t="n">
         <v>2717</v>
@@ -27056,13 +27200,14 @@
       <c r="H480" s="1" t="n">
         <v>503.157</v>
       </c>
+      <c r="J480" s="1"/>
     </row>
     <row r="481" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A481" s="1" t="n">
         <v>1775776895.94527</v>
       </c>
       <c r="B481" s="1" t="n">
-        <v>-846</v>
+        <v>-666</v>
       </c>
       <c r="C481" s="1" t="n">
         <v>2718</v>
@@ -27082,13 +27227,14 @@
       <c r="H481" s="1" t="n">
         <v>512.25</v>
       </c>
+      <c r="J481" s="1"/>
     </row>
     <row r="482" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A482" s="1" t="n">
         <v>1775776896.11639</v>
       </c>
       <c r="B482" s="1" t="n">
-        <v>-846</v>
+        <v>-666</v>
       </c>
       <c r="C482" s="1" t="n">
         <v>2718</v>
@@ -27108,13 +27254,14 @@
       <c r="H482" s="1" t="n">
         <v>508.4252</v>
       </c>
+      <c r="J482" s="1"/>
     </row>
     <row r="483" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A483" s="1" t="n">
         <v>1775776896.1622</v>
       </c>
       <c r="B483" s="1" t="n">
-        <v>-846</v>
+        <v>-666</v>
       </c>
       <c r="C483" s="1" t="n">
         <v>2718</v>
@@ -27134,13 +27281,14 @@
       <c r="H483" s="1" t="n">
         <v>511.2459</v>
       </c>
+      <c r="J483" s="1"/>
     </row>
     <row r="484" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A484" s="1" t="n">
         <v>1775776896.36777</v>
       </c>
       <c r="B484" s="1" t="n">
-        <v>-846</v>
+        <v>-666</v>
       </c>
       <c r="C484" s="1" t="n">
         <v>2718</v>
@@ -27160,13 +27308,14 @@
       <c r="H484" s="1" t="n">
         <v>502.4715</v>
       </c>
+      <c r="J484" s="1"/>
     </row>
     <row r="485" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A485" s="1" t="n">
         <v>1775776896.37857</v>
       </c>
       <c r="B485" s="1" t="n">
-        <v>-845</v>
+        <v>-665</v>
       </c>
       <c r="C485" s="1" t="n">
         <v>2719</v>
@@ -27186,13 +27335,14 @@
       <c r="H485" s="1" t="n">
         <v>477.1968</v>
       </c>
+      <c r="J485" s="1"/>
     </row>
     <row r="486" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A486" s="1" t="n">
         <v>1775776896.62152</v>
       </c>
       <c r="B486" s="1" t="n">
-        <v>-845</v>
+        <v>-665</v>
       </c>
       <c r="C486" s="1" t="n">
         <v>2720</v>
@@ -27212,13 +27362,14 @@
       <c r="H486" s="1" t="n">
         <v>495.6165</v>
       </c>
+      <c r="J486" s="1"/>
     </row>
     <row r="487" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A487" s="1" t="n">
         <v>1775776896.62439</v>
       </c>
       <c r="B487" s="1" t="n">
-        <v>-844</v>
+        <v>-664</v>
       </c>
       <c r="C487" s="1" t="n">
         <v>2720</v>
@@ -27238,13 +27389,14 @@
       <c r="H487" s="1" t="n">
         <v>505.1468</v>
       </c>
+      <c r="J487" s="1"/>
     </row>
     <row r="488" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A488" s="1" t="n">
         <v>1775776896.70371</v>
       </c>
       <c r="B488" s="1" t="n">
-        <v>-844</v>
+        <v>-664</v>
       </c>
       <c r="C488" s="1" t="n">
         <v>2721</v>
@@ -27264,13 +27416,14 @@
       <c r="H488" s="1" t="n">
         <v>502.3344</v>
       </c>
+      <c r="J488" s="1"/>
     </row>
     <row r="489" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A489" s="1" t="n">
         <v>1775776896.87541</v>
       </c>
       <c r="B489" s="1" t="n">
-        <v>-843</v>
+        <v>-663</v>
       </c>
       <c r="C489" s="1" t="n">
         <v>2721</v>
@@ -27290,13 +27443,14 @@
       <c r="H489" s="1" t="n">
         <v>500.0926</v>
       </c>
+      <c r="J489" s="1"/>
     </row>
     <row r="490" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A490" s="1" t="n">
         <v>1775776896.9198</v>
       </c>
       <c r="B490" s="1" t="n">
-        <v>-843</v>
+        <v>-663</v>
       </c>
       <c r="C490" s="1" t="n">
         <v>2722</v>
@@ -27316,13 +27470,14 @@
       <c r="H490" s="1" t="n">
         <v>513.7137</v>
       </c>
+      <c r="J490" s="1"/>
     </row>
     <row r="491" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A491" s="1" t="n">
         <v>1775776897.1333</v>
       </c>
       <c r="B491" s="1" t="n">
-        <v>-842</v>
+        <v>-662</v>
       </c>
       <c r="C491" s="1" t="n">
         <v>2723</v>
@@ -27342,13 +27497,14 @@
       <c r="H491" s="1" t="n">
         <v>508.0192</v>
       </c>
+      <c r="J491" s="1"/>
     </row>
     <row r="492" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A492" s="1" t="n">
         <v>1775776897.1356</v>
       </c>
       <c r="B492" s="1" t="n">
-        <v>-842</v>
+        <v>-662</v>
       </c>
       <c r="C492" s="1" t="n">
         <v>2723</v>
@@ -27368,13 +27524,14 @@
       <c r="H492" s="1" t="n">
         <v>510.201</v>
       </c>
+      <c r="J492" s="1"/>
     </row>
     <row r="493" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A493" s="1" t="n">
         <v>1775776897.38214</v>
       </c>
       <c r="B493" s="1" t="n">
-        <v>-841</v>
+        <v>-661</v>
       </c>
       <c r="C493" s="1" t="n">
         <v>2723</v>
@@ -27394,13 +27551,14 @@
       <c r="H493" s="1" t="n">
         <v>517.8506</v>
       </c>
+      <c r="J493" s="1"/>
     </row>
     <row r="494" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A494" s="1" t="n">
         <v>1775776897.38478</v>
       </c>
       <c r="B494" s="1" t="n">
-        <v>-841</v>
+        <v>-661</v>
       </c>
       <c r="C494" s="1" t="n">
         <v>2722</v>
@@ -27420,13 +27578,14 @@
       <c r="H494" s="1" t="n">
         <v>500.2779</v>
       </c>
+      <c r="J494" s="1"/>
     </row>
     <row r="495" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A495" s="1" t="n">
         <v>1775776897.45967</v>
       </c>
       <c r="B495" s="1" t="n">
-        <v>-841</v>
+        <v>-661</v>
       </c>
       <c r="C495" s="1" t="n">
         <v>2723</v>
@@ -27446,13 +27605,14 @@
       <c r="H495" s="1" t="n">
         <v>518.5336</v>
       </c>
+      <c r="J495" s="1"/>
     </row>
     <row r="496" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A496" s="1" t="n">
         <v>1775776897.63833</v>
       </c>
       <c r="B496" s="1" t="n">
-        <v>-840</v>
+        <v>-660</v>
       </c>
       <c r="C496" s="1" t="n">
         <v>2724</v>
@@ -27472,13 +27632,14 @@
       <c r="H496" s="1" t="n">
         <v>511.9768</v>
       </c>
+      <c r="J496" s="1"/>
     </row>
     <row r="497" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A497" s="1" t="n">
         <v>1775776897.67735</v>
       </c>
       <c r="B497" s="1" t="n">
-        <v>-840</v>
+        <v>-660</v>
       </c>
       <c r="C497" s="1" t="n">
         <v>2724</v>
@@ -27498,13 +27659,14 @@
       <c r="H497" s="1" t="n">
         <v>513.3024</v>
       </c>
+      <c r="J497" s="1"/>
     </row>
     <row r="498" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A498" s="1" t="n">
         <v>1775776897.88861</v>
       </c>
       <c r="B498" s="1" t="n">
-        <v>-839</v>
+        <v>-659</v>
       </c>
       <c r="C498" s="1" t="n">
         <v>2724</v>
@@ -27524,13 +27686,14 @@
       <c r="H498" s="1" t="n">
         <v>503.5076</v>
       </c>
+      <c r="J498" s="1"/>
     </row>
     <row r="499" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A499" s="1" t="n">
         <v>1775776897.89409</v>
       </c>
       <c r="B499" s="1" t="n">
-        <v>-839</v>
+        <v>-659</v>
       </c>
       <c r="C499" s="1" t="n">
         <v>2725</v>
@@ -27550,13 +27713,14 @@
       <c r="H499" s="1" t="n">
         <v>498.3585</v>
       </c>
+      <c r="J499" s="1"/>
     </row>
     <row r="500" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A500" s="1" t="n">
         <v>1775776898.14462</v>
       </c>
       <c r="B500" s="1" t="n">
-        <v>-838</v>
+        <v>-658</v>
       </c>
       <c r="C500" s="1" t="n">
         <v>2725</v>
@@ -27576,13 +27740,14 @@
       <c r="H500" s="1" t="n">
         <v>499.273</v>
       </c>
+      <c r="J500" s="1"/>
     </row>
     <row r="501" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A501" s="1" t="n">
         <v>1775776898.14714</v>
       </c>
       <c r="B501" s="1" t="n">
-        <v>-838</v>
+        <v>-658</v>
       </c>
       <c r="C501" s="1" t="n">
         <v>2726</v>
@@ -27602,13 +27767,14 @@
       <c r="H501" s="1" t="n">
         <v>502.1973</v>
       </c>
+      <c r="J501" s="1"/>
     </row>
     <row r="502" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A502" s="1" t="n">
         <v>1775776898.21773</v>
       </c>
       <c r="B502" s="1" t="n">
-        <v>-838</v>
+        <v>-658</v>
       </c>
       <c r="C502" s="1" t="n">
         <v>2727</v>
@@ -27628,13 +27794,14 @@
       <c r="H502" s="1" t="n">
         <v>498.7698</v>
       </c>
+      <c r="J502" s="1"/>
     </row>
     <row r="503" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A503" s="1" t="n">
         <v>1775776898.4022</v>
       </c>
       <c r="B503" s="1" t="n">
-        <v>-838</v>
+        <v>-658</v>
       </c>
       <c r="C503" s="1" t="n">
         <v>2728</v>
@@ -27654,13 +27821,14 @@
       <c r="H503" s="1" t="n">
         <v>505.2135</v>
       </c>
+      <c r="J503" s="1"/>
     </row>
     <row r="504" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A504" s="1" t="n">
         <v>1775776898.43376</v>
       </c>
       <c r="B504" s="1" t="n">
-        <v>-839</v>
+        <v>-659</v>
       </c>
       <c r="C504" s="1" t="n">
         <v>2730</v>
@@ -27680,13 +27848,14 @@
       <c r="H504" s="1" t="n">
         <v>506.3103</v>
       </c>
+      <c r="J504" s="1"/>
     </row>
     <row r="505" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A505" s="1" t="n">
         <v>1775776898.65502</v>
       </c>
       <c r="B505" s="1" t="n">
-        <v>-839</v>
+        <v>-659</v>
       </c>
       <c r="C505" s="1" t="n">
         <v>2730</v>
@@ -27706,13 +27875,14 @@
       <c r="H505" s="1" t="n">
         <v>509.808</v>
       </c>
+      <c r="J505" s="1"/>
     </row>
     <row r="506" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A506" s="1" t="n">
         <v>1775776898.65754</v>
       </c>
       <c r="B506" s="1" t="n">
-        <v>-839</v>
+        <v>-659</v>
       </c>
       <c r="C506" s="1" t="n">
         <v>2730</v>
@@ -27732,13 +27902,14 @@
       <c r="H506" s="1" t="n">
         <v>505.42</v>
       </c>
+      <c r="J506" s="1"/>
     </row>
     <row r="507" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A507" s="1" t="n">
         <v>1775776898.9065</v>
       </c>
       <c r="B507" s="1" t="n">
-        <v>-840</v>
+        <v>-660</v>
       </c>
       <c r="C507" s="1" t="n">
         <v>2729</v>
@@ -27758,13 +27929,14 @@
       <c r="H507" s="1" t="n">
         <v>509.0523</v>
       </c>
+      <c r="J507" s="1"/>
     </row>
     <row r="508" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A508" s="1" t="n">
         <v>1775776898.91138</v>
       </c>
       <c r="B508" s="1" t="n">
-        <v>-841</v>
+        <v>-661</v>
       </c>
       <c r="C508" s="1" t="n">
         <v>2728</v>
@@ -27784,13 +27956,14 @@
       <c r="H508" s="1" t="n">
         <v>502.8828</v>
       </c>
+      <c r="J508" s="1"/>
     </row>
     <row r="509" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A509" s="1" t="n">
         <v>1775776898.97451</v>
       </c>
       <c r="B509" s="1" t="n">
-        <v>-841</v>
+        <v>-661</v>
       </c>
       <c r="C509" s="1" t="n">
         <v>2729</v>
@@ -27810,13 +27983,14 @@
       <c r="H509" s="1" t="n">
         <v>501.7318</v>
       </c>
+      <c r="J509" s="1"/>
     </row>
     <row r="510" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A510" s="1" t="n">
         <v>1775776899.16635</v>
       </c>
       <c r="B510" s="1" t="n">
-        <v>-842</v>
+        <v>-662</v>
       </c>
       <c r="C510" s="1" t="n">
         <v>2729</v>
@@ -27836,13 +28010,14 @@
       <c r="H510" s="1" t="n">
         <v>504.4638</v>
       </c>
+      <c r="J510" s="1"/>
     </row>
     <row r="511" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A511" s="1" t="n">
         <v>1775776899.1916</v>
       </c>
       <c r="B511" s="1" t="n">
-        <v>-842</v>
+        <v>-662</v>
       </c>
       <c r="C511" s="1" t="n">
         <v>2728</v>
@@ -27862,13 +28037,14 @@
       <c r="H511" s="1" t="n">
         <v>500.9122</v>
       </c>
+      <c r="J511" s="1"/>
     </row>
     <row r="512" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A512" s="1" t="n">
         <v>1775776899.4179</v>
       </c>
       <c r="B512" s="1" t="n">
-        <v>-843</v>
+        <v>-663</v>
       </c>
       <c r="C512" s="1" t="n">
         <v>2728</v>
@@ -27888,13 +28064,14 @@
       <c r="H512" s="1" t="n">
         <v>472.0353</v>
       </c>
+      <c r="J512" s="1"/>
     </row>
     <row r="513" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A513" s="1" t="n">
         <v>1775776899.42065</v>
       </c>
       <c r="B513" s="1" t="n">
-        <v>-844</v>
+        <v>-664</v>
       </c>
       <c r="C513" s="1" t="n">
         <v>2728</v>
@@ -27914,13 +28091,14 @@
       <c r="H513" s="1" t="n">
         <v>506.6494</v>
       </c>
+      <c r="J513" s="1"/>
     </row>
     <row r="514" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A514" s="1" t="n">
         <v>1775776899.65812</v>
       </c>
       <c r="B514" s="1" t="n">
-        <v>-844</v>
+        <v>-664</v>
       </c>
       <c r="C514" s="1" t="n">
         <v>2727</v>
@@ -27940,13 +28118,14 @@
       <c r="H514" s="1" t="n">
         <v>476.051</v>
       </c>
+      <c r="J514" s="1"/>
     </row>
     <row r="515" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A515" s="1" t="n">
         <v>1775776899.6643</v>
       </c>
       <c r="B515" s="1" t="n">
-        <v>-845</v>
+        <v>-665</v>
       </c>
       <c r="C515" s="1" t="n">
         <v>2727</v>
@@ -27966,13 +28145,14 @@
       <c r="H515" s="1" t="n">
         <v>478.479</v>
       </c>
+      <c r="J515" s="1"/>
     </row>
     <row r="516" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A516" s="1" t="n">
         <v>1775776899.73328</v>
       </c>
       <c r="B516" s="1" t="n">
-        <v>-845</v>
+        <v>-665</v>
       </c>
       <c r="C516" s="1" t="n">
         <v>2727</v>
@@ -27992,13 +28172,14 @@
       <c r="H516" s="1" t="n">
         <v>468.8112</v>
       </c>
+      <c r="J516" s="1"/>
     </row>
     <row r="517" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A517" s="1" t="n">
         <v>1775776899.90654</v>
       </c>
       <c r="B517" s="1" t="n">
-        <v>-845</v>
+        <v>-665</v>
       </c>
       <c r="C517" s="1" t="n">
         <v>2726</v>
@@ -28018,13 +28199,14 @@
       <c r="H517" s="1" t="n">
         <v>476.0112</v>
       </c>
+      <c r="J517" s="1"/>
     </row>
     <row r="518" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A518" s="1" t="n">
         <v>1775776899.94852</v>
       </c>
       <c r="B518" s="1" t="n">
-        <v>-845</v>
+        <v>-665</v>
       </c>
       <c r="C518" s="1" t="n">
         <v>2724</v>
@@ -28044,13 +28226,14 @@
       <c r="H518" s="1" t="n">
         <v>470.587</v>
       </c>
+      <c r="J518" s="1"/>
     </row>
     <row r="519" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A519" s="1" t="n">
         <v>1775776900.16348</v>
       </c>
       <c r="B519" s="1" t="n">
-        <v>-845</v>
+        <v>-665</v>
       </c>
       <c r="C519" s="1" t="n">
         <v>2721</v>
@@ -28070,13 +28253,14 @@
       <c r="H519" s="1" t="n">
         <v>471.1334</v>
       </c>
+      <c r="J519" s="1"/>
     </row>
     <row r="520" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A520" s="1" t="n">
         <v>1775776900.16541</v>
       </c>
       <c r="B520" s="1" t="n">
-        <v>-845</v>
+        <v>-665</v>
       </c>
       <c r="C520" s="1" t="n">
         <v>2720</v>
@@ -28096,13 +28280,14 @@
       <c r="H520" s="1" t="n">
         <v>457.2002</v>
       </c>
+      <c r="J520" s="1"/>
     </row>
     <row r="521" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A521" s="1" t="n">
         <v>1775776900.41921</v>
       </c>
       <c r="B521" s="1" t="n">
-        <v>-845</v>
+        <v>-665</v>
       </c>
       <c r="C521" s="1" t="n">
         <v>2720</v>
@@ -28122,13 +28307,14 @@
       <c r="H521" s="1" t="n">
         <v>465.123</v>
       </c>
+      <c r="J521" s="1"/>
     </row>
     <row r="522" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A522" s="1" t="n">
         <v>1775776900.42213</v>
       </c>
       <c r="B522" s="1" t="n">
-        <v>-846</v>
+        <v>-666</v>
       </c>
       <c r="C522" s="1" t="n">
         <v>2720</v>
@@ -28148,13 +28334,14 @@
       <c r="H522" s="1" t="n">
         <v>476.051</v>
       </c>
+      <c r="J522" s="1"/>
     </row>
     <row r="523" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A523" s="1" t="n">
         <v>1775776900.48811</v>
       </c>
       <c r="B523" s="1" t="n">
-        <v>-846</v>
+        <v>-666</v>
       </c>
       <c r="C523" s="1" t="n">
         <v>2720</v>
@@ -28174,13 +28361,14 @@
       <c r="H523" s="1" t="n">
         <v>488.076</v>
       </c>
+      <c r="J523" s="1"/>
     </row>
     <row r="524" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A524" s="1" t="n">
         <v>1775776900.67169</v>
       </c>
       <c r="B524" s="1" t="n">
-        <v>-846</v>
+        <v>-666</v>
       </c>
       <c r="C524" s="1" t="n">
         <v>2722</v>
@@ -28200,13 +28388,14 @@
       <c r="H524" s="1" t="n">
         <v>491.4868</v>
       </c>
+      <c r="J524" s="1"/>
     </row>
     <row r="525" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A525" s="1" t="n">
         <v>1775776900.70518</v>
       </c>
       <c r="B525" s="1" t="n">
-        <v>-846</v>
+        <v>-666</v>
       </c>
       <c r="C525" s="1" t="n">
         <v>2723</v>
@@ -28226,13 +28415,14 @@
       <c r="H525" s="1" t="n">
         <v>492.5796</v>
       </c>
+      <c r="J525" s="1"/>
     </row>
     <row r="526" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A526" s="1" t="n">
         <v>1775776900.92457</v>
       </c>
       <c r="B526" s="1" t="n">
-        <v>-846</v>
+        <v>-666</v>
       </c>
       <c r="C526" s="1" t="n">
         <v>2725</v>
@@ -28252,13 +28442,14 @@
       <c r="H526" s="1" t="n">
         <v>469.472</v>
       </c>
+      <c r="J526" s="1"/>
     </row>
     <row r="527" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A527" s="1" t="n">
         <v>1775776900.92691</v>
       </c>
       <c r="B527" s="1" t="n">
-        <v>-846</v>
+        <v>-666</v>
       </c>
       <c r="C527" s="1" t="n">
         <v>2726</v>
@@ -28278,13 +28469,14 @@
       <c r="H527" s="1" t="n">
         <v>478.783</v>
       </c>
+      <c r="J527" s="1"/>
     </row>
     <row r="528" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A528" s="1" t="n">
         <v>1775776901.17772</v>
       </c>
       <c r="B528" s="1" t="n">
-        <v>-846</v>
+        <v>-666</v>
       </c>
       <c r="C528" s="1" t="n">
         <v>2725</v>
@@ -28304,13 +28496,14 @@
       <c r="H528" s="1" t="n">
         <v>482.6078</v>
       </c>
+      <c r="J528" s="1"/>
     </row>
     <row r="529" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A529" s="1" t="n">
         <v>1775776901.18285</v>
       </c>
       <c r="B529" s="1" t="n">
-        <v>-847</v>
+        <v>-667</v>
       </c>
       <c r="C529" s="1" t="n">
         <v>2724</v>
@@ -28330,13 +28523,14 @@
       <c r="H529" s="1" t="n">
         <v>464.0302</v>
       </c>
+      <c r="J529" s="1"/>
     </row>
     <row r="530" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A530" s="1" t="n">
         <v>1775776901.24688</v>
       </c>
       <c r="B530" s="1" t="n">
-        <v>-847</v>
+        <v>-667</v>
       </c>
       <c r="C530" s="1" t="n">
         <v>2723</v>
@@ -28356,13 +28550,14 @@
       <c r="H530" s="1" t="n">
         <v>469.4942</v>
       </c>
+      <c r="J530" s="1"/>
     </row>
     <row r="531" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A531" s="1" t="n">
         <v>1775776901.44768</v>
       </c>
       <c r="B531" s="1" t="n">
-        <v>-847</v>
+        <v>-667</v>
       </c>
       <c r="C531" s="1" t="n">
         <v>2723</v>
@@ -28382,13 +28577,14 @@
       <c r="H531" s="1" t="n">
         <v>500.3658</v>
       </c>
+      <c r="J531" s="1"/>
     </row>
     <row r="532" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A532" s="1" t="n">
         <v>1775776901.46156</v>
       </c>
       <c r="B532" s="1" t="n">
-        <v>-847</v>
+        <v>-667</v>
       </c>
       <c r="C532" s="1" t="n">
         <v>2724</v>
@@ -28408,13 +28604,14 @@
       <c r="H532" s="1" t="n">
         <v>478.2366</v>
       </c>
+      <c r="J532" s="1"/>
     </row>
     <row r="533" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A533" s="1" t="n">
         <v>1775776901.70073</v>
       </c>
       <c r="B533" s="1" t="n">
-        <v>-847</v>
+        <v>-667</v>
       </c>
       <c r="C533" s="1" t="n">
         <v>2725</v>
@@ -28434,13 +28631,14 @@
       <c r="H533" s="1" t="n">
         <v>491.64</v>
       </c>
+      <c r="J533" s="1"/>
     </row>
     <row r="534" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A534" s="1" t="n">
         <v>1775776901.70312</v>
       </c>
       <c r="B534" s="1" t="n">
-        <v>-847</v>
+        <v>-667</v>
       </c>
       <c r="C534" s="1" t="n">
         <v>2728</v>
@@ -28460,13 +28658,14 @@
       <c r="H534" s="1" t="n">
         <v>505.2834</v>
       </c>
+      <c r="J534" s="1"/>
     </row>
     <row r="535" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A535" s="1" t="n">
         <v>1775776901.78635</v>
       </c>
       <c r="B535" s="1" t="n">
-        <v>-848</v>
+        <v>-668</v>
       </c>
       <c r="C535" s="1" t="n">
         <v>2731</v>
@@ -28486,13 +28685,14 @@
       <c r="H535" s="1" t="n">
         <v>505.9664</v>
       </c>
+      <c r="J535" s="1"/>
     </row>
     <row r="536" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A536" s="1" t="n">
         <v>1775776901.96642</v>
       </c>
       <c r="B536" s="1" t="n">
-        <v>-847</v>
+        <v>-667</v>
       </c>
       <c r="C536" s="1" t="n">
         <v>2733</v>
@@ -28512,13 +28712,14 @@
       <c r="H536" s="1" t="n">
         <v>508.835</v>
       </c>
+      <c r="J536" s="1"/>
     </row>
     <row r="537" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A537" s="1" t="n">
         <v>1775776902.00228</v>
       </c>
       <c r="B537" s="1" t="n">
-        <v>-847</v>
+        <v>-667</v>
       </c>
       <c r="C537" s="1" t="n">
         <v>2735</v>
@@ -28538,13 +28739,14 @@
       <c r="H537" s="1" t="n">
         <v>510.6108</v>
       </c>
+      <c r="J537" s="1"/>
     </row>
     <row r="538" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A538" s="1" t="n">
         <v>1775776902.22851</v>
       </c>
       <c r="B538" s="1" t="n">
-        <v>-847</v>
+        <v>-667</v>
       </c>
       <c r="C538" s="1" t="n">
         <v>2736</v>
@@ -28564,13 +28766,14 @@
       <c r="H538" s="1" t="n">
         <v>509.2448</v>
       </c>
+      <c r="J538" s="1"/>
     </row>
     <row r="539" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A539" s="1" t="n">
         <v>1775776902.23095</v>
       </c>
       <c r="B539" s="1" t="n">
-        <v>-847</v>
+        <v>-667</v>
       </c>
       <c r="C539" s="1" t="n">
         <v>2737</v>
@@ -28590,13 +28793,14 @@
       <c r="H539" s="1" t="n">
         <v>515.2552</v>
       </c>
+      <c r="J539" s="1"/>
     </row>
     <row r="540" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A540" s="1" t="n">
         <v>1775776902.47895</v>
       </c>
       <c r="B540" s="1" t="n">
-        <v>-847</v>
+        <v>-667</v>
       </c>
       <c r="C540" s="1" t="n">
         <v>2738</v>
@@ -28616,13 +28820,14 @@
       <c r="H540" s="1" t="n">
         <v>515.5284</v>
       </c>
+      <c r="J540" s="1"/>
     </row>
     <row r="541" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A541" s="1" t="n">
         <v>1775776902.48633</v>
       </c>
       <c r="B541" s="1" t="n">
-        <v>-846</v>
+        <v>-666</v>
       </c>
       <c r="C541" s="1" t="n">
         <v>2739</v>
@@ -28642,13 +28847,14 @@
       <c r="H541" s="1" t="n">
         <v>507.8788</v>
       </c>
+      <c r="J541" s="1"/>
     </row>
     <row r="542" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A542" s="1" t="n">
         <v>1775776902.54551</v>
       </c>
       <c r="B542" s="1" t="n">
-        <v>-846</v>
+        <v>-666</v>
       </c>
       <c r="C542" s="1" t="n">
         <v>2739</v>
@@ -28668,13 +28874,14 @@
       <c r="H542" s="1" t="n">
         <v>512.584</v>
       </c>
+      <c r="J542" s="1"/>
     </row>
     <row r="543" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A543" s="1" t="n">
         <v>1775776902.74448</v>
       </c>
       <c r="B543" s="1" t="n">
-        <v>-846</v>
+        <v>-666</v>
       </c>
       <c r="C543" s="1" t="n">
         <v>2739</v>
@@ -28694,13 +28901,14 @@
       <c r="H543" s="1" t="n">
         <v>515.0847</v>
       </c>
+      <c r="J543" s="1"/>
     </row>
     <row r="544" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A544" s="1" t="n">
         <v>1775776902.76129</v>
       </c>
       <c r="B544" s="1" t="n">
-        <v>-846</v>
+        <v>-666</v>
       </c>
       <c r="C544" s="1" t="n">
         <v>2741</v>
@@ -28720,13 +28928,14 @@
       <c r="H544" s="1" t="n">
         <v>511.2938</v>
       </c>
+      <c r="J544" s="1"/>
     </row>
     <row r="545" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A545" s="1" t="n">
         <v>1775776902.99668</v>
       </c>
       <c r="B545" s="1" t="n">
-        <v>-845</v>
+        <v>-665</v>
       </c>
       <c r="C545" s="1" t="n">
         <v>2742</v>
@@ -28746,13 +28955,14 @@
       <c r="H545" s="1" t="n">
         <v>507.144</v>
       </c>
+      <c r="J545" s="1"/>
     </row>
     <row r="546" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A546" s="1" t="n">
         <v>1775776902.99901</v>
       </c>
       <c r="B546" s="1" t="n">
-        <v>-845</v>
+        <v>-665</v>
       </c>
       <c r="C546" s="1" t="n">
         <v>2743</v>
@@ -28772,13 +28982,14 @@
       <c r="H546" s="1" t="n">
         <v>498.7266</v>
       </c>
+      <c r="J546" s="1"/>
     </row>
     <row r="547" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A547" s="1" t="n">
         <v>1775776903.08501</v>
       </c>
       <c r="B547" s="1" t="n">
-        <v>-845</v>
+        <v>-665</v>
       </c>
       <c r="C547" s="1" t="n">
         <v>2744</v>
@@ -28798,13 +29009,14 @@
       <c r="H547" s="1" t="n">
         <v>458.976</v>
       </c>
+      <c r="J547" s="1"/>
     </row>
     <row r="548" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A548" s="1" t="n">
         <v>1775776903.2479</v>
       </c>
       <c r="B548" s="1" t="n">
-        <v>-845</v>
+        <v>-665</v>
       </c>
       <c r="C548" s="1" t="n">
         <v>2744</v>
@@ -28824,13 +29036,14 @@
       <c r="H548" s="1" t="n">
         <v>470.1772</v>
       </c>
+      <c r="J548" s="1"/>
     </row>
     <row r="549" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A549" s="1" t="n">
         <v>1775776903.30106</v>
       </c>
       <c r="B549" s="1" t="n">
-        <v>-845</v>
+        <v>-665</v>
       </c>
       <c r="C549" s="1" t="n">
         <v>2745</v>
@@ -28850,13 +29063,14 @@
       <c r="H549" s="1" t="n">
         <v>453.2388</v>
       </c>
+      <c r="J549" s="1"/>
     </row>
     <row r="550" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A550" s="1" t="n">
         <v>1775776903.50677</v>
       </c>
       <c r="B550" s="1" t="n">
-        <v>-844</v>
+        <v>-664</v>
       </c>
       <c r="C550" s="1" t="n">
         <v>2745</v>
@@ -28876,13 +29090,14 @@
       <c r="H550" s="1" t="n">
         <v>461.0673</v>
       </c>
+      <c r="J550" s="1"/>
     </row>
     <row r="551" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A551" s="1" t="n">
         <v>1775776903.51688</v>
       </c>
       <c r="B551" s="1" t="n">
-        <v>-842</v>
+        <v>-662</v>
       </c>
       <c r="C551" s="1" t="n">
         <v>2744</v>
@@ -28902,13 +29117,14 @@
       <c r="H551" s="1" t="n">
         <v>425.9324</v>
       </c>
+      <c r="J551" s="1"/>
     </row>
     <row r="552" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A552" s="1" t="n">
         <v>1775776903.75389</v>
       </c>
       <c r="B552" s="1" t="n">
-        <v>-839</v>
+        <v>-659</v>
       </c>
       <c r="C552" s="1" t="n">
         <v>2740</v>
@@ -28928,13 +29144,14 @@
       <c r="H552" s="1" t="n">
         <v>423.3066</v>
       </c>
+      <c r="J552" s="1"/>
     </row>
     <row r="553" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A553" s="1" t="n">
         <v>1775776903.75641</v>
       </c>
       <c r="B553" s="1" t="n">
-        <v>-832</v>
+        <v>-652</v>
       </c>
       <c r="C553" s="1" t="n">
         <v>2727</v>
@@ -28954,13 +29171,14 @@
       <c r="H553" s="1" t="n">
         <v>434.9536</v>
       </c>
+      <c r="J553" s="1"/>
     </row>
     <row r="554" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A554" s="1" t="n">
         <v>1775776903.84419</v>
       </c>
       <c r="B554" s="1" t="n">
-        <v>-828</v>
+        <v>-648</v>
       </c>
       <c r="C554" s="1" t="n">
         <v>2716</v>
@@ -28980,13 +29198,14 @@
       <c r="H554" s="1" t="n">
         <v>435.3664</v>
       </c>
+      <c r="J554" s="1"/>
     </row>
     <row r="555" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A555" s="1" t="n">
         <v>1775776904.01151</v>
       </c>
       <c r="B555" s="1" t="n">
-        <v>-824</v>
+        <v>-644</v>
       </c>
       <c r="C555" s="1" t="n">
         <v>2703</v>
@@ -29006,13 +29225,14 @@
       <c r="H555" s="1" t="n">
         <v>429.4496</v>
       </c>
+      <c r="J555" s="1"/>
     </row>
     <row r="556" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A556" s="1" t="n">
         <v>1775776904.05914</v>
       </c>
       <c r="B556" s="1" t="n">
-        <v>-821</v>
+        <v>-641</v>
       </c>
       <c r="C556" s="1" t="n">
         <v>2689</v>
@@ -29032,13 +29252,14 @@
       <c r="H556" s="1" t="n">
         <v>435.0912</v>
       </c>
+      <c r="J556" s="1"/>
     </row>
     <row r="557" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A557" s="1" t="n">
         <v>1775776904.26791</v>
       </c>
       <c r="B557" s="1" t="n">
-        <v>-817</v>
+        <v>-637</v>
       </c>
       <c r="C557" s="1" t="n">
         <v>2674</v>
@@ -29058,13 +29279,14 @@
       <c r="H557" s="1" t="n">
         <v>425.9324</v>
       </c>
+      <c r="J557" s="1"/>
     </row>
     <row r="558" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A558" s="1" t="n">
         <v>1775776904.27482</v>
       </c>
       <c r="B558" s="1" t="n">
-        <v>-813</v>
+        <v>-633</v>
       </c>
       <c r="C558" s="1" t="n">
         <v>2659</v>
@@ -29084,13 +29306,14 @@
       <c r="H558" s="1" t="n">
         <v>397.0981</v>
       </c>
+      <c r="J558" s="1"/>
     </row>
     <row r="559" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A559" s="1" t="n">
         <v>1775776904.52534</v>
       </c>
       <c r="B559" s="1" t="n">
-        <v>-808</v>
+        <v>-628</v>
       </c>
       <c r="C559" s="1" t="n">
         <v>2644</v>
@@ -29110,13 +29333,14 @@
       <c r="H559" s="1" t="n">
         <v>379.8993</v>
       </c>
+      <c r="J559" s="1"/>
     </row>
     <row r="560" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A560" s="1" t="n">
         <v>1775776904.52797</v>
       </c>
       <c r="B560" s="1" t="n">
-        <v>-803</v>
+        <v>-623</v>
       </c>
       <c r="C560" s="1" t="n">
         <v>2629</v>
@@ -29136,13 +29360,14 @@
       <c r="H560" s="1" t="n">
         <v>328.9296</v>
       </c>
+      <c r="J560" s="1"/>
     </row>
     <row r="561" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A561" s="1" t="n">
         <v>1775776904.59941</v>
       </c>
       <c r="B561" s="1" t="n">
-        <v>-791</v>
+        <v>-611</v>
       </c>
       <c r="C561" s="1" t="n">
         <v>2613</v>
@@ -29162,13 +29387,14 @@
       <c r="H561" s="1" t="n">
         <v>325.5942</v>
       </c>
+      <c r="J561" s="1"/>
     </row>
     <row r="562" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A562" s="1" t="n">
         <v>1775776904.76286</v>
       </c>
       <c r="B562" s="1" t="n">
-        <v>-783</v>
+        <v>-603</v>
       </c>
       <c r="C562" s="1" t="n">
         <v>2571</v>
@@ -29188,13 +29414,14 @@
       <c r="H562" s="1" t="n">
         <v>336.4464</v>
       </c>
+      <c r="J562" s="1"/>
     </row>
     <row r="563" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A563" s="1" t="n">
         <v>1775776904.81593</v>
       </c>
       <c r="B563" s="1" t="n">
-        <v>-773</v>
+        <v>-593</v>
       </c>
       <c r="C563" s="1" t="n">
         <v>2543</v>
@@ -29214,13 +29441,14 @@
       <c r="H563" s="1" t="n">
         <v>346.8438</v>
       </c>
+      <c r="J563" s="1"/>
     </row>
     <row r="564" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A564" s="1" t="n">
         <v>1775776905.02201</v>
       </c>
       <c r="B564" s="1" t="n">
-        <v>-764</v>
+        <v>-584</v>
       </c>
       <c r="C564" s="1" t="n">
         <v>2511</v>
@@ -29240,13 +29468,14 @@
       <c r="H564" s="1" t="n">
         <v>341.9111</v>
       </c>
+      <c r="J564" s="1"/>
     </row>
     <row r="565" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A565" s="1" t="n">
         <v>1775776905.0316</v>
       </c>
       <c r="B565" s="1" t="n">
-        <v>-757</v>
+        <v>-577</v>
       </c>
       <c r="C565" s="1" t="n">
         <v>2477</v>
@@ -29266,13 +29495,14 @@
       <c r="H565" s="1" t="n">
         <v>335.4573</v>
       </c>
+      <c r="J565" s="1"/>
     </row>
     <row r="566" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A566" s="1" t="n">
         <v>1775776905.27461</v>
       </c>
       <c r="B566" s="1" t="n">
-        <v>-749</v>
+        <v>-569</v>
       </c>
       <c r="C566" s="1" t="n">
         <v>2444</v>
@@ -29292,13 +29522,14 @@
       <c r="H566" s="1" t="n">
         <v>337.0006</v>
       </c>
+      <c r="J566" s="1"/>
     </row>
     <row r="567" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A567" s="1" t="n">
         <v>1775776905.27715</v>
       </c>
       <c r="B567" s="1" t="n">
-        <v>-742</v>
+        <v>-562</v>
       </c>
       <c r="C567" s="1" t="n">
         <v>2411</v>
@@ -29318,13 +29549,14 @@
       <c r="H567" s="1" t="n">
         <v>333.6334</v>
       </c>
+      <c r="J567" s="1"/>
     </row>
     <row r="568" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A568" s="1" t="n">
         <v>1775776905.35633</v>
       </c>
       <c r="B568" s="1" t="n">
-        <v>-736</v>
+        <v>-556</v>
       </c>
       <c r="C568" s="1" t="n">
         <v>2380</v>
@@ -29344,13 +29576,14 @@
       <c r="H568" s="1" t="n">
         <v>329.9856</v>
       </c>
+      <c r="J568" s="1"/>
     </row>
     <row r="569" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A569" s="1" t="n">
         <v>1775776905.53347</v>
       </c>
       <c r="B569" s="1" t="n">
-        <v>-724</v>
+        <v>-544</v>
       </c>
       <c r="C569" s="1" t="n">
         <v>2351</v>
@@ -29370,13 +29603,14 @@
       <c r="H569" s="1" t="n">
         <v>315.2541</v>
       </c>
+      <c r="J569" s="1"/>
     </row>
     <row r="570" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A570" s="1" t="n">
         <v>1775776905.5742</v>
       </c>
       <c r="B570" s="1" t="n">
-        <v>-718</v>
+        <v>-538</v>
       </c>
       <c r="C570" s="1" t="n">
         <v>2324</v>
@@ -29396,13 +29630,14 @@
       <c r="H570" s="1" t="n">
         <v>326.7471</v>
       </c>
+      <c r="J570" s="1"/>
     </row>
     <row r="571" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A571" s="1" t="n">
         <v>1775776905.7809</v>
       </c>
       <c r="B571" s="1" t="n">
-        <v>-711</v>
+        <v>-531</v>
       </c>
       <c r="C571" s="1" t="n">
         <v>2297</v>
@@ -29422,13 +29657,14 @@
       <c r="H571" s="1" t="n">
         <v>322.2383</v>
       </c>
+      <c r="J571" s="1"/>
     </row>
     <row r="572" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A572" s="1" t="n">
         <v>1775776905.79009</v>
       </c>
       <c r="B572" s="1" t="n">
-        <v>-704</v>
+        <v>-524</v>
       </c>
       <c r="C572" s="1" t="n">
         <v>2242</v>
@@ -29448,13 +29684,14 @@
       <c r="H572" s="1" t="n">
         <v>293.3538</v>
       </c>
+      <c r="J572" s="1"/>
     </row>
     <row r="573" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A573" s="1" t="n">
         <v>1775776906.03756</v>
       </c>
       <c r="B573" s="1" t="n">
-        <v>-696</v>
+        <v>-516</v>
       </c>
       <c r="C573" s="1" t="n">
         <v>2212</v>
@@ -29474,13 +29711,14 @@
       <c r="H573" s="1" t="n">
         <v>288.1732</v>
       </c>
+      <c r="J573" s="1"/>
     </row>
     <row r="574" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A574" s="1" t="n">
         <v>1775776906.03984</v>
       </c>
       <c r="B574" s="1" t="n">
-        <v>-689</v>
+        <v>-509</v>
       </c>
       <c r="C574" s="1" t="n">
         <v>2181</v>
@@ -29500,13 +29738,14 @@
       <c r="H574" s="1" t="n">
         <v>252.0825</v>
       </c>
+      <c r="J574" s="1"/>
     </row>
     <row r="575" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A575" s="1" t="n">
         <v>1775776906.11472</v>
       </c>
       <c r="B575" s="1" t="n">
-        <v>-682</v>
+        <v>-502</v>
       </c>
       <c r="C575" s="1" t="n">
         <v>2148</v>
@@ -29526,13 +29765,14 @@
       <c r="H575" s="1" t="n">
         <v>263.0826</v>
       </c>
+      <c r="J575" s="1"/>
     </row>
     <row r="576" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A576" s="1" t="n">
         <v>1775776906.28858</v>
       </c>
       <c r="B576" s="1" t="n">
-        <v>-674</v>
+        <v>-494</v>
       </c>
       <c r="C576" s="1" t="n">
         <v>2115</v>
@@ -29552,13 +29792,14 @@
       <c r="H576" s="1" t="n">
         <v>242.7909</v>
       </c>
+      <c r="J576" s="1"/>
     </row>
     <row r="577" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A577" s="1" t="n">
         <v>1775776906.32996</v>
       </c>
       <c r="B577" s="1" t="n">
-        <v>-669</v>
+        <v>-489</v>
       </c>
       <c r="C577" s="1" t="n">
         <v>2084</v>
@@ -29578,13 +29819,14 @@
       <c r="H577" s="1" t="n">
         <v>227.656</v>
       </c>
+      <c r="J577" s="1"/>
     </row>
     <row r="578" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A578" s="1" t="n">
         <v>1775776906.54586</v>
       </c>
       <c r="B578" s="1" t="n">
-        <v>-658</v>
+        <v>-478</v>
       </c>
       <c r="C578" s="1" t="n">
         <v>2055</v>
@@ -29604,13 +29846,14 @@
       <c r="H578" s="1" t="n">
         <v>219.791</v>
       </c>
+      <c r="J578" s="1"/>
     </row>
     <row r="579" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A579" s="1" t="n">
         <v>1775776906.54836</v>
       </c>
       <c r="B579" s="1" t="n">
-        <v>-652</v>
+        <v>-472</v>
       </c>
       <c r="C579" s="1" t="n">
         <v>2029</v>
@@ -29630,13 +29873,14 @@
       <c r="H579" s="1" t="n">
         <v>153.1783</v>
       </c>
+      <c r="J579" s="1"/>
     </row>
     <row r="580" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A580" s="1" t="n">
         <v>1775776906.80282</v>
       </c>
       <c r="B580" s="1" t="n">
-        <v>-644</v>
+        <v>-464</v>
       </c>
       <c r="C580" s="1" t="n">
         <v>2003</v>
@@ -29656,13 +29900,14 @@
       <c r="H580" s="1" t="n">
         <v>182.3885</v>
       </c>
+      <c r="J580" s="1"/>
     </row>
     <row r="581" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A581" s="1" t="n">
         <v>1775776906.80514</v>
       </c>
       <c r="B581" s="1" t="n">
-        <v>-635</v>
+        <v>-455</v>
       </c>
       <c r="C581" s="1" t="n">
         <v>1975</v>
@@ -29682,13 +29927,14 @@
       <c r="H581" s="1" t="n">
         <v>194.9673</v>
       </c>
+      <c r="J581" s="1"/>
     </row>
     <row r="582" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A582" s="1" t="n">
         <v>1775776906.87152</v>
       </c>
       <c r="B582" s="1" t="n">
-        <v>-622</v>
+        <v>-442</v>
       </c>
       <c r="C582" s="1" t="n">
         <v>1904</v>
@@ -29708,13 +29954,14 @@
       <c r="H582" s="1" t="n">
         <v>196.8406</v>
       </c>
+      <c r="J582" s="1"/>
     </row>
     <row r="583" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A583" s="1" t="n">
         <v>1775776907.04735</v>
       </c>
       <c r="B583" s="1" t="n">
-        <v>-611</v>
+        <v>-431</v>
       </c>
       <c r="C583" s="1" t="n">
         <v>1862</v>
@@ -29734,13 +29981,14 @@
       <c r="H583" s="1" t="n">
         <v>189.994</v>
       </c>
+      <c r="J583" s="1"/>
     </row>
     <row r="584" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A584" s="1" t="n">
         <v>1775776907.08765</v>
       </c>
       <c r="B584" s="1" t="n">
-        <v>-601</v>
+        <v>-421</v>
       </c>
       <c r="C584" s="1" t="n">
         <v>1817</v>
@@ -29760,13 +30008,14 @@
       <c r="H584" s="1" t="n">
         <v>194.535</v>
       </c>
+      <c r="J584" s="1"/>
     </row>
     <row r="585" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A585" s="1" t="n">
         <v>1775776907.30689</v>
       </c>
       <c r="B585" s="1" t="n">
-        <v>-592</v>
+        <v>-412</v>
       </c>
       <c r="C585" s="1" t="n">
         <v>1773</v>
@@ -29786,13 +30035,14 @@
       <c r="H585" s="1" t="n">
         <v>193.2381</v>
       </c>
+      <c r="J585" s="1"/>
     </row>
     <row r="586" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A586" s="1" t="n">
         <v>1775776907.30979</v>
       </c>
       <c r="B586" s="1" t="n">
-        <v>-575</v>
+        <v>-395</v>
       </c>
       <c r="C586" s="1" t="n">
         <v>1728</v>
@@ -29812,13 +30062,14 @@
       <c r="H586" s="1" t="n">
         <v>171.6231</v>
       </c>
+      <c r="J586" s="1"/>
     </row>
     <row r="587" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A587" s="1" t="n">
         <v>1775776907.55948</v>
       </c>
       <c r="B587" s="1" t="n">
-        <v>-566</v>
+        <v>-386</v>
       </c>
       <c r="C587" s="1" t="n">
         <v>1684</v>
@@ -29838,13 +30089,14 @@
       <c r="H587" s="1" t="n">
         <v>172.1995</v>
       </c>
+      <c r="J587" s="1"/>
     </row>
     <row r="588" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A588" s="1" t="n">
         <v>1775776907.56186</v>
       </c>
       <c r="B588" s="1" t="n">
-        <v>-557</v>
+        <v>-377</v>
       </c>
       <c r="C588" s="1" t="n">
         <v>1641</v>
@@ -29864,13 +30116,14 @@
       <c r="H588" s="1" t="n">
         <v>148.9752</v>
       </c>
+      <c r="J588" s="1"/>
     </row>
     <row r="589" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A589" s="1" t="n">
         <v>1775776907.62888</v>
       </c>
       <c r="B589" s="1" t="n">
-        <v>-549</v>
+        <v>-369</v>
       </c>
       <c r="C589" s="1" t="n">
         <v>1600</v>
@@ -29890,13 +30143,14 @@
       <c r="H589" s="1" t="n">
         <v>99.2217</v>
       </c>
+      <c r="J589" s="1"/>
     </row>
     <row r="590" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A590" s="1" t="n">
         <v>1775776907.81424</v>
       </c>
       <c r="B590" s="1" t="n">
-        <v>-539</v>
+        <v>-359</v>
       </c>
       <c r="C590" s="1" t="n">
         <v>1560</v>
@@ -29916,13 +30170,14 @@
       <c r="H590" s="1" t="n">
         <v>130.9843</v>
       </c>
+      <c r="J590" s="1"/>
     </row>
     <row r="591" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A591" s="1" t="n">
         <v>1775776907.84424</v>
       </c>
       <c r="B591" s="1" t="n">
-        <v>-530</v>
+        <v>-350</v>
       </c>
       <c r="C591" s="1" t="n">
         <v>1479</v>
@@ -29942,13 +30197,14 @@
       <c r="H591" s="1" t="n">
         <v>123.2622</v>
       </c>
+      <c r="J591" s="1"/>
     </row>
     <row r="592" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A592" s="1" t="n">
         <v>1775776908.06755</v>
       </c>
       <c r="B592" s="1" t="n">
-        <v>-518</v>
+        <v>-338</v>
       </c>
       <c r="C592" s="1" t="n">
         <v>1435</v>
@@ -29968,13 +30224,14 @@
       <c r="H592" s="1" t="n">
         <v>105.4102</v>
       </c>
+      <c r="J592" s="1"/>
     </row>
     <row r="593" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A593" s="1" t="n">
         <v>1775776908.07006</v>
       </c>
       <c r="B593" s="1" t="n">
-        <v>-507</v>
+        <v>-327</v>
       </c>
       <c r="C593" s="1" t="n">
         <v>1388</v>
@@ -29994,13 +30251,14 @@
       <c r="H593" s="1" t="n">
         <v>72.2256</v>
       </c>
+      <c r="J593" s="1"/>
     </row>
     <row r="594" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A594" s="1" t="n">
         <v>1775776908.31381</v>
       </c>
       <c r="B594" s="1" t="n">
-        <v>-486</v>
+        <v>-306</v>
       </c>
       <c r="C594" s="1" t="n">
         <v>1342</v>
@@ -30020,13 +30278,14 @@
       <c r="H594" s="1" t="n">
         <v>92.3984</v>
       </c>
+      <c r="J594" s="1"/>
     </row>
     <row r="595" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A595" s="1" t="n">
         <v>1775776908.3197</v>
       </c>
       <c r="B595" s="1" t="n">
-        <v>-475</v>
+        <v>-295</v>
       </c>
       <c r="C595" s="1" t="n">
         <v>1296</v>
@@ -30046,13 +30305,14 @@
       <c r="H595" s="1" t="n">
         <v>97.0768</v>
       </c>
+      <c r="J595" s="1"/>
     </row>
     <row r="596" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A596" s="1" t="n">
         <v>1775776908.38574</v>
       </c>
       <c r="B596" s="1" t="n">
-        <v>-463</v>
+        <v>-283</v>
       </c>
       <c r="C596" s="1" t="n">
         <v>1250</v>
@@ -30072,13 +30332,14 @@
       <c r="H596" s="1" t="n">
         <v>82.6484</v>
       </c>
+      <c r="J596" s="1"/>
     </row>
     <row r="597" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A597" s="1" t="n">
         <v>1775776908.56769</v>
       </c>
       <c r="B597" s="1" t="n">
-        <v>-455</v>
+        <v>-275</v>
       </c>
       <c r="C597" s="1" t="n">
         <v>1206</v>
@@ -30098,13 +30359,14 @@
       <c r="H597" s="1" t="n">
         <v>73.2532</v>
       </c>
+      <c r="J597" s="1"/>
     </row>
     <row r="598" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A598" s="1" t="n">
         <v>1775776908.60219</v>
       </c>
       <c r="B598" s="1" t="n">
-        <v>-447</v>
+        <v>-267</v>
       </c>
       <c r="C598" s="1" t="n">
         <v>1164</v>
@@ -30124,13 +30386,14 @@
       <c r="H598" s="1" t="n">
         <v>37.2669</v>
       </c>
+      <c r="J598" s="1"/>
     </row>
     <row r="599" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A599" s="1" t="n">
         <v>1775776908.80716</v>
       </c>
       <c r="B599" s="1" t="n">
-        <v>-436</v>
+        <v>-256</v>
       </c>
       <c r="C599" s="1" t="n">
         <v>1122</v>
@@ -30150,13 +30413,14 @@
       <c r="H599" s="1" t="n">
         <v>43.8954</v>
       </c>
+      <c r="J599" s="1"/>
     </row>
     <row r="600" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A600" s="1" t="n">
         <v>1775776908.81837</v>
       </c>
       <c r="B600" s="1" t="n">
-        <v>-422</v>
+        <v>-242</v>
       </c>
       <c r="C600" s="1" t="n">
         <v>1079</v>
@@ -30176,13 +30440,14 @@
       <c r="H600" s="1" t="n">
         <v>52.7334</v>
       </c>
+      <c r="J600" s="1"/>
     </row>
     <row r="601" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A601" s="1" t="n">
         <v>1775776909.05759</v>
       </c>
       <c r="B601" s="1" t="n">
-        <v>-406</v>
+        <v>-226</v>
       </c>
       <c r="C601" s="1" t="n">
         <v>984</v>
@@ -30202,13 +30467,14 @@
       <c r="H601" s="1" t="n">
         <v>40.4972</v>
       </c>
+      <c r="J601" s="1"/>
     </row>
     <row r="602" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A602" s="1" t="n">
         <v>1775776909.05992</v>
       </c>
       <c r="B602" s="1" t="n">
-        <v>-372</v>
+        <v>-192</v>
       </c>
       <c r="C602" s="1" t="n">
         <v>931</v>
@@ -30228,13 +30494,14 @@
       <c r="H602" s="1" t="n">
         <v>14.098</v>
       </c>
+      <c r="J602" s="1"/>
     </row>
     <row r="603" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A603" s="1" t="n">
         <v>1775776909.14201</v>
       </c>
       <c r="B603" s="1" t="n">
-        <v>-355</v>
+        <v>-175</v>
       </c>
       <c r="C603" s="1" t="n">
         <v>876</v>
@@ -30254,13 +30521,14 @@
       <c r="H603" s="1" t="n">
         <v>14.5432</v>
       </c>
+      <c r="J603" s="1"/>
     </row>
     <row r="604" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A604" s="1" t="n">
         <v>1775776909.3139</v>
       </c>
       <c r="B604" s="1" t="n">
-        <v>-337</v>
+        <v>-157</v>
       </c>
       <c r="C604" s="1" t="n">
         <v>819</v>
@@ -30280,13 +30548,14 @@
       <c r="H604" s="1" t="n">
         <v>33.6984</v>
       </c>
+      <c r="J604" s="1"/>
     </row>
     <row r="605" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A605" s="1" t="n">
         <v>1775776909.3586</v>
       </c>
       <c r="B605" s="1" t="n">
-        <v>-317</v>
+        <v>-137</v>
       </c>
       <c r="C605" s="1" t="n">
         <v>761</v>
@@ -30306,13 +30575,14 @@
       <c r="H605" s="1" t="n">
         <v>23.648</v>
       </c>
+      <c r="J605" s="1"/>
     </row>
     <row r="606" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A606" s="1" t="n">
         <v>1775776909.57934</v>
       </c>
       <c r="B606" s="1" t="n">
-        <v>-301</v>
+        <v>-121</v>
       </c>
       <c r="C606" s="1" t="n">
         <v>702</v>
@@ -30332,13 +30602,14 @@
       <c r="H606" s="1" t="n">
         <v>24.1892</v>
       </c>
+      <c r="J606" s="1"/>
     </row>
     <row r="607" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A607" s="1" t="n">
         <v>1775776909.58184</v>
       </c>
       <c r="B607" s="1" t="n">
-        <v>-287</v>
+        <v>-107</v>
       </c>
       <c r="C607" s="1" t="n">
         <v>644</v>
@@ -30358,13 +30629,14 @@
       <c r="H607" s="1" t="n">
         <v>13.9496</v>
       </c>
+      <c r="J607" s="1"/>
     </row>
     <row r="608" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A608" s="1" t="n">
         <v>1775776909.81952</v>
       </c>
       <c r="B608" s="1" t="n">
-        <v>-271</v>
+        <v>-91</v>
       </c>
       <c r="C608" s="1" t="n">
         <v>588</v>
@@ -30384,13 +30656,14 @@
       <c r="H608" s="1" t="n">
         <v>22.4084</v>
       </c>
+      <c r="J608" s="1"/>
     </row>
     <row r="609" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A609" s="1" t="n">
         <v>1775776909.822</v>
       </c>
       <c r="B609" s="1" t="n">
-        <v>-254</v>
+        <v>-74</v>
       </c>
       <c r="C609" s="1" t="n">
         <v>534</v>
@@ -30410,13 +30683,14 @@
       <c r="H609" s="1" t="n">
         <v>26.3553</v>
       </c>
+      <c r="J609" s="1"/>
     </row>
     <row r="610" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A610" s="1" t="n">
         <v>1775776909.89966</v>
       </c>
       <c r="B610" s="1" t="n">
-        <v>-236</v>
+        <v>-56</v>
       </c>
       <c r="C610" s="1" t="n">
         <v>483</v>
@@ -30436,13 +30710,14 @@
       <c r="H610" s="1" t="n">
         <v>27.8992</v>
       </c>
+      <c r="J610" s="1"/>
     </row>
     <row r="611" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A611" s="1" t="n">
         <v>1775776910.07744</v>
       </c>
       <c r="B611" s="1" t="n">
-        <v>-209</v>
+        <v>-29</v>
       </c>
       <c r="C611" s="1" t="n">
         <v>391</v>
@@ -30462,13 +30737,14 @@
       <c r="H611" s="1" t="n">
         <v>28.938</v>
       </c>
+      <c r="J611" s="1"/>
     </row>
     <row r="612" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A612" s="1" t="n">
         <v>1775776910.11701</v>
       </c>
       <c r="B612" s="1" t="n">
-        <v>-199</v>
+        <v>-19</v>
       </c>
       <c r="C612" s="1" t="n">
         <v>345</v>
@@ -30488,13 +30764,14 @@
       <c r="H612" s="1" t="n">
         <v>29.0864</v>
       </c>
+      <c r="J612" s="1"/>
     </row>
     <row r="613" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A613" s="1" t="n">
         <v>1775776910.32797</v>
       </c>
       <c r="B613" s="1" t="n">
-        <v>-190</v>
+        <v>-10</v>
       </c>
       <c r="C613" s="1" t="n">
         <v>301</v>
@@ -30514,13 +30791,14 @@
       <c r="H613" s="1" t="n">
         <v>28.7896</v>
       </c>
+      <c r="J613" s="1"/>
     </row>
     <row r="614" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A614" s="1" t="n">
         <v>1775776910.33305</v>
       </c>
       <c r="B614" s="1" t="n">
-        <v>-181</v>
+        <v>-1</v>
       </c>
       <c r="C614" s="1" t="n">
         <v>257</v>
@@ -30540,13 +30818,14 @@
       <c r="H614" s="1" t="n">
         <v>29.8284</v>
       </c>
+      <c r="J614" s="1"/>
     </row>
     <row r="615" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A615" s="1" t="n">
         <v>1775776910.58409</v>
       </c>
       <c r="B615" s="1" t="n">
-        <v>-177</v>
+        <v>3</v>
       </c>
       <c r="C615" s="1" t="n">
         <v>216</v>
@@ -30566,13 +30845,14 @@
       <c r="H615" s="1" t="n">
         <v>28.938</v>
       </c>
+      <c r="J615" s="1"/>
     </row>
     <row r="616" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A616" s="1" t="n">
         <v>1775776910.59144</v>
       </c>
       <c r="B616" s="1" t="n">
-        <v>-173</v>
+        <v>7</v>
       </c>
       <c r="C616" s="1" t="n">
         <v>180</v>
@@ -30592,13 +30872,14 @@
       <c r="H616" s="1" t="n">
         <v>28.2555</v>
       </c>
+      <c r="J616" s="1"/>
     </row>
     <row r="617" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A617" s="1" t="n">
         <v>1775776910.6575</v>
       </c>
       <c r="B617" s="1" t="n">
-        <v>-171</v>
+        <v>9</v>
       </c>
       <c r="C617" s="1" t="n">
         <v>149</v>
@@ -30618,13 +30899,14 @@
       <c r="H617" s="1" t="n">
         <v>28.7896</v>
       </c>
+      <c r="J617" s="1"/>
     </row>
     <row r="618" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A618" s="1" t="n">
         <v>1775776910.84939</v>
       </c>
       <c r="B618" s="1" t="n">
-        <v>-168</v>
+        <v>12</v>
       </c>
       <c r="C618" s="1" t="n">
         <v>120</v>
@@ -30644,13 +30926,14 @@
       <c r="H618" s="1" t="n">
         <v>28.291</v>
       </c>
+      <c r="J618" s="1"/>
     </row>
     <row r="619" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A619" s="1" t="n">
         <v>1775776910.87368</v>
       </c>
       <c r="B619" s="1" t="n">
-        <v>-167</v>
+        <v>13</v>
       </c>
       <c r="C619" s="1" t="n">
         <v>93</v>
@@ -30670,13 +30953,14 @@
       <c r="H619" s="1" t="n">
         <v>28.7377</v>
       </c>
+      <c r="J619" s="1"/>
     </row>
     <row r="620" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A620" s="1" t="n">
         <v>1775776911.10889</v>
       </c>
       <c r="B620" s="1" t="n">
-        <v>-171</v>
+        <v>9</v>
       </c>
       <c r="C620" s="1" t="n">
         <v>71</v>
@@ -30696,13 +30980,14 @@
       <c r="H620" s="1" t="n">
         <v>28.0476</v>
       </c>
+      <c r="J620" s="1"/>
     </row>
     <row r="621" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A621" s="1" t="n">
         <v>1775776911.11132</v>
       </c>
       <c r="B621" s="1" t="n">
-        <v>-175</v>
+        <v>5</v>
       </c>
       <c r="C621" s="1" t="n">
         <v>38</v>
@@ -30722,13 +31007,14 @@
       <c r="H621" s="1" t="n">
         <v>28.5888</v>
       </c>
+      <c r="J621" s="1"/>
     </row>
     <row r="622" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A622" s="1" t="n">
         <v>1775776911.19801</v>
       </c>
       <c r="B622" s="1" t="n">
-        <v>-177</v>
+        <v>3</v>
       </c>
       <c r="C622" s="1" t="n">
         <v>25</v>
@@ -30748,13 +31034,14 @@
       <c r="H622" s="1" t="n">
         <v>29.0355</v>
       </c>
+      <c r="J622" s="1"/>
     </row>
     <row r="623" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A623" s="1" t="n">
         <v>1775776911.38044</v>
       </c>
       <c r="B623" s="1" t="n">
-        <v>-179</v>
+        <v>1</v>
       </c>
       <c r="C623" s="1" t="n">
         <v>14</v>
@@ -30774,13 +31061,14 @@
       <c r="H623" s="1" t="n">
         <v>26.802</v>
       </c>
+      <c r="J623" s="1"/>
     </row>
     <row r="624" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A624" s="1" t="n">
         <v>1775776911.4141</v>
       </c>
       <c r="B624" s="1" t="n">
-        <v>-182</v>
+        <v>-2</v>
       </c>
       <c r="C624" s="1" t="n">
         <v>4</v>
@@ -30800,13 +31088,14 @@
       <c r="H624" s="1" t="n">
         <v>27.0088</v>
       </c>
+      <c r="J624" s="1"/>
     </row>
     <row r="625" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A625" s="1" t="n">
         <v>1775776911.62309</v>
       </c>
       <c r="B625" s="1" t="n">
-        <v>-191</v>
+        <v>-11</v>
       </c>
       <c r="C625" s="1" t="n">
         <v>-6</v>
@@ -30826,13 +31115,14 @@
       <c r="H625" s="1" t="n">
         <v>27.3976</v>
       </c>
+      <c r="J625" s="1"/>
     </row>
     <row r="626" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A626" s="1" t="n">
         <v>1775776911.6316</v>
       </c>
       <c r="B626" s="1" t="n">
-        <v>-198</v>
+        <v>-18</v>
       </c>
       <c r="C626" s="1" t="n">
         <v>-12</v>
@@ -30852,13 +31142,14 @@
       <c r="H626" s="1" t="n">
         <v>26.5042</v>
       </c>
+      <c r="J626" s="1"/>
     </row>
     <row r="627" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A627" s="1" t="n">
         <v>1775776911.87774</v>
       </c>
       <c r="B627" s="1" t="n">
-        <v>-203</v>
+        <v>-23</v>
       </c>
       <c r="C627" s="1" t="n">
         <v>-17</v>
@@ -30878,13 +31169,14 @@
       <c r="H627" s="1" t="n">
         <v>27.8443</v>
       </c>
+      <c r="J627" s="1"/>
     </row>
     <row r="628" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A628" s="1" t="n">
         <v>1775776911.88024</v>
       </c>
       <c r="B628" s="1" t="n">
-        <v>-204</v>
+        <v>-24</v>
       </c>
       <c r="C628" s="1" t="n">
         <v>-19</v>
@@ -30904,13 +31196,14 @@
       <c r="H628" s="1" t="n">
         <v>27.0998</v>
       </c>
+      <c r="J628" s="1"/>
     </row>
     <row r="629" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A629" s="1" t="n">
         <v>1775776911.95639</v>
       </c>
       <c r="B629" s="1" t="n">
-        <v>-205</v>
+        <v>-25</v>
       </c>
       <c r="C629" s="1" t="n">
         <v>-20</v>
@@ -30930,13 +31223,14 @@
       <c r="H629" s="1" t="n">
         <v>26.802</v>
       </c>
+      <c r="J629" s="1"/>
     </row>
     <row r="630" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A630" s="1" t="n">
         <v>1775776912.13984</v>
       </c>
       <c r="B630" s="1" t="n">
-        <v>-206</v>
+        <v>-26</v>
       </c>
       <c r="C630" s="1" t="n">
         <v>-21</v>
@@ -30956,13 +31250,14 @@
       <c r="H630" s="1" t="n">
         <v>27.209</v>
       </c>
+      <c r="J630" s="1"/>
     </row>
     <row r="631" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A631" s="1" t="n">
         <v>1775776912.1716</v>
       </c>
       <c r="B631" s="1" t="n">
-        <v>-207</v>
+        <v>-27</v>
       </c>
       <c r="C631" s="1" t="n">
         <v>-21</v>
@@ -30982,13 +31277,14 @@
       <c r="H631" s="1" t="n">
         <v>28.5888</v>
       </c>
+      <c r="J631" s="1"/>
     </row>
     <row r="632" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A632" s="1" t="n">
         <v>1775776912.3887</v>
       </c>
       <c r="B632" s="1" t="n">
-        <v>-208</v>
+        <v>-28</v>
       </c>
       <c r="C632" s="1" t="n">
         <v>-22</v>
@@ -31008,13 +31304,14 @@
       <c r="H632" s="1" t="n">
         <v>27.6954</v>
       </c>
+      <c r="J632" s="1"/>
     </row>
     <row r="633" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A633" s="1" t="n">
         <v>1775776912.39195</v>
       </c>
       <c r="B633" s="1" t="n">
-        <v>-208</v>
+        <v>-28</v>
       </c>
       <c r="C633" s="1" t="n">
         <v>-22</v>
@@ -31034,13 +31331,14 @@
       <c r="H633" s="1" t="n">
         <v>27.0998</v>
       </c>
+      <c r="J633" s="1"/>
     </row>
     <row r="634" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A634" s="1" t="n">
         <v>1775776912.64263</v>
       </c>
       <c r="B634" s="1" t="n">
-        <v>-209</v>
+        <v>-29</v>
       </c>
       <c r="C634" s="1" t="n">
         <v>-22</v>
@@ -31060,13 +31358,14 @@
       <c r="H634" s="1" t="n">
         <v>27.3976</v>
       </c>
+      <c r="J634" s="1"/>
     </row>
     <row r="635" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A635" s="1" t="n">
         <v>1775776912.64996</v>
       </c>
       <c r="B635" s="1" t="n">
-        <v>-210</v>
+        <v>-30</v>
       </c>
       <c r="C635" s="1" t="n">
         <v>-22</v>
@@ -31086,13 +31385,14 @@
       <c r="H635" s="1" t="n">
         <v>27.9932</v>
       </c>
+      <c r="J635" s="1"/>
     </row>
     <row r="636" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A636" s="1" t="n">
         <v>1775776912.71234</v>
       </c>
       <c r="B636" s="1" t="n">
-        <v>-211</v>
+        <v>-31</v>
       </c>
       <c r="C636" s="1" t="n">
         <v>-23</v>
@@ -31112,13 +31412,14 @@
       <c r="H636" s="1" t="n">
         <v>28.291</v>
       </c>
+      <c r="J636" s="1"/>
     </row>
     <row r="637" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A637" s="1" t="n">
         <v>1775776912.90049</v>
       </c>
       <c r="B637" s="1" t="n">
-        <v>-211</v>
+        <v>-31</v>
       </c>
       <c r="C637" s="1" t="n">
         <v>-23</v>
@@ -31138,13 +31439,14 @@
       <c r="H637" s="1" t="n">
         <v>28.1421</v>
       </c>
+      <c r="J637" s="1"/>
     </row>
     <row r="638" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A638" s="1" t="n">
         <v>1775776912.92819</v>
       </c>
       <c r="B638" s="1" t="n">
-        <v>-212</v>
+        <v>-32</v>
       </c>
       <c r="C638" s="1" t="n">
         <v>-23</v>
@@ -31164,13 +31466,14 @@
       <c r="H638" s="1" t="n">
         <v>28.8866</v>
       </c>
+      <c r="J638" s="1"/>
     </row>
     <row r="639" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A639" s="1" t="n">
         <v>1775776913.15299</v>
       </c>
       <c r="B639" s="1" t="n">
-        <v>-212</v>
+        <v>-32</v>
       </c>
       <c r="C639" s="1" t="n">
         <v>-23</v>
@@ -31190,13 +31493,14 @@
       <c r="H639" s="1" t="n">
         <v>28.1421</v>
       </c>
+      <c r="J639" s="1"/>
     </row>
     <row r="640" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A640" s="1" t="n">
         <v>1775776913.15576</v>
       </c>
       <c r="B640" s="1" t="n">
-        <v>-213</v>
+        <v>-33</v>
       </c>
       <c r="C640" s="1" t="n">
         <v>-23</v>
@@ -31216,13 +31520,14 @@
       <c r="H640" s="1" t="n">
         <v>27.5465</v>
       </c>
+      <c r="J640" s="1"/>
     </row>
     <row r="641" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A641" s="1" t="n">
         <v>1775776913.39766</v>
       </c>
       <c r="B641" s="1" t="n">
-        <v>-214</v>
+        <v>-34</v>
       </c>
       <c r="C641" s="1" t="n">
         <v>-23</v>
@@ -31242,13 +31547,14 @@
       <c r="H641" s="1" t="n">
         <v>27.508</v>
       </c>
+      <c r="J641" s="1"/>
     </row>
     <row r="642" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A642" s="1" t="n">
         <v>1775776913.40253</v>
       </c>
       <c r="B642" s="1" t="n">
-        <v>-214</v>
+        <v>-34</v>
       </c>
       <c r="C642" s="1" t="n">
         <v>-23</v>
@@ -31268,13 +31574,14 @@
       <c r="H642" s="1" t="n">
         <v>28.5888</v>
       </c>
+      <c r="J642" s="1"/>
     </row>
     <row r="643" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A643" s="1" t="n">
         <v>1775776913.47082</v>
       </c>
       <c r="B643" s="1" t="n">
-        <v>-215</v>
+        <v>-35</v>
       </c>
       <c r="C643" s="1" t="n">
         <v>-22</v>
@@ -31294,13 +31601,14 @@
       <c r="H643" s="1" t="n">
         <v>28.291</v>
       </c>
+      <c r="J643" s="1"/>
     </row>
     <row r="644" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A644" s="1" t="n">
         <v>1775776913.66381</v>
       </c>
       <c r="B644" s="1" t="n">
-        <v>-216</v>
+        <v>-36</v>
       </c>
       <c r="C644" s="1" t="n">
         <v>-22</v>
@@ -31320,13 +31628,14 @@
       <c r="H644" s="1" t="n">
         <v>28.1421</v>
       </c>
+      <c r="J644" s="1"/>
     </row>
     <row r="645" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A645" s="1" t="n">
         <v>1775776913.68584</v>
       </c>
       <c r="B645" s="1" t="n">
-        <v>-217</v>
+        <v>-37</v>
       </c>
       <c r="C645" s="1" t="n">
         <v>-23</v>
@@ -31346,13 +31655,14 @@
       <c r="H645" s="1" t="n">
         <v>27.9932</v>
       </c>
+      <c r="J645" s="1"/>
     </row>
     <row r="646" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A646" s="1" t="n">
         <v>1775776913.91957</v>
       </c>
       <c r="B646" s="1" t="n">
-        <v>-217</v>
+        <v>-37</v>
       </c>
       <c r="C646" s="1" t="n">
         <v>-22</v>
@@ -31372,13 +31682,14 @@
       <c r="H646" s="1" t="n">
         <v>29.1844</v>
       </c>
+      <c r="J646" s="1"/>
     </row>
     <row r="647" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A647" s="1" t="n">
         <v>1775776913.92357</v>
       </c>
       <c r="B647" s="1" t="n">
-        <v>-218</v>
+        <v>-38</v>
       </c>
       <c r="C647" s="1" t="n">
         <v>-22</v>
@@ -31398,13 +31709,14 @@
       <c r="H647" s="1" t="n">
         <v>27.3976</v>
       </c>
+      <c r="J647" s="1"/>
     </row>
     <row r="648" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A648" s="1" t="n">
         <v>1775776914.01053</v>
       </c>
       <c r="B648" s="1" t="n">
-        <v>-219</v>
+        <v>-39</v>
       </c>
       <c r="C648" s="1" t="n">
         <v>-22</v>
@@ -31424,13 +31736,14 @@
       <c r="H648" s="1" t="n">
         <v>28.106</v>
       </c>
+      <c r="J648" s="1"/>
     </row>
     <row r="649" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A649" s="1" t="n">
         <v>1775776914.17068</v>
       </c>
       <c r="B649" s="1" t="n">
-        <v>-219</v>
+        <v>-39</v>
       </c>
       <c r="C649" s="1" t="n">
         <v>-22</v>
@@ -31450,13 +31763,14 @@
       <c r="H649" s="1" t="n">
         <v>28.5888</v>
       </c>
+      <c r="J649" s="1"/>
     </row>
     <row r="650" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A650" s="1" t="n">
         <v>1775776914.22586</v>
       </c>
       <c r="B650" s="1" t="n">
-        <v>-220</v>
+        <v>-40</v>
       </c>
       <c r="C650" s="1" t="n">
         <v>-22</v>
@@ -31476,13 +31790,14 @@
       <c r="H650" s="1" t="n">
         <v>28.7377</v>
       </c>
+      <c r="J650" s="1"/>
     </row>
     <row r="651" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A651" s="1" t="n">
         <v>1775776914.42788</v>
       </c>
       <c r="B651" s="1" t="n">
-        <v>-220</v>
+        <v>-40</v>
       </c>
       <c r="C651" s="1" t="n">
         <v>-22</v>
@@ -31502,13 +31817,14 @@
       <c r="H651" s="1" t="n">
         <v>28.4399</v>
       </c>
+      <c r="J651" s="1"/>
     </row>
     <row r="652" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A652" s="1" t="n">
         <v>1775776914.44249</v>
       </c>
       <c r="B652" s="1" t="n">
-        <v>-221</v>
+        <v>-41</v>
       </c>
       <c r="C652" s="1" t="n">
         <v>-22</v>
@@ -31528,13 +31844,14 @@
       <c r="H652" s="1" t="n">
         <v>28.8535</v>
       </c>
+      <c r="J652" s="1"/>
     </row>
     <row r="653" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A653" s="1" t="n">
         <v>1775776914.70415</v>
       </c>
       <c r="B653" s="1" t="n">
-        <v>-222</v>
+        <v>-42</v>
       </c>
       <c r="C653" s="1" t="n">
         <v>-22</v>
@@ -31554,13 +31871,14 @@
       <c r="H653" s="1" t="n">
         <v>29.1525</v>
       </c>
+      <c r="J653" s="1"/>
     </row>
     <row r="654" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A654" s="1" t="n">
         <v>1775776914.71247</v>
       </c>
       <c r="B654" s="1" t="n">
-        <v>-222</v>
+        <v>-42</v>
       </c>
       <c r="C654" s="1" t="n">
         <v>-22</v>
@@ -31580,1406 +31898,7 @@
       <c r="H654" s="1" t="n">
         <v>27.807</v>
       </c>
-    </row>
-    <row r="655" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A655" s="0"/>
-      <c r="B655" s="0"/>
-      <c r="C655" s="0"/>
-      <c r="D655" s="0"/>
-      <c r="E655" s="0"/>
-      <c r="F655" s="0"/>
-      <c r="G655" s="0"/>
-      <c r="H655" s="0"/>
-    </row>
-    <row r="656" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A656" s="0"/>
-      <c r="B656" s="0"/>
-      <c r="C656" s="0"/>
-      <c r="D656" s="0"/>
-      <c r="E656" s="0"/>
-      <c r="F656" s="0"/>
-      <c r="G656" s="0"/>
-      <c r="H656" s="0"/>
-    </row>
-    <row r="657" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A657" s="0"/>
-      <c r="B657" s="0"/>
-      <c r="C657" s="0"/>
-      <c r="D657" s="0"/>
-      <c r="E657" s="0"/>
-      <c r="F657" s="0"/>
-      <c r="G657" s="0"/>
-      <c r="H657" s="0"/>
-    </row>
-    <row r="658" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A658" s="0"/>
-      <c r="B658" s="0"/>
-      <c r="C658" s="0"/>
-      <c r="D658" s="0"/>
-      <c r="E658" s="0"/>
-      <c r="F658" s="0"/>
-      <c r="G658" s="0"/>
-      <c r="H658" s="0"/>
-    </row>
-    <row r="659" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A659" s="0"/>
-      <c r="B659" s="0"/>
-      <c r="C659" s="0"/>
-      <c r="D659" s="0"/>
-      <c r="E659" s="0"/>
-      <c r="F659" s="0"/>
-      <c r="G659" s="0"/>
-      <c r="H659" s="0"/>
-    </row>
-    <row r="660" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A660" s="0"/>
-      <c r="B660" s="0"/>
-      <c r="C660" s="0"/>
-      <c r="D660" s="0"/>
-      <c r="E660" s="0"/>
-      <c r="F660" s="0"/>
-      <c r="G660" s="0"/>
-      <c r="H660" s="0"/>
-    </row>
-    <row r="661" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A661" s="0"/>
-      <c r="B661" s="0"/>
-      <c r="C661" s="0"/>
-      <c r="D661" s="0"/>
-      <c r="E661" s="0"/>
-      <c r="F661" s="0"/>
-      <c r="G661" s="0"/>
-      <c r="H661" s="0"/>
-    </row>
-    <row r="662" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A662" s="0"/>
-      <c r="B662" s="0"/>
-      <c r="C662" s="0"/>
-      <c r="D662" s="0"/>
-      <c r="E662" s="0"/>
-      <c r="F662" s="0"/>
-      <c r="G662" s="0"/>
-      <c r="H662" s="0"/>
-    </row>
-    <row r="663" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A663" s="0"/>
-      <c r="B663" s="0"/>
-      <c r="C663" s="0"/>
-      <c r="D663" s="0"/>
-      <c r="E663" s="0"/>
-      <c r="F663" s="0"/>
-      <c r="G663" s="0"/>
-      <c r="H663" s="0"/>
-    </row>
-    <row r="664" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A664" s="0"/>
-      <c r="B664" s="0"/>
-      <c r="C664" s="0"/>
-      <c r="D664" s="0"/>
-      <c r="E664" s="0"/>
-      <c r="F664" s="0"/>
-      <c r="G664" s="0"/>
-      <c r="H664" s="0"/>
-    </row>
-    <row r="665" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A665" s="0"/>
-      <c r="B665" s="0"/>
-      <c r="C665" s="0"/>
-      <c r="D665" s="0"/>
-      <c r="E665" s="0"/>
-      <c r="F665" s="0"/>
-      <c r="G665" s="0"/>
-      <c r="H665" s="0"/>
-    </row>
-    <row r="666" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A666" s="0"/>
-      <c r="B666" s="0"/>
-      <c r="C666" s="0"/>
-      <c r="D666" s="0"/>
-      <c r="E666" s="0"/>
-      <c r="F666" s="0"/>
-      <c r="G666" s="0"/>
-      <c r="H666" s="0"/>
-    </row>
-    <row r="667" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A667" s="0"/>
-      <c r="B667" s="0"/>
-      <c r="C667" s="0"/>
-      <c r="D667" s="0"/>
-      <c r="E667" s="0"/>
-      <c r="F667" s="0"/>
-      <c r="G667" s="0"/>
-      <c r="H667" s="0"/>
-    </row>
-    <row r="668" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A668" s="0"/>
-      <c r="B668" s="0"/>
-      <c r="C668" s="0"/>
-      <c r="D668" s="0"/>
-      <c r="E668" s="0"/>
-      <c r="F668" s="0"/>
-      <c r="G668" s="0"/>
-      <c r="H668" s="0"/>
-    </row>
-    <row r="669" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A669" s="0"/>
-      <c r="B669" s="0"/>
-      <c r="C669" s="0"/>
-      <c r="D669" s="0"/>
-      <c r="E669" s="0"/>
-      <c r="F669" s="0"/>
-      <c r="G669" s="0"/>
-      <c r="H669" s="0"/>
-    </row>
-    <row r="670" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A670" s="0"/>
-      <c r="B670" s="0"/>
-      <c r="C670" s="0"/>
-      <c r="D670" s="0"/>
-      <c r="E670" s="0"/>
-      <c r="F670" s="0"/>
-      <c r="G670" s="0"/>
-      <c r="H670" s="0"/>
-    </row>
-    <row r="671" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A671" s="0"/>
-      <c r="B671" s="0"/>
-      <c r="C671" s="0"/>
-      <c r="D671" s="0"/>
-      <c r="E671" s="0"/>
-      <c r="F671" s="0"/>
-      <c r="G671" s="0"/>
-      <c r="H671" s="0"/>
-    </row>
-    <row r="672" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A672" s="0"/>
-      <c r="B672" s="0"/>
-      <c r="C672" s="0"/>
-      <c r="D672" s="0"/>
-      <c r="E672" s="0"/>
-      <c r="F672" s="0"/>
-      <c r="G672" s="0"/>
-      <c r="H672" s="0"/>
-    </row>
-    <row r="673" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A673" s="0"/>
-      <c r="B673" s="0"/>
-      <c r="C673" s="0"/>
-      <c r="D673" s="0"/>
-      <c r="E673" s="0"/>
-      <c r="F673" s="0"/>
-      <c r="G673" s="0"/>
-      <c r="H673" s="0"/>
-    </row>
-    <row r="674" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A674" s="0"/>
-      <c r="B674" s="0"/>
-      <c r="C674" s="0"/>
-      <c r="D674" s="0"/>
-      <c r="E674" s="0"/>
-      <c r="F674" s="0"/>
-      <c r="G674" s="0"/>
-      <c r="H674" s="0"/>
-    </row>
-    <row r="675" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A675" s="0"/>
-      <c r="B675" s="0"/>
-      <c r="C675" s="0"/>
-      <c r="D675" s="0"/>
-      <c r="E675" s="0"/>
-      <c r="F675" s="0"/>
-      <c r="G675" s="0"/>
-      <c r="H675" s="0"/>
-    </row>
-    <row r="676" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A676" s="0"/>
-      <c r="B676" s="0"/>
-      <c r="C676" s="0"/>
-      <c r="D676" s="0"/>
-      <c r="E676" s="0"/>
-      <c r="F676" s="0"/>
-      <c r="G676" s="0"/>
-      <c r="H676" s="0"/>
-    </row>
-    <row r="677" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A677" s="0"/>
-      <c r="B677" s="0"/>
-      <c r="C677" s="0"/>
-      <c r="D677" s="0"/>
-      <c r="E677" s="0"/>
-      <c r="F677" s="0"/>
-      <c r="G677" s="0"/>
-      <c r="H677" s="0"/>
-    </row>
-    <row r="678" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A678" s="0"/>
-      <c r="B678" s="0"/>
-      <c r="C678" s="0"/>
-      <c r="D678" s="0"/>
-      <c r="E678" s="0"/>
-      <c r="F678" s="0"/>
-      <c r="G678" s="0"/>
-      <c r="H678" s="0"/>
-    </row>
-    <row r="679" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A679" s="0"/>
-      <c r="B679" s="0"/>
-      <c r="C679" s="0"/>
-      <c r="D679" s="0"/>
-      <c r="E679" s="0"/>
-      <c r="F679" s="0"/>
-      <c r="G679" s="0"/>
-      <c r="H679" s="0"/>
-    </row>
-    <row r="680" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A680" s="0"/>
-      <c r="B680" s="0"/>
-      <c r="C680" s="0"/>
-      <c r="D680" s="0"/>
-      <c r="E680" s="0"/>
-      <c r="F680" s="0"/>
-      <c r="G680" s="0"/>
-      <c r="H680" s="0"/>
-    </row>
-    <row r="681" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A681" s="0"/>
-      <c r="B681" s="0"/>
-      <c r="C681" s="0"/>
-      <c r="D681" s="0"/>
-      <c r="E681" s="0"/>
-      <c r="F681" s="0"/>
-      <c r="G681" s="0"/>
-      <c r="H681" s="0"/>
-    </row>
-    <row r="682" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A682" s="0"/>
-      <c r="B682" s="0"/>
-      <c r="C682" s="0"/>
-      <c r="D682" s="0"/>
-      <c r="E682" s="0"/>
-      <c r="F682" s="0"/>
-      <c r="G682" s="0"/>
-      <c r="H682" s="0"/>
-    </row>
-    <row r="683" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A683" s="0"/>
-      <c r="B683" s="0"/>
-      <c r="C683" s="0"/>
-      <c r="D683" s="0"/>
-      <c r="E683" s="0"/>
-      <c r="F683" s="0"/>
-      <c r="G683" s="0"/>
-      <c r="H683" s="0"/>
-    </row>
-    <row r="684" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A684" s="0"/>
-      <c r="B684" s="0"/>
-      <c r="C684" s="0"/>
-      <c r="D684" s="0"/>
-      <c r="E684" s="0"/>
-      <c r="F684" s="0"/>
-      <c r="G684" s="0"/>
-      <c r="H684" s="0"/>
-    </row>
-    <row r="685" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A685" s="0"/>
-      <c r="B685" s="0"/>
-      <c r="C685" s="0"/>
-      <c r="D685" s="0"/>
-      <c r="E685" s="0"/>
-      <c r="F685" s="0"/>
-      <c r="G685" s="0"/>
-      <c r="H685" s="0"/>
-    </row>
-    <row r="686" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A686" s="0"/>
-      <c r="B686" s="0"/>
-      <c r="C686" s="0"/>
-      <c r="D686" s="0"/>
-      <c r="E686" s="0"/>
-      <c r="F686" s="0"/>
-      <c r="G686" s="0"/>
-      <c r="H686" s="0"/>
-    </row>
-    <row r="687" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A687" s="0"/>
-      <c r="B687" s="0"/>
-      <c r="C687" s="0"/>
-      <c r="D687" s="0"/>
-      <c r="E687" s="0"/>
-      <c r="F687" s="0"/>
-      <c r="G687" s="0"/>
-      <c r="H687" s="0"/>
-    </row>
-    <row r="688" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A688" s="0"/>
-      <c r="B688" s="0"/>
-      <c r="C688" s="0"/>
-      <c r="D688" s="0"/>
-      <c r="E688" s="0"/>
-      <c r="F688" s="0"/>
-      <c r="G688" s="0"/>
-      <c r="H688" s="0"/>
-    </row>
-    <row r="689" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A689" s="0"/>
-      <c r="B689" s="0"/>
-      <c r="C689" s="0"/>
-      <c r="D689" s="0"/>
-      <c r="E689" s="0"/>
-      <c r="F689" s="0"/>
-      <c r="G689" s="0"/>
-      <c r="H689" s="0"/>
-    </row>
-    <row r="690" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A690" s="0"/>
-      <c r="B690" s="0"/>
-      <c r="C690" s="0"/>
-      <c r="D690" s="0"/>
-      <c r="E690" s="0"/>
-      <c r="F690" s="0"/>
-      <c r="G690" s="0"/>
-      <c r="H690" s="0"/>
-    </row>
-    <row r="691" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A691" s="0"/>
-      <c r="B691" s="0"/>
-      <c r="C691" s="0"/>
-      <c r="D691" s="0"/>
-      <c r="E691" s="0"/>
-      <c r="F691" s="0"/>
-      <c r="G691" s="0"/>
-      <c r="H691" s="0"/>
-    </row>
-    <row r="692" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A692" s="0"/>
-      <c r="B692" s="0"/>
-      <c r="C692" s="0"/>
-      <c r="D692" s="0"/>
-      <c r="E692" s="0"/>
-      <c r="F692" s="0"/>
-      <c r="G692" s="0"/>
-      <c r="H692" s="0"/>
-    </row>
-    <row r="693" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A693" s="0"/>
-      <c r="B693" s="0"/>
-      <c r="C693" s="0"/>
-      <c r="D693" s="0"/>
-      <c r="E693" s="0"/>
-      <c r="F693" s="0"/>
-      <c r="G693" s="0"/>
-      <c r="H693" s="0"/>
-    </row>
-    <row r="694" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A694" s="0"/>
-      <c r="B694" s="0"/>
-      <c r="C694" s="0"/>
-      <c r="D694" s="0"/>
-      <c r="E694" s="0"/>
-      <c r="F694" s="0"/>
-      <c r="G694" s="0"/>
-      <c r="H694" s="0"/>
-    </row>
-    <row r="695" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A695" s="0"/>
-      <c r="B695" s="0"/>
-      <c r="C695" s="0"/>
-      <c r="D695" s="0"/>
-      <c r="E695" s="0"/>
-      <c r="F695" s="0"/>
-      <c r="G695" s="0"/>
-      <c r="H695" s="0"/>
-    </row>
-    <row r="696" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A696" s="0"/>
-      <c r="B696" s="0"/>
-      <c r="C696" s="0"/>
-      <c r="D696" s="0"/>
-      <c r="E696" s="0"/>
-      <c r="F696" s="0"/>
-      <c r="G696" s="0"/>
-      <c r="H696" s="0"/>
-    </row>
-    <row r="697" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A697" s="0"/>
-      <c r="B697" s="0"/>
-      <c r="C697" s="0"/>
-      <c r="D697" s="0"/>
-      <c r="E697" s="0"/>
-      <c r="F697" s="0"/>
-      <c r="G697" s="0"/>
-      <c r="H697" s="0"/>
-    </row>
-    <row r="698" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A698" s="0"/>
-      <c r="B698" s="0"/>
-      <c r="C698" s="0"/>
-      <c r="D698" s="0"/>
-      <c r="E698" s="0"/>
-      <c r="F698" s="0"/>
-      <c r="G698" s="0"/>
-      <c r="H698" s="0"/>
-    </row>
-    <row r="699" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A699" s="0"/>
-      <c r="B699" s="0"/>
-      <c r="C699" s="0"/>
-      <c r="D699" s="0"/>
-      <c r="E699" s="0"/>
-      <c r="F699" s="0"/>
-      <c r="G699" s="0"/>
-      <c r="H699" s="0"/>
-    </row>
-    <row r="700" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A700" s="0"/>
-      <c r="B700" s="0"/>
-      <c r="C700" s="0"/>
-      <c r="D700" s="0"/>
-      <c r="E700" s="0"/>
-      <c r="F700" s="0"/>
-      <c r="G700" s="0"/>
-      <c r="H700" s="0"/>
-    </row>
-    <row r="701" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A701" s="0"/>
-      <c r="B701" s="0"/>
-      <c r="C701" s="0"/>
-      <c r="D701" s="0"/>
-      <c r="E701" s="0"/>
-      <c r="F701" s="0"/>
-      <c r="G701" s="0"/>
-      <c r="H701" s="0"/>
-    </row>
-    <row r="702" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A702" s="0"/>
-      <c r="B702" s="0"/>
-      <c r="C702" s="0"/>
-      <c r="D702" s="0"/>
-      <c r="E702" s="0"/>
-      <c r="F702" s="0"/>
-      <c r="G702" s="0"/>
-      <c r="H702" s="0"/>
-    </row>
-    <row r="703" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A703" s="0"/>
-      <c r="B703" s="0"/>
-      <c r="C703" s="0"/>
-      <c r="D703" s="0"/>
-      <c r="E703" s="0"/>
-      <c r="F703" s="0"/>
-      <c r="G703" s="0"/>
-      <c r="H703" s="0"/>
-    </row>
-    <row r="704" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A704" s="0"/>
-      <c r="B704" s="0"/>
-      <c r="C704" s="0"/>
-      <c r="D704" s="0"/>
-      <c r="E704" s="0"/>
-      <c r="F704" s="0"/>
-      <c r="G704" s="0"/>
-      <c r="H704" s="0"/>
-    </row>
-    <row r="705" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A705" s="0"/>
-      <c r="B705" s="0"/>
-      <c r="C705" s="0"/>
-      <c r="D705" s="0"/>
-      <c r="E705" s="0"/>
-      <c r="F705" s="0"/>
-      <c r="G705" s="0"/>
-      <c r="H705" s="0"/>
-    </row>
-    <row r="706" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A706" s="0"/>
-      <c r="B706" s="0"/>
-      <c r="C706" s="0"/>
-      <c r="D706" s="0"/>
-      <c r="E706" s="0"/>
-      <c r="F706" s="0"/>
-      <c r="G706" s="0"/>
-      <c r="H706" s="0"/>
-    </row>
-    <row r="707" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A707" s="0"/>
-      <c r="B707" s="0"/>
-      <c r="C707" s="0"/>
-      <c r="D707" s="0"/>
-      <c r="E707" s="0"/>
-      <c r="F707" s="0"/>
-      <c r="G707" s="0"/>
-      <c r="H707" s="0"/>
-    </row>
-    <row r="708" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A708" s="0"/>
-      <c r="B708" s="0"/>
-      <c r="C708" s="0"/>
-      <c r="D708" s="0"/>
-      <c r="E708" s="0"/>
-      <c r="F708" s="0"/>
-      <c r="G708" s="0"/>
-      <c r="H708" s="0"/>
-    </row>
-    <row r="709" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A709" s="0"/>
-      <c r="B709" s="0"/>
-      <c r="C709" s="0"/>
-      <c r="D709" s="0"/>
-      <c r="E709" s="0"/>
-      <c r="F709" s="0"/>
-      <c r="G709" s="0"/>
-      <c r="H709" s="0"/>
-    </row>
-    <row r="710" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A710" s="0"/>
-      <c r="B710" s="0"/>
-      <c r="C710" s="0"/>
-      <c r="D710" s="0"/>
-      <c r="E710" s="0"/>
-      <c r="F710" s="0"/>
-      <c r="G710" s="0"/>
-      <c r="H710" s="0"/>
-    </row>
-    <row r="711" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A711" s="0"/>
-      <c r="B711" s="0"/>
-      <c r="C711" s="0"/>
-      <c r="D711" s="0"/>
-      <c r="E711" s="0"/>
-      <c r="F711" s="0"/>
-      <c r="G711" s="0"/>
-      <c r="H711" s="0"/>
-    </row>
-    <row r="712" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A712" s="0"/>
-      <c r="B712" s="0"/>
-      <c r="C712" s="0"/>
-      <c r="D712" s="0"/>
-      <c r="E712" s="0"/>
-      <c r="F712" s="0"/>
-      <c r="G712" s="0"/>
-      <c r="H712" s="0"/>
-    </row>
-    <row r="713" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A713" s="0"/>
-      <c r="B713" s="0"/>
-      <c r="C713" s="0"/>
-      <c r="D713" s="0"/>
-      <c r="E713" s="0"/>
-      <c r="F713" s="0"/>
-      <c r="G713" s="0"/>
-      <c r="H713" s="0"/>
-    </row>
-    <row r="714" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A714" s="0"/>
-      <c r="B714" s="0"/>
-      <c r="C714" s="0"/>
-      <c r="D714" s="0"/>
-      <c r="E714" s="0"/>
-      <c r="F714" s="0"/>
-      <c r="G714" s="0"/>
-      <c r="H714" s="0"/>
-    </row>
-    <row r="715" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A715" s="0"/>
-      <c r="B715" s="0"/>
-      <c r="C715" s="0"/>
-      <c r="D715" s="0"/>
-      <c r="E715" s="0"/>
-      <c r="F715" s="0"/>
-      <c r="G715" s="0"/>
-      <c r="H715" s="0"/>
-    </row>
-    <row r="716" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A716" s="0"/>
-      <c r="B716" s="0"/>
-      <c r="C716" s="0"/>
-      <c r="D716" s="0"/>
-      <c r="E716" s="0"/>
-      <c r="F716" s="0"/>
-      <c r="G716" s="0"/>
-      <c r="H716" s="0"/>
-    </row>
-    <row r="717" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A717" s="0"/>
-      <c r="B717" s="0"/>
-      <c r="C717" s="0"/>
-      <c r="D717" s="0"/>
-      <c r="E717" s="0"/>
-      <c r="F717" s="0"/>
-      <c r="G717" s="0"/>
-      <c r="H717" s="0"/>
-    </row>
-    <row r="718" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A718" s="0"/>
-      <c r="B718" s="0"/>
-      <c r="C718" s="0"/>
-      <c r="D718" s="0"/>
-      <c r="E718" s="0"/>
-      <c r="F718" s="0"/>
-      <c r="G718" s="0"/>
-      <c r="H718" s="0"/>
-    </row>
-    <row r="719" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A719" s="0"/>
-      <c r="B719" s="0"/>
-      <c r="C719" s="0"/>
-      <c r="D719" s="0"/>
-      <c r="E719" s="0"/>
-      <c r="F719" s="0"/>
-      <c r="G719" s="0"/>
-      <c r="H719" s="0"/>
-    </row>
-    <row r="720" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A720" s="0"/>
-      <c r="B720" s="0"/>
-      <c r="C720" s="0"/>
-      <c r="D720" s="0"/>
-      <c r="E720" s="0"/>
-      <c r="F720" s="0"/>
-      <c r="G720" s="0"/>
-      <c r="H720" s="0"/>
-    </row>
-    <row r="721" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A721" s="0"/>
-      <c r="B721" s="0"/>
-      <c r="C721" s="0"/>
-      <c r="D721" s="0"/>
-      <c r="E721" s="0"/>
-      <c r="F721" s="0"/>
-      <c r="G721" s="0"/>
-      <c r="H721" s="0"/>
-    </row>
-    <row r="722" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A722" s="0"/>
-      <c r="B722" s="0"/>
-      <c r="C722" s="0"/>
-      <c r="D722" s="0"/>
-      <c r="E722" s="0"/>
-      <c r="F722" s="0"/>
-      <c r="G722" s="0"/>
-      <c r="H722" s="0"/>
-    </row>
-    <row r="723" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A723" s="0"/>
-      <c r="B723" s="0"/>
-      <c r="C723" s="0"/>
-      <c r="D723" s="0"/>
-      <c r="E723" s="0"/>
-      <c r="F723" s="0"/>
-      <c r="G723" s="0"/>
-      <c r="H723" s="0"/>
-    </row>
-    <row r="724" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A724" s="0"/>
-      <c r="B724" s="0"/>
-      <c r="C724" s="0"/>
-      <c r="D724" s="0"/>
-      <c r="E724" s="0"/>
-      <c r="F724" s="0"/>
-      <c r="G724" s="0"/>
-      <c r="H724" s="0"/>
-    </row>
-    <row r="725" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A725" s="0"/>
-      <c r="B725" s="0"/>
-      <c r="C725" s="0"/>
-      <c r="D725" s="0"/>
-      <c r="E725" s="0"/>
-      <c r="F725" s="0"/>
-      <c r="G725" s="0"/>
-      <c r="H725" s="0"/>
-    </row>
-    <row r="726" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A726" s="0"/>
-      <c r="B726" s="0"/>
-      <c r="C726" s="0"/>
-      <c r="D726" s="0"/>
-      <c r="E726" s="0"/>
-      <c r="F726" s="0"/>
-      <c r="G726" s="0"/>
-      <c r="H726" s="0"/>
-    </row>
-    <row r="727" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A727" s="0"/>
-      <c r="B727" s="0"/>
-      <c r="C727" s="0"/>
-      <c r="D727" s="0"/>
-      <c r="E727" s="0"/>
-      <c r="F727" s="0"/>
-      <c r="G727" s="0"/>
-      <c r="H727" s="0"/>
-    </row>
-    <row r="728" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A728" s="0"/>
-      <c r="B728" s="0"/>
-      <c r="C728" s="0"/>
-      <c r="D728" s="0"/>
-      <c r="E728" s="0"/>
-      <c r="F728" s="0"/>
-      <c r="G728" s="0"/>
-      <c r="H728" s="0"/>
-    </row>
-    <row r="729" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A729" s="0"/>
-      <c r="B729" s="0"/>
-      <c r="C729" s="0"/>
-      <c r="D729" s="0"/>
-      <c r="E729" s="0"/>
-      <c r="F729" s="0"/>
-      <c r="G729" s="0"/>
-      <c r="H729" s="0"/>
-    </row>
-    <row r="730" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A730" s="0"/>
-      <c r="B730" s="0"/>
-      <c r="C730" s="0"/>
-      <c r="D730" s="0"/>
-      <c r="E730" s="0"/>
-      <c r="F730" s="0"/>
-      <c r="G730" s="0"/>
-      <c r="H730" s="0"/>
-    </row>
-    <row r="731" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A731" s="0"/>
-      <c r="B731" s="0"/>
-      <c r="C731" s="0"/>
-      <c r="D731" s="0"/>
-      <c r="E731" s="0"/>
-      <c r="F731" s="0"/>
-      <c r="G731" s="0"/>
-      <c r="H731" s="0"/>
-    </row>
-    <row r="732" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A732" s="0"/>
-      <c r="B732" s="0"/>
-      <c r="C732" s="0"/>
-      <c r="D732" s="0"/>
-      <c r="E732" s="0"/>
-      <c r="F732" s="0"/>
-      <c r="G732" s="0"/>
-      <c r="H732" s="0"/>
-    </row>
-    <row r="733" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A733" s="0"/>
-      <c r="B733" s="0"/>
-      <c r="C733" s="0"/>
-      <c r="D733" s="0"/>
-      <c r="E733" s="0"/>
-      <c r="F733" s="0"/>
-      <c r="G733" s="0"/>
-      <c r="H733" s="0"/>
-    </row>
-    <row r="734" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A734" s="0"/>
-      <c r="B734" s="0"/>
-      <c r="C734" s="0"/>
-      <c r="D734" s="0"/>
-      <c r="E734" s="0"/>
-      <c r="F734" s="0"/>
-      <c r="G734" s="0"/>
-      <c r="H734" s="0"/>
-    </row>
-    <row r="735" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A735" s="0"/>
-      <c r="B735" s="0"/>
-      <c r="C735" s="0"/>
-      <c r="D735" s="0"/>
-      <c r="E735" s="0"/>
-      <c r="F735" s="0"/>
-      <c r="G735" s="0"/>
-      <c r="H735" s="0"/>
-    </row>
-    <row r="736" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A736" s="0"/>
-      <c r="B736" s="0"/>
-      <c r="C736" s="0"/>
-      <c r="D736" s="0"/>
-      <c r="E736" s="0"/>
-      <c r="F736" s="0"/>
-      <c r="G736" s="0"/>
-      <c r="H736" s="0"/>
-    </row>
-    <row r="737" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A737" s="0"/>
-      <c r="B737" s="0"/>
-      <c r="C737" s="0"/>
-      <c r="D737" s="0"/>
-      <c r="E737" s="0"/>
-      <c r="F737" s="0"/>
-      <c r="G737" s="0"/>
-      <c r="H737" s="0"/>
-    </row>
-    <row r="738" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A738" s="0"/>
-      <c r="B738" s="0"/>
-      <c r="C738" s="0"/>
-      <c r="D738" s="0"/>
-      <c r="E738" s="0"/>
-      <c r="F738" s="0"/>
-      <c r="G738" s="0"/>
-      <c r="H738" s="0"/>
-    </row>
-    <row r="739" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A739" s="0"/>
-      <c r="B739" s="0"/>
-      <c r="C739" s="0"/>
-      <c r="D739" s="0"/>
-      <c r="E739" s="0"/>
-      <c r="F739" s="0"/>
-      <c r="G739" s="0"/>
-      <c r="H739" s="0"/>
-    </row>
-    <row r="740" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A740" s="0"/>
-      <c r="B740" s="0"/>
-      <c r="C740" s="0"/>
-      <c r="D740" s="0"/>
-      <c r="E740" s="0"/>
-      <c r="F740" s="0"/>
-      <c r="G740" s="0"/>
-      <c r="H740" s="0"/>
-    </row>
-    <row r="741" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A741" s="0"/>
-      <c r="B741" s="0"/>
-      <c r="C741" s="0"/>
-      <c r="D741" s="0"/>
-      <c r="E741" s="0"/>
-      <c r="F741" s="0"/>
-      <c r="G741" s="0"/>
-      <c r="H741" s="0"/>
-    </row>
-    <row r="742" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A742" s="0"/>
-      <c r="B742" s="0"/>
-      <c r="C742" s="0"/>
-      <c r="D742" s="0"/>
-      <c r="E742" s="0"/>
-      <c r="F742" s="0"/>
-      <c r="G742" s="0"/>
-      <c r="H742" s="0"/>
-    </row>
-    <row r="743" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A743" s="0"/>
-      <c r="B743" s="0"/>
-      <c r="C743" s="0"/>
-      <c r="D743" s="0"/>
-      <c r="E743" s="0"/>
-      <c r="F743" s="0"/>
-      <c r="G743" s="0"/>
-      <c r="H743" s="0"/>
-    </row>
-    <row r="744" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A744" s="0"/>
-      <c r="B744" s="0"/>
-      <c r="C744" s="0"/>
-      <c r="D744" s="0"/>
-      <c r="E744" s="0"/>
-      <c r="F744" s="0"/>
-      <c r="G744" s="0"/>
-      <c r="H744" s="0"/>
-    </row>
-    <row r="745" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A745" s="0"/>
-      <c r="B745" s="0"/>
-      <c r="C745" s="0"/>
-      <c r="D745" s="0"/>
-      <c r="E745" s="0"/>
-      <c r="F745" s="0"/>
-      <c r="G745" s="0"/>
-      <c r="H745" s="0"/>
-    </row>
-    <row r="746" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A746" s="0"/>
-      <c r="B746" s="0"/>
-      <c r="C746" s="0"/>
-      <c r="D746" s="0"/>
-      <c r="E746" s="0"/>
-      <c r="F746" s="0"/>
-      <c r="G746" s="0"/>
-      <c r="H746" s="0"/>
-    </row>
-    <row r="747" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A747" s="0"/>
-      <c r="B747" s="0"/>
-      <c r="C747" s="0"/>
-      <c r="D747" s="0"/>
-      <c r="E747" s="0"/>
-      <c r="F747" s="0"/>
-      <c r="G747" s="0"/>
-      <c r="H747" s="0"/>
-    </row>
-    <row r="748" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A748" s="0"/>
-      <c r="B748" s="0"/>
-      <c r="C748" s="0"/>
-      <c r="D748" s="0"/>
-      <c r="E748" s="0"/>
-      <c r="F748" s="0"/>
-      <c r="G748" s="0"/>
-      <c r="H748" s="0"/>
-    </row>
-    <row r="749" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A749" s="0"/>
-      <c r="B749" s="0"/>
-      <c r="C749" s="0"/>
-      <c r="D749" s="0"/>
-      <c r="E749" s="0"/>
-      <c r="F749" s="0"/>
-      <c r="G749" s="0"/>
-      <c r="H749" s="0"/>
-    </row>
-    <row r="750" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A750" s="0"/>
-      <c r="B750" s="0"/>
-      <c r="C750" s="0"/>
-      <c r="D750" s="0"/>
-      <c r="E750" s="0"/>
-      <c r="F750" s="0"/>
-      <c r="G750" s="0"/>
-      <c r="H750" s="0"/>
-    </row>
-    <row r="751" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A751" s="0"/>
-      <c r="B751" s="0"/>
-      <c r="C751" s="0"/>
-      <c r="D751" s="0"/>
-      <c r="E751" s="0"/>
-      <c r="F751" s="0"/>
-      <c r="G751" s="0"/>
-      <c r="H751" s="0"/>
-    </row>
-    <row r="752" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A752" s="0"/>
-      <c r="B752" s="0"/>
-      <c r="C752" s="0"/>
-      <c r="D752" s="0"/>
-      <c r="E752" s="0"/>
-      <c r="F752" s="0"/>
-      <c r="G752" s="0"/>
-      <c r="H752" s="0"/>
-    </row>
-    <row r="753" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A753" s="0"/>
-      <c r="B753" s="0"/>
-      <c r="C753" s="0"/>
-      <c r="D753" s="0"/>
-      <c r="E753" s="0"/>
-      <c r="F753" s="0"/>
-      <c r="G753" s="0"/>
-      <c r="H753" s="0"/>
-    </row>
-    <row r="754" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A754" s="0"/>
-      <c r="B754" s="0"/>
-      <c r="C754" s="0"/>
-      <c r="D754" s="0"/>
-      <c r="E754" s="0"/>
-      <c r="F754" s="0"/>
-      <c r="G754" s="0"/>
-      <c r="H754" s="0"/>
-    </row>
-    <row r="755" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A755" s="0"/>
-      <c r="B755" s="0"/>
-      <c r="C755" s="0"/>
-      <c r="D755" s="0"/>
-      <c r="E755" s="0"/>
-      <c r="F755" s="0"/>
-      <c r="G755" s="0"/>
-      <c r="H755" s="0"/>
-    </row>
-    <row r="756" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A756" s="0"/>
-      <c r="B756" s="0"/>
-      <c r="C756" s="0"/>
-      <c r="D756" s="0"/>
-      <c r="E756" s="0"/>
-      <c r="F756" s="0"/>
-      <c r="G756" s="0"/>
-      <c r="H756" s="0"/>
-    </row>
-    <row r="757" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A757" s="0"/>
-      <c r="B757" s="0"/>
-      <c r="C757" s="0"/>
-      <c r="D757" s="0"/>
-      <c r="E757" s="0"/>
-      <c r="F757" s="0"/>
-      <c r="G757" s="0"/>
-      <c r="H757" s="0"/>
-    </row>
-    <row r="758" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A758" s="0"/>
-      <c r="B758" s="0"/>
-      <c r="C758" s="0"/>
-      <c r="D758" s="0"/>
-      <c r="E758" s="0"/>
-      <c r="F758" s="0"/>
-      <c r="G758" s="0"/>
-      <c r="H758" s="0"/>
-    </row>
-    <row r="759" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A759" s="0"/>
-      <c r="B759" s="0"/>
-      <c r="C759" s="0"/>
-      <c r="D759" s="0"/>
-      <c r="E759" s="0"/>
-      <c r="F759" s="0"/>
-      <c r="G759" s="0"/>
-      <c r="H759" s="0"/>
-    </row>
-    <row r="760" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A760" s="0"/>
-      <c r="B760" s="0"/>
-      <c r="C760" s="0"/>
-      <c r="D760" s="0"/>
-      <c r="E760" s="0"/>
-      <c r="F760" s="0"/>
-      <c r="G760" s="0"/>
-      <c r="H760" s="0"/>
-    </row>
-    <row r="761" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A761" s="0"/>
-      <c r="B761" s="0"/>
-      <c r="C761" s="0"/>
-      <c r="D761" s="0"/>
-      <c r="E761" s="0"/>
-      <c r="F761" s="0"/>
-      <c r="G761" s="0"/>
-      <c r="H761" s="0"/>
-    </row>
-    <row r="762" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A762" s="0"/>
-      <c r="B762" s="0"/>
-      <c r="C762" s="0"/>
-      <c r="D762" s="0"/>
-      <c r="E762" s="0"/>
-      <c r="F762" s="0"/>
-      <c r="G762" s="0"/>
-      <c r="H762" s="0"/>
-    </row>
-    <row r="763" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A763" s="0"/>
-      <c r="B763" s="0"/>
-      <c r="C763" s="0"/>
-      <c r="D763" s="0"/>
-      <c r="E763" s="0"/>
-      <c r="F763" s="0"/>
-      <c r="G763" s="0"/>
-      <c r="H763" s="0"/>
-    </row>
-    <row r="764" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A764" s="0"/>
-      <c r="B764" s="0"/>
-      <c r="C764" s="0"/>
-      <c r="D764" s="0"/>
-      <c r="E764" s="0"/>
-      <c r="F764" s="0"/>
-      <c r="G764" s="0"/>
-      <c r="H764" s="0"/>
-    </row>
-    <row r="765" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A765" s="0"/>
-      <c r="B765" s="0"/>
-      <c r="C765" s="0"/>
-      <c r="D765" s="0"/>
-      <c r="E765" s="0"/>
-      <c r="F765" s="0"/>
-      <c r="G765" s="0"/>
-      <c r="H765" s="0"/>
-    </row>
-    <row r="766" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A766" s="0"/>
-      <c r="B766" s="0"/>
-      <c r="C766" s="0"/>
-      <c r="D766" s="0"/>
-      <c r="E766" s="0"/>
-      <c r="F766" s="0"/>
-      <c r="G766" s="0"/>
-      <c r="H766" s="0"/>
-    </row>
-    <row r="767" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A767" s="0"/>
-      <c r="B767" s="0"/>
-      <c r="C767" s="0"/>
-      <c r="D767" s="0"/>
-      <c r="E767" s="0"/>
-      <c r="F767" s="0"/>
-      <c r="G767" s="0"/>
-      <c r="H767" s="0"/>
-    </row>
-    <row r="768" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A768" s="0"/>
-      <c r="B768" s="0"/>
-      <c r="C768" s="0"/>
-      <c r="D768" s="0"/>
-      <c r="E768" s="0"/>
-      <c r="F768" s="0"/>
-      <c r="G768" s="0"/>
-      <c r="H768" s="0"/>
-    </row>
-    <row r="769" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A769" s="0"/>
-      <c r="B769" s="0"/>
-      <c r="C769" s="0"/>
-      <c r="D769" s="0"/>
-      <c r="E769" s="0"/>
-      <c r="F769" s="0"/>
-      <c r="G769" s="0"/>
-      <c r="H769" s="0"/>
-    </row>
-    <row r="770" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A770" s="0"/>
-      <c r="B770" s="0"/>
-      <c r="C770" s="0"/>
-      <c r="D770" s="0"/>
-      <c r="E770" s="0"/>
-      <c r="F770" s="0"/>
-      <c r="G770" s="0"/>
-      <c r="H770" s="0"/>
-    </row>
-    <row r="771" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A771" s="0"/>
-      <c r="B771" s="0"/>
-      <c r="C771" s="0"/>
-      <c r="D771" s="0"/>
-      <c r="E771" s="0"/>
-      <c r="F771" s="0"/>
-      <c r="G771" s="0"/>
-      <c r="H771" s="0"/>
-    </row>
-    <row r="772" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A772" s="0"/>
-      <c r="B772" s="0"/>
-      <c r="C772" s="0"/>
-      <c r="D772" s="0"/>
-      <c r="E772" s="0"/>
-      <c r="F772" s="0"/>
-      <c r="G772" s="0"/>
-      <c r="H772" s="0"/>
-    </row>
-    <row r="773" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A773" s="0"/>
-      <c r="B773" s="0"/>
-      <c r="C773" s="0"/>
-      <c r="D773" s="0"/>
-      <c r="E773" s="0"/>
-      <c r="F773" s="0"/>
-      <c r="G773" s="0"/>
-      <c r="H773" s="0"/>
-    </row>
-    <row r="774" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A774" s="0"/>
-      <c r="B774" s="0"/>
-      <c r="C774" s="0"/>
-      <c r="D774" s="0"/>
-      <c r="E774" s="0"/>
-      <c r="F774" s="0"/>
-      <c r="G774" s="0"/>
-      <c r="H774" s="0"/>
-    </row>
-    <row r="775" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A775" s="0"/>
-      <c r="B775" s="0"/>
-      <c r="C775" s="0"/>
-      <c r="D775" s="0"/>
-      <c r="E775" s="0"/>
-      <c r="F775" s="0"/>
-      <c r="G775" s="0"/>
-      <c r="H775" s="0"/>
-    </row>
-    <row r="776" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A776" s="0"/>
-      <c r="B776" s="0"/>
-      <c r="C776" s="0"/>
-      <c r="D776" s="0"/>
-      <c r="E776" s="0"/>
-      <c r="F776" s="0"/>
-      <c r="G776" s="0"/>
-      <c r="H776" s="0"/>
-    </row>
-    <row r="777" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A777" s="0"/>
-      <c r="B777" s="0"/>
-      <c r="C777" s="0"/>
-      <c r="D777" s="0"/>
-      <c r="E777" s="0"/>
-      <c r="F777" s="0"/>
-      <c r="G777" s="0"/>
-      <c r="H777" s="0"/>
-    </row>
-    <row r="778" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A778" s="0"/>
-      <c r="B778" s="0"/>
-      <c r="C778" s="0"/>
-      <c r="D778" s="0"/>
-      <c r="E778" s="0"/>
-      <c r="F778" s="0"/>
-      <c r="G778" s="0"/>
-      <c r="H778" s="0"/>
-    </row>
-    <row r="779" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A779" s="0"/>
-      <c r="B779" s="0"/>
-      <c r="C779" s="0"/>
-      <c r="D779" s="0"/>
-      <c r="E779" s="0"/>
-      <c r="F779" s="0"/>
-      <c r="G779" s="0"/>
-      <c r="H779" s="0"/>
-    </row>
-    <row r="780" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A780" s="0"/>
-      <c r="B780" s="0"/>
-      <c r="C780" s="0"/>
-      <c r="D780" s="0"/>
-      <c r="E780" s="0"/>
-      <c r="F780" s="0"/>
-      <c r="G780" s="0"/>
-      <c r="H780" s="0"/>
-    </row>
-    <row r="781" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A781" s="0"/>
-      <c r="B781" s="0"/>
-      <c r="C781" s="0"/>
-      <c r="D781" s="0"/>
-      <c r="E781" s="0"/>
-      <c r="F781" s="0"/>
-      <c r="G781" s="0"/>
-      <c r="H781" s="0"/>
-    </row>
-    <row r="782" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A782" s="0"/>
-      <c r="B782" s="0"/>
-      <c r="C782" s="0"/>
-      <c r="D782" s="0"/>
-      <c r="E782" s="0"/>
-      <c r="F782" s="0"/>
-      <c r="G782" s="0"/>
-      <c r="H782" s="0"/>
-    </row>
-    <row r="783" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A783" s="0"/>
-      <c r="B783" s="0"/>
-      <c r="C783" s="0"/>
-      <c r="D783" s="0"/>
-      <c r="E783" s="0"/>
-      <c r="F783" s="0"/>
-      <c r="G783" s="0"/>
-      <c r="H783" s="0"/>
-    </row>
-    <row r="784" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A784" s="0"/>
-      <c r="B784" s="0"/>
-      <c r="C784" s="0"/>
-      <c r="D784" s="0"/>
-      <c r="E784" s="0"/>
-      <c r="F784" s="0"/>
-      <c r="G784" s="0"/>
-      <c r="H784" s="0"/>
-    </row>
-    <row r="785" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A785" s="0"/>
-      <c r="B785" s="0"/>
-      <c r="C785" s="0"/>
-      <c r="D785" s="0"/>
-      <c r="E785" s="0"/>
-      <c r="F785" s="0"/>
-      <c r="G785" s="0"/>
-      <c r="H785" s="0"/>
-    </row>
-    <row r="786" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A786" s="0"/>
-      <c r="B786" s="0"/>
-      <c r="C786" s="0"/>
-      <c r="D786" s="0"/>
-      <c r="E786" s="0"/>
-      <c r="F786" s="0"/>
-      <c r="G786" s="0"/>
-      <c r="H786" s="0"/>
-    </row>
-    <row r="787" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A787" s="0"/>
-      <c r="B787" s="0"/>
-      <c r="C787" s="0"/>
-      <c r="D787" s="0"/>
-      <c r="E787" s="0"/>
-      <c r="F787" s="0"/>
-      <c r="G787" s="0"/>
-      <c r="H787" s="0"/>
-    </row>
-    <row r="788" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A788" s="0"/>
-      <c r="B788" s="0"/>
-      <c r="C788" s="0"/>
-      <c r="D788" s="0"/>
-      <c r="E788" s="0"/>
-      <c r="F788" s="0"/>
-      <c r="G788" s="0"/>
-      <c r="H788" s="0"/>
-    </row>
-    <row r="789" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A789" s="0"/>
-      <c r="B789" s="0"/>
-      <c r="C789" s="0"/>
-      <c r="D789" s="0"/>
-      <c r="E789" s="0"/>
-      <c r="F789" s="0"/>
-      <c r="G789" s="0"/>
-      <c r="H789" s="0"/>
-    </row>
-    <row r="790" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A790" s="0"/>
-      <c r="B790" s="0"/>
-      <c r="C790" s="0"/>
-      <c r="D790" s="0"/>
-      <c r="E790" s="0"/>
-      <c r="F790" s="0"/>
-      <c r="G790" s="0"/>
-      <c r="H790" s="0"/>
-    </row>
-    <row r="791" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A791" s="0"/>
-      <c r="B791" s="0"/>
-      <c r="C791" s="0"/>
-      <c r="D791" s="0"/>
-      <c r="E791" s="0"/>
-      <c r="F791" s="0"/>
-      <c r="G791" s="0"/>
-      <c r="H791" s="0"/>
-    </row>
-    <row r="792" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A792" s="0"/>
-      <c r="B792" s="0"/>
-      <c r="C792" s="0"/>
-      <c r="D792" s="0"/>
-      <c r="E792" s="0"/>
-      <c r="F792" s="0"/>
-      <c r="G792" s="0"/>
-      <c r="H792" s="0"/>
-    </row>
-    <row r="793" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A793" s="0"/>
-      <c r="B793" s="0"/>
-      <c r="C793" s="0"/>
-      <c r="D793" s="0"/>
-      <c r="E793" s="0"/>
-      <c r="F793" s="0"/>
-      <c r="G793" s="0"/>
-      <c r="H793" s="0"/>
-    </row>
-    <row r="794" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A794" s="0"/>
-      <c r="B794" s="0"/>
-      <c r="C794" s="0"/>
-      <c r="D794" s="0"/>
-      <c r="E794" s="0"/>
-      <c r="F794" s="0"/>
-      <c r="G794" s="0"/>
-      <c r="H794" s="0"/>
+      <c r="J654" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
